--- a/research/traditional_assets/database/data/switzerland/switzerland_beverage_soft.xlsx
+++ b/research/traditional_assets/database/data/switzerland/switzerland_beverage_soft.xlsx
@@ -650,10 +650,10 @@
         <v>0.2065475827592514</v>
       </c>
       <c r="X2">
-        <v>0.08274789221960682</v>
+        <v>0.08272413800996634</v>
       </c>
       <c r="Y2">
-        <v>0.1237996905396445</v>
+        <v>0.123823444749285</v>
       </c>
       <c r="Z2">
         <v>1.914927824358199</v>
@@ -662,10 +662,10 @@
         <v>0.1244795660790922</v>
       </c>
       <c r="AB2">
-        <v>0.0737703418967371</v>
+        <v>0.07375275427117015</v>
       </c>
       <c r="AC2">
-        <v>0.05070922418235513</v>
+        <v>0.05072681180792209</v>
       </c>
       <c r="AD2">
         <v>4341.7</v>
@@ -787,10 +787,10 @@
         <v>0.2065475827592514</v>
       </c>
       <c r="X3">
-        <v>0.08274789221960682</v>
+        <v>0.08272413800996634</v>
       </c>
       <c r="Y3">
-        <v>0.1237996905396445</v>
+        <v>0.123823444749285</v>
       </c>
       <c r="Z3">
         <v>1.914927824358199</v>
@@ -799,10 +799,10 @@
         <v>0.1244795660790922</v>
       </c>
       <c r="AB3">
-        <v>0.0737703418967371</v>
+        <v>0.07375275427117015</v>
       </c>
       <c r="AC3">
-        <v>0.05070922418235513</v>
+        <v>0.05072681180792209</v>
       </c>
       <c r="AD3">
         <v>4341.7</v>
@@ -1139,49 +1139,49 @@
         <v>9.550000000000001</v>
       </c>
       <c r="F2">
-        <v>6.87050315776159</v>
+        <v>3.01400891178672</v>
       </c>
       <c r="G2">
         <v>3.16635064177363</v>
       </c>
       <c r="H2">
-        <v>2.07349912485414</v>
+        <v>4.51290985997666</v>
       </c>
       <c r="I2">
         <v>0.259599631680279</v>
       </c>
       <c r="J2">
-        <v>0.17</v>
+        <v>0.37</v>
       </c>
       <c r="K2">
         <v>12382.9</v>
       </c>
       <c r="L2">
-        <v>14085.7483882684</v>
+        <v>10845.4860228087</v>
       </c>
       <c r="M2">
         <v>15555.4</v>
       </c>
       <c r="N2">
-        <v>15759.7303882684</v>
+        <v>15864.3880228087</v>
       </c>
       <c r="O2">
         <v>4341.7</v>
       </c>
       <c r="P2">
-        <v>2843.182</v>
+        <v>6188.102</v>
       </c>
       <c r="Q2">
-        <v>0.0737703418967371</v>
+        <v>0.0737527542711701</v>
       </c>
       <c r="R2">
-        <v>0.07340769668143481</v>
+        <v>0.07320832316787849</v>
       </c>
       <c r="S2">
         <v>0.0481656</v>
       </c>
       <c r="T2">
-        <v>0.0450912</v>
+        <v>0.0472262</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -1190,20 +1190,20 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="W2">
-        <v>0.08274789221960679</v>
+        <v>0.08272413800996629</v>
       </c>
       <c r="X2">
-        <v>0.0792074610619697</v>
+        <v>0.0884676653458388</v>
       </c>
       <c r="Y2">
         <v>0.852751455195527</v>
       </c>
       <c r="Z2">
-        <v>0.771038869163555</v>
+        <v>0.985396428310365</v>
       </c>
       <c r="AA2">
         <v>4341.7</v>
@@ -1236,7 +1236,7 @@
         <v>12382.9</v>
       </c>
       <c r="AK2">
-        <v>0.043327855959079</v>
+        <v>0.04330000000000001</v>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
@@ -1424,13 +1424,13 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>0.07423392264139422</v>
+        <v>0.07421564215721098</v>
       </c>
       <c r="C2">
-        <v>16470.98800258459</v>
+        <v>16471.20413505058</v>
       </c>
       <c r="D2">
-        <v>15301.78800258458</v>
+        <v>15302.00413505058</v>
       </c>
       <c r="E2">
         <v>-4341.7</v>
@@ -1475,19 +1475,19 @@
         <v>0</v>
       </c>
       <c r="S2">
-        <v>0.07423392264139422</v>
+        <v>0.07421564215721098</v>
       </c>
       <c r="T2">
         <v>0.6562503962404382</v>
       </c>
       <c r="U2">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V2">
         <v>0.146</v>
       </c>
       <c r="W2">
-        <v>0.0441518</v>
+        <v>0.0429562</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
@@ -1506,13 +1506,13 @@
         <v>0.01</v>
       </c>
       <c r="B3">
-        <v>0.07417592711433779</v>
+        <v>0.07414571731966144</v>
       </c>
       <c r="C3">
-        <v>16335.0162321997</v>
+        <v>16341.70599449825</v>
       </c>
       <c r="D3">
-        <v>15333.0622321997</v>
+        <v>15339.75199449825</v>
       </c>
       <c r="E3">
         <v>-4174.454</v>
@@ -1539,37 +1539,37 @@
         <v>1031.4</v>
       </c>
       <c r="M3">
-        <v>8.646618199999999</v>
+        <v>8.412473799999999</v>
       </c>
       <c r="N3">
-        <v>1022.7533818</v>
+        <v>1022.9875262</v>
       </c>
       <c r="O3">
-        <v>149.3219937428</v>
+        <v>149.3561788252</v>
       </c>
       <c r="P3">
-        <v>873.4313880572</v>
+        <v>873.6313473748</v>
       </c>
       <c r="Q3">
-        <v>1213.2313880572</v>
+        <v>1213.4313473748</v>
       </c>
       <c r="R3">
         <v>0.0101010101010101</v>
       </c>
       <c r="S3">
-        <v>0.07447920112559372</v>
+        <v>0.07446076294915298</v>
       </c>
       <c r="T3">
         <v>0.6619113845069972</v>
       </c>
       <c r="U3">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V3">
         <v>0.146</v>
       </c>
       <c r="W3">
-        <v>0.0441518</v>
+        <v>0.0429562</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>119.2836292922012</v>
+        <v>122.6036507834354</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1588,13 +1588,13 @@
         <v>0.02</v>
       </c>
       <c r="B4">
-        <v>0.07411793158728136</v>
+        <v>0.07407579248211192</v>
       </c>
       <c r="C4">
-        <v>16199.17256194983</v>
+        <v>16212.39455166207</v>
       </c>
       <c r="D4">
-        <v>15364.46456194984</v>
+        <v>15377.68655166207</v>
       </c>
       <c r="E4">
         <v>-4007.208</v>
@@ -1621,37 +1621,37 @@
         <v>1031.4</v>
       </c>
       <c r="M4">
-        <v>17.2932364</v>
+        <v>16.8249476</v>
       </c>
       <c r="N4">
-        <v>1014.1067636</v>
+        <v>1014.5750524</v>
       </c>
       <c r="O4">
-        <v>148.0595874856</v>
+        <v>148.1279576504</v>
       </c>
       <c r="P4">
-        <v>866.0471761144001</v>
+        <v>866.4470947496001</v>
       </c>
       <c r="Q4">
-        <v>1205.8471761144</v>
+        <v>1206.2470947496</v>
       </c>
       <c r="R4">
         <v>0.02040816326530612</v>
       </c>
       <c r="S4">
-        <v>0.07472948529314424</v>
+        <v>0.07471088620623666</v>
       </c>
       <c r="T4">
         <v>0.667687903146343</v>
       </c>
       <c r="U4">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V4">
         <v>0.146</v>
       </c>
       <c r="W4">
-        <v>0.0441518</v>
+        <v>0.0429562</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>59.64181464610061</v>
+        <v>61.30182539171773</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1670,13 +1670,13 @@
         <v>0.03</v>
       </c>
       <c r="B5">
-        <v>0.07405993606022493</v>
+        <v>0.07400586764456239</v>
       </c>
       <c r="C5">
-        <v>16063.45778050288</v>
+        <v>16083.27119506247</v>
       </c>
       <c r="D5">
-        <v>15395.99578050288</v>
+        <v>15415.80919506247</v>
       </c>
       <c r="E5">
         <v>-3839.962</v>
@@ -1703,37 +1703,37 @@
         <v>1031.4</v>
       </c>
       <c r="M5">
-        <v>25.9398546</v>
+        <v>25.2374214</v>
       </c>
       <c r="N5">
-        <v>1005.4601454</v>
+        <v>1006.1625786</v>
       </c>
       <c r="O5">
-        <v>146.7971812284</v>
+        <v>146.8997364756</v>
       </c>
       <c r="P5">
-        <v>858.6629641716002</v>
+        <v>859.2628421244001</v>
       </c>
       <c r="Q5">
-        <v>1198.4629641716</v>
+        <v>1199.0628421244</v>
       </c>
       <c r="R5">
         <v>0.03092783505154639</v>
       </c>
       <c r="S5">
-        <v>0.07498492995899476</v>
+        <v>0.07496616664387876</v>
       </c>
       <c r="T5">
         <v>0.6735835252627888</v>
       </c>
       <c r="U5">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V5">
         <v>0.146</v>
       </c>
       <c r="W5">
-        <v>0.0441518</v>
+        <v>0.0429562</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>39.76120976406708</v>
+        <v>40.86788359447849</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1752,13 +1752,13 @@
         <v>0.04</v>
       </c>
       <c r="B6">
-        <v>0.07400194053316847</v>
+        <v>0.07393594280701286</v>
       </c>
       <c r="C6">
-        <v>15927.87268301415</v>
+        <v>15954.33732702311</v>
       </c>
       <c r="D6">
-        <v>15427.65668301415</v>
+        <v>15454.12132702311</v>
       </c>
       <c r="E6">
         <v>-3672.716</v>
@@ -1785,37 +1785,37 @@
         <v>1031.4</v>
       </c>
       <c r="M6">
-        <v>34.5864728</v>
+        <v>33.6498952</v>
       </c>
       <c r="N6">
-        <v>996.8135272000001</v>
+        <v>997.7501048000001</v>
       </c>
       <c r="O6">
-        <v>145.5347749712</v>
+        <v>145.6715153008</v>
       </c>
       <c r="P6">
-        <v>851.2787522288</v>
+        <v>852.0785894992001</v>
       </c>
       <c r="Q6">
-        <v>1191.0787522288</v>
+        <v>1191.8785894992</v>
       </c>
       <c r="R6">
         <v>0.04166666666666667</v>
       </c>
       <c r="S6">
-        <v>0.07524569638871717</v>
+        <v>0.07522676542397173</v>
       </c>
       <c r="T6">
         <v>0.6796019728399938</v>
       </c>
       <c r="U6">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V6">
         <v>0.146</v>
       </c>
       <c r="W6">
-        <v>0.0441518</v>
+        <v>0.0429562</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
@@ -1823,7 +1823,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>29.82090732305031</v>
+        <v>30.65091269585886</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1834,13 +1834,13 @@
         <v>0.05</v>
       </c>
       <c r="B7">
-        <v>0.07394394500611204</v>
+        <v>0.07386601796946332</v>
       </c>
       <c r="C7">
-        <v>15792.41807119313</v>
+        <v>15825.5943638429</v>
       </c>
       <c r="D7">
-        <v>15459.44807119313</v>
+        <v>15492.6243638429</v>
       </c>
       <c r="E7">
         <v>-3505.47</v>
@@ -1867,37 +1867,37 @@
         <v>1031.4</v>
       </c>
       <c r="M7">
-        <v>43.233091</v>
+        <v>42.062369</v>
       </c>
       <c r="N7">
-        <v>988.166909</v>
+        <v>989.3376310000001</v>
       </c>
       <c r="O7">
-        <v>144.272368714</v>
+        <v>144.443294126</v>
       </c>
       <c r="P7">
-        <v>843.8945402860001</v>
+        <v>844.8943368740001</v>
       </c>
       <c r="Q7">
-        <v>1183.694540286</v>
+        <v>1184.694336874</v>
       </c>
       <c r="R7">
         <v>0.05263157894736843</v>
       </c>
       <c r="S7">
-        <v>0.07551195263801268</v>
+        <v>0.07549285049417193</v>
       </c>
       <c r="T7">
         <v>0.6857471245767189</v>
       </c>
       <c r="U7">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V7">
         <v>0.146</v>
       </c>
       <c r="W7">
-        <v>0.0441518</v>
+        <v>0.0429562</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
@@ -1905,7 +1905,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>23.85672585844024</v>
+        <v>24.52073015668709</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1916,13 +1916,13 @@
         <v>0.06</v>
       </c>
       <c r="B8">
-        <v>0.07388594947905561</v>
+        <v>0.07379609313191381</v>
       </c>
       <c r="C8">
-        <v>15657.09475337124</v>
+        <v>15697.04373597046</v>
       </c>
       <c r="D8">
-        <v>15491.37075337124</v>
+        <v>15531.31973597046</v>
       </c>
       <c r="E8">
         <v>-3338.224</v>
@@ -1949,37 +1949,37 @@
         <v>1031.4</v>
       </c>
       <c r="M8">
-        <v>51.87970919999999</v>
+        <v>50.47484279999999</v>
       </c>
       <c r="N8">
-        <v>979.5202908000001</v>
+        <v>980.9251572000001</v>
       </c>
       <c r="O8">
-        <v>143.0099624568</v>
+        <v>143.2150729512</v>
       </c>
       <c r="P8">
-        <v>836.5103283432002</v>
+        <v>837.7100842488001</v>
       </c>
       <c r="Q8">
-        <v>1176.3103283432</v>
+        <v>1177.5100842488</v>
       </c>
       <c r="R8">
         <v>0.06382978723404255</v>
       </c>
       <c r="S8">
-        <v>0.07578387391388895</v>
+        <v>0.07576459694884448</v>
       </c>
       <c r="T8">
         <v>0.6920230242227362</v>
       </c>
       <c r="U8">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V8">
         <v>0.146</v>
       </c>
       <c r="W8">
-        <v>0.0441518</v>
+        <v>0.0429562</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
@@ -1987,7 +1987,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>19.88060488203354</v>
+        <v>20.43394179723924</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1998,13 +1998,13 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="B9">
-        <v>0.07382795395199918</v>
+        <v>0.07372616829436429</v>
       </c>
       <c r="C9">
-        <v>15521.90354457031</v>
+        <v>15568.68688818138</v>
       </c>
       <c r="D9">
-        <v>15523.42554457031</v>
+        <v>15570.20888818138</v>
       </c>
       <c r="E9">
         <v>-3170.978</v>
@@ -2031,37 +2031,37 @@
         <v>1031.4</v>
       </c>
       <c r="M9">
-        <v>60.5263274</v>
+        <v>58.8873166</v>
       </c>
       <c r="N9">
-        <v>970.8736726000001</v>
+        <v>972.5126834000001</v>
       </c>
       <c r="O9">
-        <v>141.7475561996</v>
+        <v>141.9868517764</v>
       </c>
       <c r="P9">
-        <v>829.1261164004001</v>
+        <v>830.5258316236001</v>
       </c>
       <c r="Q9">
-        <v>1168.9261164004</v>
+        <v>1170.3258316236</v>
       </c>
       <c r="R9">
         <v>0.07526881720430109</v>
       </c>
       <c r="S9">
-        <v>0.07606164295913891</v>
+        <v>0.07604218741329494</v>
       </c>
       <c r="T9">
         <v>0.6984338894525387</v>
       </c>
       <c r="U9">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V9">
         <v>0.146</v>
       </c>
       <c r="W9">
-        <v>0.0441518</v>
+        <v>0.0429562</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
@@ -2069,7 +2069,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>17.04051847031446</v>
+        <v>17.51480725477649</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2080,13 +2080,13 @@
         <v>0.08</v>
       </c>
       <c r="B10">
-        <v>0.07376995842494274</v>
+        <v>0.07365624345681475</v>
       </c>
       <c r="C10">
-        <v>15386.84526657191</v>
+        <v>15440.52527975796</v>
       </c>
       <c r="D10">
-        <v>15555.61326657191</v>
+        <v>15609.29327975796</v>
       </c>
       <c r="E10">
         <v>-3003.732</v>
@@ -2113,37 +2113,37 @@
         <v>1031.4</v>
       </c>
       <c r="M10">
-        <v>69.17294559999999</v>
+        <v>67.29979039999999</v>
       </c>
       <c r="N10">
-        <v>962.2270544</v>
+        <v>964.1002096000001</v>
       </c>
       <c r="O10">
-        <v>140.4851499424</v>
+        <v>140.7586306016</v>
       </c>
       <c r="P10">
-        <v>821.7419044576001</v>
+        <v>823.3415789984001</v>
       </c>
       <c r="Q10">
-        <v>1161.5419044576</v>
+        <v>1163.1415789984</v>
       </c>
       <c r="R10">
         <v>0.08695652173913043</v>
       </c>
       <c r="S10">
-        <v>0.07634545046189428</v>
+        <v>0.07632581245305951</v>
       </c>
       <c r="T10">
         <v>0.7049841213177717</v>
       </c>
       <c r="U10">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V10">
         <v>0.146</v>
       </c>
       <c r="W10">
-        <v>0.0441518</v>
+        <v>0.0429562</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>14.91045366152515</v>
+        <v>15.32545634792943</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2162,13 +2162,13 @@
         <v>0.09</v>
       </c>
       <c r="B11">
-        <v>0.07371196289788631</v>
+        <v>0.07358631861926523</v>
       </c>
       <c r="C11">
-        <v>15251.92074798766</v>
+        <v>15312.56038467169</v>
       </c>
       <c r="D11">
-        <v>15587.93474798766</v>
+        <v>15648.57438467169</v>
       </c>
       <c r="E11">
         <v>-2836.486</v>
@@ -2195,37 +2195,37 @@
         <v>1031.4</v>
       </c>
       <c r="M11">
-        <v>77.81956379999998</v>
+        <v>75.71226419999998</v>
       </c>
       <c r="N11">
-        <v>953.5804362000001</v>
+        <v>955.6877358000002</v>
       </c>
       <c r="O11">
-        <v>139.2227436852</v>
+        <v>139.5304094268</v>
       </c>
       <c r="P11">
-        <v>814.3576925148001</v>
+        <v>816.1573263732001</v>
       </c>
       <c r="Q11">
-        <v>1154.1576925148</v>
+        <v>1155.9573263732</v>
       </c>
       <c r="R11">
         <v>0.0989010989010989</v>
       </c>
       <c r="S11">
-        <v>0.07663549549218275</v>
+        <v>0.07661567101018157</v>
       </c>
       <c r="T11">
         <v>0.7116783143228999</v>
       </c>
       <c r="U11">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V11">
         <v>0.146</v>
       </c>
       <c r="W11">
-        <v>0.0441518</v>
+        <v>0.0429562</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
@@ -2233,7 +2233,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>13.25373658802236</v>
+        <v>13.62262786482616</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2244,13 +2244,13 @@
         <v>0.1</v>
       </c>
       <c r="B12">
-        <v>0.07365396737082987</v>
+        <v>0.07351639378171571</v>
       </c>
       <c r="C12">
-        <v>15117.13082433022</v>
+        <v>15184.7936917687</v>
       </c>
       <c r="D12">
-        <v>15620.39082433022</v>
+        <v>15688.05369176869</v>
       </c>
       <c r="E12">
         <v>-2669.24</v>
@@ -2277,37 +2277,37 @@
         <v>1031.4</v>
       </c>
       <c r="M12">
-        <v>86.466182</v>
+        <v>84.12473799999999</v>
       </c>
       <c r="N12">
-        <v>944.9338180000001</v>
+        <v>947.2752620000001</v>
       </c>
       <c r="O12">
-        <v>137.960337428</v>
+        <v>138.302188252</v>
       </c>
       <c r="P12">
-        <v>806.9734805720001</v>
+        <v>808.9730737480002</v>
       </c>
       <c r="Q12">
-        <v>1146.773480572</v>
+        <v>1148.773073748</v>
       </c>
       <c r="R12">
         <v>0.1111111111111111</v>
       </c>
       <c r="S12">
-        <v>0.07693198596758874</v>
+        <v>0.076911970868573</v>
       </c>
       <c r="T12">
         <v>0.7185212671725865</v>
       </c>
       <c r="U12">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V12">
         <v>0.146</v>
       </c>
       <c r="W12">
-        <v>0.0441518</v>
+        <v>0.0429562</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
@@ -2315,7 +2315,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>11.92836292922012</v>
+        <v>12.26036507834355</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2326,13 +2326,13 @@
         <v>0.11</v>
       </c>
       <c r="B13">
-        <v>0.07359597184377345</v>
+        <v>0.07344646894416618</v>
       </c>
       <c r="C13">
-        <v>14982.47633808538</v>
+        <v>15057.22670495771</v>
       </c>
       <c r="D13">
-        <v>15652.98233808538</v>
+        <v>15727.73270495771</v>
       </c>
       <c r="E13">
         <v>-2501.994</v>
@@ -2359,37 +2359,37 @@
         <v>1031.4</v>
       </c>
       <c r="M13">
-        <v>95.1128002</v>
+        <v>92.53721179999999</v>
       </c>
       <c r="N13">
-        <v>936.2871998000001</v>
+        <v>938.8627882000001</v>
       </c>
       <c r="O13">
-        <v>136.6979311708</v>
+        <v>137.0739670772</v>
       </c>
       <c r="P13">
-        <v>799.5892686292001</v>
+        <v>801.7888211228001</v>
       </c>
       <c r="Q13">
-        <v>1139.3892686292</v>
+        <v>1141.5888211228</v>
       </c>
       <c r="R13">
         <v>0.1235955056179775</v>
       </c>
       <c r="S13">
-        <v>0.07723513915030723</v>
+        <v>0.07721492915074851</v>
       </c>
       <c r="T13">
         <v>0.7255179942436144</v>
       </c>
       <c r="U13">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V13">
         <v>0.146</v>
       </c>
       <c r="W13">
-        <v>0.0441518</v>
+        <v>0.0429562</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
@@ -2397,7 +2397,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>10.84396629929102</v>
+        <v>11.14578643485777</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2408,13 +2408,13 @@
         <v>0.12</v>
       </c>
       <c r="B14">
-        <v>0.073537976316717</v>
+        <v>0.07337654410661665</v>
       </c>
       <c r="C14">
-        <v>14847.95813878493</v>
+        <v>14929.8609434011</v>
       </c>
       <c r="D14">
-        <v>15685.71013878493</v>
+        <v>15767.6129434011</v>
       </c>
       <c r="E14">
         <v>-2334.748</v>
@@ -2441,37 +2441,37 @@
         <v>1031.4</v>
       </c>
       <c r="M14">
-        <v>103.7594184</v>
+        <v>100.9496856</v>
       </c>
       <c r="N14">
-        <v>927.6405816000001</v>
+        <v>930.4503144000001</v>
       </c>
       <c r="O14">
-        <v>135.4355249136</v>
+        <v>135.8457459024</v>
       </c>
       <c r="P14">
-        <v>792.2050566864001</v>
+        <v>794.6045684976001</v>
       </c>
       <c r="Q14">
-        <v>1132.0050566864</v>
+        <v>1134.4045684976</v>
       </c>
       <c r="R14">
         <v>0.1363636363636364</v>
       </c>
       <c r="S14">
-        <v>0.07754518217808751</v>
+        <v>0.077524772848428</v>
       </c>
       <c r="T14">
         <v>0.7326737378389837</v>
       </c>
       <c r="U14">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V14">
         <v>0.146</v>
       </c>
       <c r="W14">
-        <v>0.0441518</v>
+        <v>0.0429562</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
@@ -2479,7 +2479,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>9.940302441016769</v>
+        <v>10.21697089861962</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2490,13 +2490,13 @@
         <v>0.13</v>
       </c>
       <c r="B15">
-        <v>0.07347998078966056</v>
+        <v>0.07330661926906712</v>
       </c>
       <c r="C15">
-        <v>14713.57708308046</v>
+        <v>14802.69794170875</v>
       </c>
       <c r="D15">
-        <v>15718.57508308046</v>
+        <v>15807.69594170875</v>
       </c>
       <c r="E15">
         <v>-2167.502</v>
@@ -2523,37 +2523,37 @@
         <v>1031.4</v>
       </c>
       <c r="M15">
-        <v>112.4060366</v>
+        <v>109.3621594</v>
       </c>
       <c r="N15">
-        <v>918.9939634000001</v>
+        <v>922.0378406000001</v>
       </c>
       <c r="O15">
-        <v>134.1731186564</v>
+        <v>134.6175247276</v>
       </c>
       <c r="P15">
-        <v>784.8208447436001</v>
+        <v>787.4203158724001</v>
       </c>
       <c r="Q15">
-        <v>1124.6208447436</v>
+        <v>1127.2203158724</v>
       </c>
       <c r="R15">
         <v>0.1494252873563219</v>
       </c>
       <c r="S15">
-        <v>0.07786235263179375</v>
+        <v>0.07784173938973232</v>
       </c>
       <c r="T15">
         <v>0.7399939812871204</v>
       </c>
       <c r="U15">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V15">
         <v>0.146</v>
       </c>
       <c r="W15">
-        <v>0.0441518</v>
+        <v>0.0429562</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
@@ -2561,7 +2561,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>9.175663791707786</v>
+        <v>9.431050060264266</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2572,13 +2572,13 @@
         <v>0.14</v>
       </c>
       <c r="B16">
-        <v>0.07355350126260413</v>
+        <v>0.07323669443151759</v>
       </c>
       <c r="C16">
-        <v>14504.69175753474</v>
+        <v>14675.73925013489</v>
       </c>
       <c r="D16">
-        <v>15676.93575753474</v>
+        <v>15847.98325013489</v>
       </c>
       <c r="E16">
         <v>-2000.256</v>
@@ -2605,45 +2605,45 @@
         <v>1031.4</v>
       </c>
       <c r="M16">
-        <v>123.6282432</v>
+        <v>117.7746332</v>
       </c>
       <c r="N16">
-        <v>907.7717568</v>
+        <v>913.6253668000001</v>
       </c>
       <c r="O16">
-        <v>132.5346764928</v>
+        <v>133.3893035528</v>
       </c>
       <c r="P16">
-        <v>775.2370803072</v>
+        <v>780.2360632472</v>
       </c>
       <c r="Q16">
-        <v>1115.0370803072</v>
+        <v>1120.0360632472</v>
       </c>
       <c r="R16">
         <v>0.1627906976744186</v>
       </c>
       <c r="S16">
-        <v>0.07818689914256294</v>
+        <v>0.07816607724595068</v>
       </c>
       <c r="T16">
         <v>0.7474844629549811</v>
       </c>
       <c r="U16">
-        <v>0.0528</v>
+        <v>0.0503</v>
       </c>
       <c r="V16">
         <v>0.146</v>
       </c>
       <c r="W16">
-        <v>0.0450912</v>
+        <v>0.0429562</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>Aaa/AAA</t>
         </is>
       </c>
       <c r="Y16">
-        <v>8.342753834424787</v>
+        <v>8.757403627388246</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2654,13 +2654,13 @@
         <v>0.15</v>
       </c>
       <c r="B17">
-        <v>0.07350489973554769</v>
+        <v>0.07335891959396806</v>
       </c>
       <c r="C17">
-        <v>14364.94713904685</v>
+        <v>14438.20666576226</v>
       </c>
       <c r="D17">
-        <v>15704.43713904685</v>
+        <v>15777.69666576225</v>
       </c>
       <c r="E17">
         <v>-1833.01</v>
@@ -2687,37 +2687,37 @@
         <v>1031.4</v>
       </c>
       <c r="M17">
-        <v>132.458832</v>
+        <v>129.950142</v>
       </c>
       <c r="N17">
-        <v>898.9411680000001</v>
+        <v>901.4498580000002</v>
       </c>
       <c r="O17">
-        <v>131.245410528</v>
+        <v>131.611679268</v>
       </c>
       <c r="P17">
-        <v>767.6957574720001</v>
+        <v>769.8381787320002</v>
       </c>
       <c r="Q17">
-        <v>1107.495757472</v>
+        <v>1109.638178732</v>
       </c>
       <c r="R17">
         <v>0.1764705882352941</v>
       </c>
       <c r="S17">
-        <v>0.07851908204182081</v>
+        <v>0.0784980465811389</v>
       </c>
       <c r="T17">
         <v>0.7551511912503208</v>
       </c>
       <c r="U17">
-        <v>0.0528</v>
+        <v>0.0518</v>
       </c>
       <c r="V17">
         <v>0.146</v>
       </c>
       <c r="W17">
-        <v>0.0450912</v>
+        <v>0.0442372</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
@@ -2725,7 +2725,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>7.786570245463135</v>
+        <v>7.936890134371692</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2736,13 +2736,13 @@
         <v>0.16</v>
       </c>
       <c r="B18">
-        <v>0.07345629820849126</v>
+        <v>0.07330180475641852</v>
       </c>
       <c r="C18">
-        <v>14225.29917913036</v>
+        <v>14303.72726380745</v>
       </c>
       <c r="D18">
-        <v>15732.03517913035</v>
+        <v>15810.46326380745</v>
       </c>
       <c r="E18">
         <v>-1665.764</v>
@@ -2769,37 +2769,37 @@
         <v>1031.4</v>
       </c>
       <c r="M18">
-        <v>141.2894208</v>
+        <v>138.6134848</v>
       </c>
       <c r="N18">
-        <v>890.1105792000001</v>
+        <v>892.7865152000002</v>
       </c>
       <c r="O18">
-        <v>129.9561445632</v>
+        <v>130.3468312192</v>
       </c>
       <c r="P18">
-        <v>760.1544346368</v>
+        <v>762.4396839808002</v>
       </c>
       <c r="Q18">
-        <v>1099.9544346368</v>
+        <v>1102.2396839808</v>
       </c>
       <c r="R18">
         <v>0.1904761904761905</v>
       </c>
       <c r="S18">
-        <v>0.07885917405772769</v>
+        <v>0.0788379199481173</v>
       </c>
       <c r="T18">
         <v>0.7630004606955496</v>
       </c>
       <c r="U18">
-        <v>0.0528</v>
+        <v>0.0518</v>
       </c>
       <c r="V18">
         <v>0.146</v>
       </c>
       <c r="W18">
-        <v>0.0450912</v>
+        <v>0.0442372</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
@@ -2807,7 +2807,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>7.299909605121689</v>
+        <v>7.44083450097346</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2818,13 +2818,13 @@
         <v>0.17</v>
       </c>
       <c r="B19">
-        <v>0.07340769668143482</v>
+        <v>0.073244689918869</v>
       </c>
       <c r="C19">
-        <v>14085.74838826837</v>
+        <v>14169.38424225481</v>
       </c>
       <c r="D19">
-        <v>15759.73038826838</v>
+        <v>15843.36624225481</v>
       </c>
       <c r="E19">
         <v>-1498.518</v>
@@ -2851,37 +2851,37 @@
         <v>1031.4</v>
       </c>
       <c r="M19">
-        <v>150.1200096</v>
+        <v>147.2768276</v>
       </c>
       <c r="N19">
-        <v>881.2799904000001</v>
+        <v>884.1231724000002</v>
       </c>
       <c r="O19">
-        <v>128.6668785984</v>
+        <v>129.0819831704</v>
       </c>
       <c r="P19">
-        <v>752.6131118016001</v>
+        <v>755.0411892296001</v>
       </c>
       <c r="Q19">
-        <v>1092.4131118016</v>
+        <v>1094.8411892296</v>
       </c>
       <c r="R19">
         <v>0.2048192771084338</v>
       </c>
       <c r="S19">
-        <v>0.07920746106196966</v>
+        <v>0.07918598303478193</v>
       </c>
       <c r="T19">
         <v>0.7710388691635548</v>
       </c>
       <c r="U19">
-        <v>0.0528</v>
+        <v>0.0518</v>
       </c>
       <c r="V19">
         <v>0.146</v>
       </c>
       <c r="W19">
-        <v>0.0450912</v>
+        <v>0.0442372</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
@@ -2889,7 +2889,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>6.87050315776159</v>
+        <v>7.003138353857373</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2900,13 +2900,13 @@
         <v>0.18</v>
       </c>
       <c r="B20">
-        <v>0.0736972791543784</v>
+        <v>0.07344889908131946</v>
       </c>
       <c r="C20">
-        <v>13754.91146337911</v>
+        <v>13885.1223516325</v>
       </c>
       <c r="D20">
-        <v>15596.13946337911</v>
+        <v>15726.35035163251</v>
       </c>
       <c r="E20">
         <v>-1331.272</v>
@@ -2933,37 +2933,37 @@
         <v>1031.4</v>
       </c>
       <c r="M20">
-        <v>165.57354</v>
+        <v>161.057898</v>
       </c>
       <c r="N20">
-        <v>865.8264600000001</v>
+        <v>870.3421020000001</v>
       </c>
       <c r="O20">
-        <v>126.41066316</v>
+        <v>127.069946892</v>
       </c>
       <c r="P20">
-        <v>739.4157968400001</v>
+        <v>743.2721551080001</v>
       </c>
       <c r="Q20">
-        <v>1079.21579684</v>
+        <v>1083.072155108</v>
       </c>
       <c r="R20">
         <v>0.2195121951219512</v>
       </c>
       <c r="S20">
-        <v>0.07956424287119315</v>
+        <v>0.07954253546502374</v>
       </c>
       <c r="T20">
         <v>0.7792733363746823</v>
       </c>
       <c r="U20">
-        <v>0.055</v>
+        <v>0.0535</v>
       </c>
       <c r="V20">
         <v>0.146</v>
       </c>
       <c r="W20">
-        <v>0.04697</v>
+        <v>0.045689</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
@@ -2971,7 +2971,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>6.229256196370509</v>
+        <v>6.403908239259401</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2982,13 +2982,13 @@
         <v>0.19</v>
       </c>
       <c r="B21">
-        <v>0.07366746562732196</v>
+        <v>0.07340630224376996</v>
       </c>
       <c r="C21">
-        <v>13604.35072396526</v>
+        <v>13742.14228863703</v>
       </c>
       <c r="D21">
-        <v>15612.82472396526</v>
+        <v>15750.61628863703</v>
       </c>
       <c r="E21">
         <v>-1164.026</v>
@@ -3015,37 +3015,37 @@
         <v>1031.4</v>
       </c>
       <c r="M21">
-        <v>174.77207</v>
+        <v>170.005559</v>
       </c>
       <c r="N21">
-        <v>856.6279300000001</v>
+        <v>861.3944410000001</v>
       </c>
       <c r="O21">
-        <v>125.06767778</v>
+        <v>125.763588386</v>
       </c>
       <c r="P21">
-        <v>731.5602522200001</v>
+        <v>735.6308526140001</v>
       </c>
       <c r="Q21">
-        <v>1071.36025222</v>
+        <v>1075.430852614</v>
       </c>
       <c r="R21">
         <v>0.2345679012345679</v>
       </c>
       <c r="S21">
-        <v>0.07992983410780488</v>
+        <v>0.07990789165897524</v>
       </c>
       <c r="T21">
         <v>0.7877111237638623</v>
       </c>
       <c r="U21">
-        <v>0.055</v>
+        <v>0.0535</v>
       </c>
       <c r="V21">
         <v>0.146</v>
       </c>
       <c r="W21">
-        <v>0.04697</v>
+        <v>0.045689</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
@@ -3053,7 +3053,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>5.901400607087849</v>
+        <v>6.066860437193117</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3064,13 +3064,13 @@
         <v>0.2</v>
       </c>
       <c r="B22">
-        <v>0.07389385210026553</v>
+        <v>0.07336370540622042</v>
       </c>
       <c r="C22">
-        <v>13311.29312969438</v>
+        <v>13599.23722660108</v>
       </c>
       <c r="D22">
-        <v>15487.01312969438</v>
+        <v>15774.95722660108</v>
       </c>
       <c r="E22">
         <v>-996.7799999999997</v>
@@ -3097,45 +3097,45 @@
         <v>1031.4</v>
       </c>
       <c r="M22">
-        <v>188.98798</v>
+        <v>178.95322</v>
       </c>
       <c r="N22">
-        <v>842.4120200000001</v>
+        <v>852.4467800000001</v>
       </c>
       <c r="O22">
-        <v>122.99215492</v>
+        <v>124.45722988</v>
       </c>
       <c r="P22">
-        <v>719.4198650800001</v>
+        <v>727.9895501200001</v>
       </c>
       <c r="Q22">
-        <v>1059.21986508</v>
+        <v>1067.78955012</v>
       </c>
       <c r="R22">
         <v>0.25</v>
       </c>
       <c r="S22">
-        <v>0.08030456512533191</v>
+        <v>0.08028238175777552</v>
       </c>
       <c r="T22">
         <v>0.7963598558377718</v>
       </c>
       <c r="U22">
-        <v>0.0565</v>
+        <v>0.0535</v>
       </c>
       <c r="V22">
         <v>0.146</v>
       </c>
       <c r="W22">
-        <v>0.048251</v>
+        <v>0.045689</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y22">
-        <v>5.457489941952922</v>
+        <v>5.76351741533346</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3146,13 +3146,13 @@
         <v>0.21</v>
       </c>
       <c r="B23">
-        <v>0.07387684857320909</v>
+        <v>0.07346458056867089</v>
       </c>
       <c r="C23">
-        <v>13153.42616830292</v>
+        <v>13374.46997234123</v>
       </c>
       <c r="D23">
-        <v>15496.39216830292</v>
+        <v>15717.43597234123</v>
       </c>
       <c r="E23">
         <v>-829.5340000000001</v>
@@ -3179,37 +3179,37 @@
         <v>1031.4</v>
       </c>
       <c r="M23">
-        <v>198.437379</v>
+        <v>190.7106138</v>
       </c>
       <c r="N23">
-        <v>832.9626210000001</v>
+        <v>840.6893862000002</v>
       </c>
       <c r="O23">
-        <v>121.612542666</v>
+        <v>122.7406503852</v>
       </c>
       <c r="P23">
-        <v>711.3500783340002</v>
+        <v>717.9487358148001</v>
       </c>
       <c r="Q23">
-        <v>1051.150078334</v>
+        <v>1057.7487358148</v>
       </c>
       <c r="R23">
         <v>0.2658227848101266</v>
       </c>
       <c r="S23">
-        <v>0.08068878300406213</v>
+        <v>0.08066635261857075</v>
       </c>
       <c r="T23">
         <v>0.8052275431540586</v>
       </c>
       <c r="U23">
-        <v>0.0565</v>
+        <v>0.0543</v>
       </c>
       <c r="V23">
         <v>0.146</v>
       </c>
       <c r="W23">
-        <v>0.048251</v>
+        <v>0.0463722</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
@@ -3217,7 +3217,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>5.197609468526593</v>
+        <v>5.408194014212754</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3228,13 +3228,13 @@
         <v>0.22</v>
       </c>
       <c r="B24">
-        <v>0.07385984504615264</v>
+        <v>0.07342881573112137</v>
       </c>
       <c r="C24">
-        <v>12995.5705738122</v>
+        <v>13227.56981523643</v>
       </c>
       <c r="D24">
-        <v>15505.7825738122</v>
+        <v>15737.78181523643</v>
       </c>
       <c r="E24">
         <v>-662.288</v>
@@ -3261,37 +3261,37 @@
         <v>1031.4</v>
       </c>
       <c r="M24">
-        <v>207.886778</v>
+        <v>199.7920716</v>
       </c>
       <c r="N24">
-        <v>823.513222</v>
+        <v>831.6079284000001</v>
       </c>
       <c r="O24">
-        <v>120.232930412</v>
+        <v>121.4147575464</v>
       </c>
       <c r="P24">
-        <v>703.2802915880001</v>
+        <v>710.1931708536001</v>
       </c>
       <c r="Q24">
-        <v>1043.080291588</v>
+        <v>1049.9931708536</v>
       </c>
       <c r="R24">
         <v>0.282051282051282</v>
       </c>
       <c r="S24">
-        <v>0.08108285262327262</v>
+        <v>0.08106016888605302</v>
       </c>
       <c r="T24">
         <v>0.8143226070681991</v>
       </c>
       <c r="U24">
-        <v>0.0565</v>
+        <v>0.0543</v>
       </c>
       <c r="V24">
         <v>0.146</v>
       </c>
       <c r="W24">
-        <v>0.048251</v>
+        <v>0.0463722</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
@@ -3299,7 +3299,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>4.961354492684475</v>
+        <v>5.162367013566719</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3310,13 +3310,13 @@
         <v>0.23</v>
       </c>
       <c r="B25">
-        <v>0.07384284151909622</v>
+        <v>0.07339305089357184</v>
       </c>
       <c r="C25">
-        <v>12837.72636689887</v>
+        <v>13080.72240081447</v>
       </c>
       <c r="D25">
-        <v>15515.18436689887</v>
+        <v>15758.18040081447</v>
       </c>
       <c r="E25">
         <v>-495.0419999999999</v>
@@ -3343,37 +3343,37 @@
         <v>1031.4</v>
       </c>
       <c r="M25">
-        <v>217.336177</v>
+        <v>208.8735294</v>
       </c>
       <c r="N25">
-        <v>814.0638230000001</v>
+        <v>822.5264706</v>
       </c>
       <c r="O25">
-        <v>118.853318158</v>
+        <v>120.0888647076</v>
       </c>
       <c r="P25">
-        <v>695.2105048420001</v>
+        <v>702.4376058924</v>
       </c>
       <c r="Q25">
-        <v>1035.010504842</v>
+        <v>1042.2376058924</v>
       </c>
       <c r="R25">
         <v>0.2987012987012987</v>
       </c>
       <c r="S25">
-        <v>0.08148715781700806</v>
+        <v>0.08146421414749588</v>
       </c>
       <c r="T25">
         <v>0.8236539064086809</v>
       </c>
       <c r="U25">
-        <v>0.0565</v>
+        <v>0.0543</v>
       </c>
       <c r="V25">
         <v>0.146</v>
       </c>
       <c r="W25">
-        <v>0.048251</v>
+        <v>0.0463722</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
@@ -3381,7 +3381,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>4.745643427785151</v>
+        <v>4.937916273846427</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3392,13 +3392,13 @@
         <v>0.24</v>
       </c>
       <c r="B26">
-        <v>0.07382583799203979</v>
+        <v>0.07335728605602231</v>
       </c>
       <c r="C26">
-        <v>12679.89356828978</v>
+        <v>12933.92793442942</v>
       </c>
       <c r="D26">
-        <v>15524.59756828978</v>
+        <v>15778.63193442942</v>
       </c>
       <c r="E26">
         <v>-327.7960000000003</v>
@@ -3425,37 +3425,37 @@
         <v>1031.4</v>
       </c>
       <c r="M26">
-        <v>226.785576</v>
+        <v>217.9549872</v>
       </c>
       <c r="N26">
-        <v>804.6144240000001</v>
+        <v>813.4450128000001</v>
       </c>
       <c r="O26">
-        <v>117.473705904</v>
+        <v>118.7629718688</v>
       </c>
       <c r="P26">
-        <v>687.1407180960001</v>
+        <v>694.6820409312</v>
       </c>
       <c r="Q26">
-        <v>1026.940718096</v>
+        <v>1034.4820409312</v>
       </c>
       <c r="R26">
         <v>0.3157894736842105</v>
       </c>
       <c r="S26">
-        <v>0.08190210262110498</v>
+        <v>0.08187889217897672</v>
       </c>
       <c r="T26">
         <v>0.8332307662581228</v>
       </c>
       <c r="U26">
-        <v>0.0565</v>
+        <v>0.0543</v>
       </c>
       <c r="V26">
         <v>0.146</v>
       </c>
       <c r="W26">
-        <v>0.048251</v>
+        <v>0.0463722</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
@@ -3463,7 +3463,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>4.547908284960769</v>
+        <v>4.732169762436159</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3474,13 +3474,13 @@
         <v>0.25</v>
       </c>
       <c r="B27">
-        <v>0.07380883446498333</v>
+        <v>0.07332152121847277</v>
       </c>
       <c r="C27">
-        <v>12522.07219876211</v>
+        <v>12787.18662250276</v>
       </c>
       <c r="D27">
-        <v>15534.02219876211</v>
+        <v>15799.13662250277</v>
       </c>
       <c r="E27">
         <v>-160.5500000000002</v>
@@ -3507,37 +3507,37 @@
         <v>1031.4</v>
       </c>
       <c r="M27">
-        <v>236.234975</v>
+        <v>227.036445</v>
       </c>
       <c r="N27">
-        <v>795.1650250000001</v>
+        <v>804.3635550000001</v>
       </c>
       <c r="O27">
-        <v>116.09409365</v>
+        <v>117.43707903</v>
       </c>
       <c r="P27">
-        <v>679.0709313500001</v>
+        <v>686.9264759700002</v>
       </c>
       <c r="Q27">
-        <v>1018.87093135</v>
+        <v>1026.72647597</v>
       </c>
       <c r="R27">
         <v>0.3333333333333333</v>
       </c>
       <c r="S27">
-        <v>0.08232811261997777</v>
+        <v>0.08230462829129703</v>
       </c>
       <c r="T27">
         <v>0.8430630090368829</v>
       </c>
       <c r="U27">
-        <v>0.0565</v>
+        <v>0.0543</v>
       </c>
       <c r="V27">
         <v>0.146</v>
       </c>
       <c r="W27">
-        <v>0.048251</v>
+        <v>0.0463722</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
@@ -3545,7 +3545,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>4.365991953562338</v>
+        <v>4.542882971938713</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3556,13 +3556,13 @@
         <v>0.26</v>
       </c>
       <c r="B28">
-        <v>0.0741026869379269</v>
+        <v>0.07328575638092324</v>
       </c>
       <c r="C28">
-        <v>12193.54430888791</v>
+        <v>12640.4986725304</v>
       </c>
       <c r="D28">
-        <v>15372.74030888791</v>
+        <v>15819.6946725304</v>
       </c>
       <c r="E28">
         <v>6.695999999999913</v>
@@ -3589,45 +3589,45 @@
         <v>1031.4</v>
       </c>
       <c r="M28">
-        <v>251.7721284</v>
+        <v>236.1179028</v>
       </c>
       <c r="N28">
-        <v>779.6278716000002</v>
+        <v>795.2820972000001</v>
       </c>
       <c r="O28">
-        <v>113.8256692536</v>
+        <v>116.1111861912</v>
       </c>
       <c r="P28">
-        <v>665.8022023464001</v>
+        <v>679.1709110088001</v>
       </c>
       <c r="Q28">
-        <v>1005.6022023464</v>
+        <v>1018.9709110088</v>
       </c>
       <c r="R28">
         <v>0.3513513513513514</v>
       </c>
       <c r="S28">
-        <v>0.08276563640260393</v>
+        <v>0.08274187078503142</v>
       </c>
       <c r="T28">
         <v>0.8531609881069611</v>
       </c>
       <c r="U28">
-        <v>0.0579</v>
+        <v>0.0543</v>
       </c>
       <c r="V28">
         <v>0.146</v>
       </c>
       <c r="W28">
-        <v>0.0494466</v>
+        <v>0.0463722</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y28">
-        <v>4.096561468318589</v>
+        <v>4.368156703787223</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3638,13 +3638,13 @@
         <v>0.27</v>
       </c>
       <c r="B29">
-        <v>0.07409763941087048</v>
+        <v>0.07348057154337373</v>
       </c>
       <c r="C29">
-        <v>12029.0403864695</v>
+        <v>12361.91406152243</v>
       </c>
       <c r="D29">
-        <v>15375.4823864695</v>
+        <v>15708.35606152243</v>
       </c>
       <c r="E29">
         <v>173.942</v>
@@ -3671,37 +3671,37 @@
         <v>1031.4</v>
       </c>
       <c r="M29">
-        <v>261.4556718</v>
+        <v>249.7150026</v>
       </c>
       <c r="N29">
-        <v>769.9443282000001</v>
+        <v>781.6849974000002</v>
       </c>
       <c r="O29">
-        <v>112.4118719172</v>
+        <v>114.1260096204</v>
       </c>
       <c r="P29">
-        <v>657.5324562828001</v>
+        <v>667.5589877796001</v>
       </c>
       <c r="Q29">
-        <v>997.3324562828001</v>
+        <v>1007.3589877796</v>
       </c>
       <c r="R29">
         <v>0.3698630136986302</v>
       </c>
       <c r="S29">
-        <v>0.08321514713817874</v>
+        <v>0.08319109252516949</v>
       </c>
       <c r="T29">
         <v>0.8635356241378633</v>
       </c>
       <c r="U29">
-        <v>0.0579</v>
+        <v>0.0553</v>
       </c>
       <c r="V29">
         <v>0.146</v>
       </c>
       <c r="W29">
-        <v>0.0494466</v>
+        <v>0.0472262</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
@@ -3709,7 +3709,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>3.944836969491974</v>
+        <v>4.130308508744761</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3720,13 +3720,13 @@
         <v>0.28</v>
       </c>
       <c r="B30">
-        <v>0.07409259188381404</v>
+        <v>0.07345334670582421</v>
       </c>
       <c r="C30">
-        <v>11864.53744244933</v>
+        <v>12210.13300493396</v>
       </c>
       <c r="D30">
-        <v>15378.22544244933</v>
+        <v>15723.82100493396</v>
       </c>
       <c r="E30">
         <v>341.1880000000001</v>
@@ -3753,37 +3753,37 @@
         <v>1031.4</v>
       </c>
       <c r="M30">
-        <v>271.1392152</v>
+        <v>258.9637064</v>
       </c>
       <c r="N30">
-        <v>760.2607848</v>
+        <v>772.4362936000001</v>
       </c>
       <c r="O30">
-        <v>110.9980745808</v>
+        <v>112.7756988656</v>
       </c>
       <c r="P30">
-        <v>649.2627102192</v>
+        <v>659.6605947344001</v>
       </c>
       <c r="Q30">
-        <v>989.0627102192</v>
+        <v>999.4605947344</v>
       </c>
       <c r="R30">
         <v>0.388888888888889</v>
       </c>
       <c r="S30">
-        <v>0.08367714428307504</v>
+        <v>0.08365279264697806</v>
       </c>
       <c r="T30">
         <v>0.8741984445029573</v>
       </c>
       <c r="U30">
-        <v>0.0579</v>
+        <v>0.0553</v>
       </c>
       <c r="V30">
         <v>0.146</v>
       </c>
       <c r="W30">
-        <v>0.0494466</v>
+        <v>0.0472262</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -3791,7 +3791,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>3.80394993486726</v>
+        <v>3.982797490575305</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3802,13 +3802,13 @@
         <v>0.29</v>
       </c>
       <c r="B31">
-        <v>0.0740875443567576</v>
+        <v>0.07342612186827466</v>
       </c>
       <c r="C31">
-        <v>11700.03547735111</v>
+        <v>12058.38242895904</v>
       </c>
       <c r="D31">
-        <v>15380.96947735111</v>
+        <v>15739.31642895904</v>
       </c>
       <c r="E31">
         <v>508.4339999999993</v>
@@ -3835,37 +3835,37 @@
         <v>1031.4</v>
       </c>
       <c r="M31">
-        <v>280.8227585999999</v>
+        <v>268.2124102</v>
       </c>
       <c r="N31">
-        <v>750.5772414000002</v>
+        <v>763.1875898000001</v>
       </c>
       <c r="O31">
-        <v>109.5842772444</v>
+        <v>111.4253881108</v>
       </c>
       <c r="P31">
-        <v>640.9929641556001</v>
+        <v>651.7622016892001</v>
       </c>
       <c r="Q31">
-        <v>980.7929641556001</v>
+        <v>991.5622016892</v>
       </c>
       <c r="R31">
         <v>0.4084507042253521</v>
       </c>
       <c r="S31">
-        <v>0.08415215543205296</v>
+        <v>0.08412749840602066</v>
       </c>
       <c r="T31">
         <v>0.885161626005096</v>
       </c>
       <c r="U31">
-        <v>0.0579</v>
+        <v>0.0553</v>
       </c>
       <c r="V31">
         <v>0.146</v>
       </c>
       <c r="W31">
-        <v>0.0494466</v>
+        <v>0.0472262</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -3873,7 +3873,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>3.672779247458045</v>
+        <v>3.845459646072709</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3884,13 +3884,13 @@
         <v>0.3</v>
       </c>
       <c r="B32">
-        <v>0.07408249682970115</v>
+        <v>0.07339889703072514</v>
       </c>
       <c r="C32">
-        <v>11535.53449169899</v>
+        <v>11906.66242380014</v>
       </c>
       <c r="D32">
-        <v>15383.71449169899</v>
+        <v>15754.84242380014</v>
       </c>
       <c r="E32">
         <v>675.6799999999994</v>
@@ -3917,37 +3917,37 @@
         <v>1031.4</v>
       </c>
       <c r="M32">
-        <v>290.5063019999999</v>
+        <v>277.461114</v>
       </c>
       <c r="N32">
-        <v>740.8936980000001</v>
+        <v>753.9388860000001</v>
       </c>
       <c r="O32">
-        <v>108.170479908</v>
+        <v>110.075077356</v>
       </c>
       <c r="P32">
-        <v>632.723218092</v>
+        <v>643.8638086440001</v>
       </c>
       <c r="Q32">
-        <v>972.523218092</v>
+        <v>983.663808644</v>
       </c>
       <c r="R32">
         <v>0.4285714285714286</v>
       </c>
       <c r="S32">
-        <v>0.08464073832814452</v>
+        <v>0.08461576718675021</v>
       </c>
       <c r="T32">
         <v>0.8964380412644387</v>
       </c>
       <c r="U32">
-        <v>0.0579</v>
+        <v>0.0553</v>
       </c>
       <c r="V32">
         <v>0.146</v>
       </c>
       <c r="W32">
-        <v>0.0494466</v>
+        <v>0.0472262</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -3955,7 +3955,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>3.550353272542777</v>
+        <v>3.717277657870286</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3966,13 +3966,13 @@
         <v>0.31</v>
       </c>
       <c r="B33">
-        <v>0.07407744930264472</v>
+        <v>0.07337167219317561</v>
       </c>
       <c r="C33">
-        <v>11371.03448601744</v>
+        <v>11754.97308001602</v>
       </c>
       <c r="D33">
-        <v>15386.46048601744</v>
+        <v>15770.39908001602</v>
       </c>
       <c r="E33">
         <v>842.9259999999995</v>
@@ -3999,37 +3999,37 @@
         <v>1031.4</v>
       </c>
       <c r="M33">
-        <v>300.1898454</v>
+        <v>286.7098178</v>
       </c>
       <c r="N33">
-        <v>731.2101546000001</v>
+        <v>744.6901822000001</v>
       </c>
       <c r="O33">
-        <v>106.7566825716</v>
+        <v>108.7247666012</v>
       </c>
       <c r="P33">
-        <v>624.4534720284001</v>
+        <v>635.9654155988001</v>
       </c>
       <c r="Q33">
-        <v>964.2534720284001</v>
+        <v>975.7654155988</v>
       </c>
       <c r="R33">
         <v>0.4492753623188406</v>
       </c>
       <c r="S33">
-        <v>0.0851434830473112</v>
+        <v>0.08511818868576176</v>
       </c>
       <c r="T33">
         <v>0.9080413091399944</v>
       </c>
       <c r="U33">
-        <v>0.0579</v>
+        <v>0.0553</v>
       </c>
       <c r="V33">
         <v>0.146</v>
       </c>
       <c r="W33">
-        <v>0.0494466</v>
+        <v>0.0472262</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -4037,7 +4037,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>3.435825747622042</v>
+        <v>3.59736547535834</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4048,13 +4048,13 @@
         <v>0.32</v>
       </c>
       <c r="B34">
-        <v>0.07407240177558828</v>
+        <v>0.07334444735562608</v>
       </c>
       <c r="C34">
-        <v>11206.53546083134</v>
+        <v>11603.3144885235</v>
       </c>
       <c r="D34">
-        <v>15389.20746083134</v>
+        <v>15785.9864885235</v>
       </c>
       <c r="E34">
         <v>1010.172</v>
@@ -4081,37 +4081,37 @@
         <v>1031.4</v>
       </c>
       <c r="M34">
-        <v>309.8733888</v>
+        <v>295.9585216</v>
       </c>
       <c r="N34">
-        <v>721.5266112000002</v>
+        <v>735.4414784000001</v>
       </c>
       <c r="O34">
-        <v>105.3428852352</v>
+        <v>107.3744558464</v>
       </c>
       <c r="P34">
-        <v>616.1837259648001</v>
+        <v>628.0670225536001</v>
       </c>
       <c r="Q34">
-        <v>955.9837259648001</v>
+        <v>967.8670225536</v>
       </c>
       <c r="R34">
         <v>0.4705882352941177</v>
       </c>
       <c r="S34">
-        <v>0.08566101437586512</v>
+        <v>0.08563538728768541</v>
       </c>
       <c r="T34">
         <v>0.919985849600125</v>
       </c>
       <c r="U34">
-        <v>0.0579</v>
+        <v>0.0553</v>
       </c>
       <c r="V34">
         <v>0.146</v>
       </c>
       <c r="W34">
-        <v>0.0494466</v>
+        <v>0.0472262</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4119,7 +4119,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>3.328456193008853</v>
+        <v>3.484947804253392</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4130,13 +4130,13 @@
         <v>0.33</v>
       </c>
       <c r="B35">
-        <v>0.07406735424853185</v>
+        <v>0.07331722251807656</v>
       </c>
       <c r="C35">
-        <v>11042.03741666592</v>
+        <v>11451.68674059915</v>
       </c>
       <c r="D35">
-        <v>15391.95541666592</v>
+        <v>15801.60474059914</v>
       </c>
       <c r="E35">
         <v>1177.418</v>
@@ -4163,37 +4163,37 @@
         <v>1031.4</v>
       </c>
       <c r="M35">
-        <v>319.5569321999999</v>
+        <v>305.2072254</v>
       </c>
       <c r="N35">
-        <v>711.8430678000002</v>
+        <v>726.1927746000001</v>
       </c>
       <c r="O35">
-        <v>103.9290878988</v>
+        <v>106.0241450916</v>
       </c>
       <c r="P35">
-        <v>607.9139799012002</v>
+        <v>620.1686295084002</v>
       </c>
       <c r="Q35">
-        <v>947.7139799012001</v>
+        <v>959.9686295084001</v>
       </c>
       <c r="R35">
         <v>0.4925373134328359</v>
       </c>
       <c r="S35">
-        <v>0.08619399440079381</v>
+        <v>0.0861680246538456</v>
       </c>
       <c r="T35">
         <v>0.9322869435068268</v>
       </c>
       <c r="U35">
-        <v>0.0579</v>
+        <v>0.0553</v>
       </c>
       <c r="V35">
         <v>0.146</v>
       </c>
       <c r="W35">
-        <v>0.0494466</v>
+        <v>0.0472262</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>3.227593884129798</v>
+        <v>3.379343325336623</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4212,13 +4212,13 @@
         <v>0.34</v>
       </c>
       <c r="B36">
-        <v>0.07406230672147542</v>
+        <v>0.07328999768052702</v>
       </c>
       <c r="C36">
-        <v>10877.54035404682</v>
+        <v>11300.08992788116</v>
       </c>
       <c r="D36">
-        <v>15394.70435404682</v>
+        <v>15817.25392788116</v>
       </c>
       <c r="E36">
         <v>1344.664</v>
@@ -4245,37 +4245,37 @@
         <v>1031.4</v>
       </c>
       <c r="M36">
-        <v>329.2404756</v>
+        <v>314.4559292</v>
       </c>
       <c r="N36">
-        <v>702.1595244000001</v>
+        <v>716.9440708000001</v>
       </c>
       <c r="O36">
-        <v>102.5152905624</v>
+        <v>104.6738343368</v>
       </c>
       <c r="P36">
-        <v>599.6442338376002</v>
+        <v>612.2702364632</v>
       </c>
       <c r="Q36">
-        <v>939.4442338376001</v>
+        <v>952.0702364632</v>
       </c>
       <c r="R36">
         <v>0.5151515151515152</v>
       </c>
       <c r="S36">
-        <v>0.08674312533556883</v>
+        <v>0.08671680254625308</v>
       </c>
       <c r="T36">
         <v>0.9449607978349438</v>
       </c>
       <c r="U36">
-        <v>0.0579</v>
+        <v>0.0553</v>
       </c>
       <c r="V36">
         <v>0.146</v>
       </c>
       <c r="W36">
-        <v>0.0494466</v>
+        <v>0.0472262</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4283,7 +4283,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>3.132664652243626</v>
+        <v>3.279950874591428</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4294,13 +4294,13 @@
         <v>0.35</v>
       </c>
       <c r="B37">
-        <v>0.07405725919441898</v>
+        <v>0.0732627728429775</v>
       </c>
       <c r="C37">
-        <v>10713.04427350002</v>
+        <v>11148.52414237109</v>
       </c>
       <c r="D37">
-        <v>15397.45427350002</v>
+        <v>15832.93414237109</v>
       </c>
       <c r="E37">
         <v>1511.91</v>
@@ -4327,37 +4327,37 @@
         <v>1031.4</v>
       </c>
       <c r="M37">
-        <v>338.924019</v>
+        <v>323.704633</v>
       </c>
       <c r="N37">
-        <v>692.475981</v>
+        <v>707.695367</v>
       </c>
       <c r="O37">
-        <v>101.101493226</v>
+        <v>103.323523582</v>
       </c>
       <c r="P37">
-        <v>591.374487774</v>
+        <v>604.371843418</v>
       </c>
       <c r="Q37">
-        <v>931.174487774</v>
+        <v>944.171843418</v>
       </c>
       <c r="R37">
         <v>0.5384615384615385</v>
       </c>
       <c r="S37">
-        <v>0.08730915260679845</v>
+        <v>0.08728246591227307</v>
       </c>
       <c r="T37">
         <v>0.9580246169116182</v>
       </c>
       <c r="U37">
-        <v>0.0579</v>
+        <v>0.0553</v>
       </c>
       <c r="V37">
         <v>0.146</v>
       </c>
       <c r="W37">
-        <v>0.0494466</v>
+        <v>0.0472262</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4365,7 +4365,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>3.043159947893808</v>
+        <v>3.186237992460244</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4376,13 +4376,13 @@
         <v>0.36</v>
       </c>
       <c r="B38">
-        <v>0.07485155566736254</v>
+        <v>0.07323554800542798</v>
       </c>
       <c r="C38">
-        <v>10124.81759481332</v>
+        <v>10996.98947643568</v>
       </c>
       <c r="D38">
-        <v>14976.47359481332</v>
+        <v>15848.64547643568</v>
       </c>
       <c r="E38">
         <v>1679.155999999999</v>
@@ -4409,45 +4409,45 @@
         <v>1031.4</v>
       </c>
       <c r="M38">
-        <v>364.2617879999999</v>
+        <v>332.9533367999999</v>
       </c>
       <c r="N38">
-        <v>667.1382120000002</v>
+        <v>698.4466632000001</v>
       </c>
       <c r="O38">
-        <v>97.40217895200001</v>
+        <v>101.9732128272</v>
       </c>
       <c r="P38">
-        <v>569.7360330480002</v>
+        <v>596.4734503728001</v>
       </c>
       <c r="Q38">
-        <v>909.5360330480001</v>
+        <v>936.2734503728001</v>
       </c>
       <c r="R38">
         <v>0.5625</v>
       </c>
       <c r="S38">
-        <v>0.08789286823025398</v>
+        <v>0.0878658062584812</v>
       </c>
       <c r="T38">
         <v>0.9714966803344387</v>
       </c>
       <c r="U38">
-        <v>0.0605</v>
+        <v>0.0553</v>
       </c>
       <c r="V38">
         <v>0.146</v>
       </c>
       <c r="W38">
-        <v>0.051667</v>
+        <v>0.0472262</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y38">
-        <v>2.831480089259323</v>
+        <v>3.097731381558571</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4458,13 +4458,13 @@
         <v>0.37</v>
       </c>
       <c r="B39">
-        <v>0.07486871214030612</v>
+        <v>0.07320832316787845</v>
       </c>
       <c r="C39">
-        <v>9948.732418767975</v>
+        <v>10845.48602280866</v>
       </c>
       <c r="D39">
-        <v>14967.63441876797</v>
+        <v>15864.38802280866</v>
       </c>
       <c r="E39">
         <v>1846.401999999999</v>
@@ -4491,45 +4491,45 @@
         <v>1031.4</v>
       </c>
       <c r="M39">
-        <v>374.3801709999999</v>
+        <v>342.2020406</v>
       </c>
       <c r="N39">
-        <v>657.0198290000002</v>
+        <v>689.1979594000002</v>
       </c>
       <c r="O39">
-        <v>95.92489503400002</v>
+        <v>100.6229020724</v>
       </c>
       <c r="P39">
-        <v>561.0949339660002</v>
+        <v>588.5750573276001</v>
       </c>
       <c r="Q39">
-        <v>900.8949339660002</v>
+        <v>928.3750573276001</v>
       </c>
       <c r="R39">
         <v>0.5873015873015873</v>
       </c>
       <c r="S39">
-        <v>0.0884951145084224</v>
+        <v>0.0884676653458388</v>
       </c>
       <c r="T39">
         <v>0.9853964283103647</v>
       </c>
       <c r="U39">
-        <v>0.0605</v>
+        <v>0.0553</v>
       </c>
       <c r="V39">
         <v>0.146</v>
       </c>
       <c r="W39">
-        <v>0.051667</v>
+        <v>0.0472262</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y39">
-        <v>2.754953600360422</v>
+        <v>3.014008911786718</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4540,13 +4540,13 @@
         <v>0.38</v>
       </c>
       <c r="B40">
-        <v>0.07488586861324967</v>
+        <v>0.07399239833032892</v>
       </c>
       <c r="C40">
-        <v>9772.657670403982</v>
+        <v>10237.02631440346</v>
       </c>
       <c r="D40">
-        <v>14958.80567040398</v>
+        <v>15423.17431440346</v>
       </c>
       <c r="E40">
         <v>2013.648</v>
@@ -4573,37 +4573,37 @@
         <v>1031.4</v>
       </c>
       <c r="M40">
-        <v>384.498554</v>
+        <v>367.3391144</v>
       </c>
       <c r="N40">
-        <v>646.9014460000001</v>
+        <v>664.0608856000001</v>
       </c>
       <c r="O40">
-        <v>94.447611116</v>
+        <v>96.95288929760001</v>
       </c>
       <c r="P40">
-        <v>552.4538348840001</v>
+        <v>567.1079963024001</v>
       </c>
       <c r="Q40">
-        <v>892.2538348840001</v>
+        <v>906.9079963024001</v>
       </c>
       <c r="R40">
         <v>0.6129032258064516</v>
       </c>
       <c r="S40">
-        <v>0.08911678808588658</v>
+        <v>0.089088939242466</v>
       </c>
       <c r="T40">
         <v>0.999744555253256</v>
       </c>
       <c r="U40">
-        <v>0.0605</v>
+        <v>0.0578</v>
       </c>
       <c r="V40">
         <v>0.146</v>
       </c>
       <c r="W40">
-        <v>0.051667</v>
+        <v>0.0493612</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4611,7 +4611,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>2.682454821403568</v>
+        <v>2.807759804410309</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4622,13 +4622,13 @@
         <v>0.39</v>
       </c>
       <c r="B41">
-        <v>0.07490302508619323</v>
+        <v>0.07398652349277939</v>
       </c>
       <c r="C41">
-        <v>9596.593331279706</v>
+        <v>10072.99492310178</v>
       </c>
       <c r="D41">
-        <v>14949.98733127971</v>
+        <v>15426.38892310178</v>
       </c>
       <c r="E41">
         <v>2180.894</v>
@@ -4655,37 +4655,37 @@
         <v>1031.4</v>
       </c>
       <c r="M41">
-        <v>394.616937</v>
+        <v>377.0059332</v>
       </c>
       <c r="N41">
-        <v>636.7830630000001</v>
+        <v>654.3940668</v>
       </c>
       <c r="O41">
-        <v>92.97032719800001</v>
+        <v>95.54153375279999</v>
       </c>
       <c r="P41">
-        <v>543.8127358020001</v>
+        <v>558.8525330472</v>
       </c>
       <c r="Q41">
-        <v>883.6127358020001</v>
+        <v>898.6525330472</v>
       </c>
       <c r="R41">
         <v>0.639344262295082</v>
       </c>
       <c r="S41">
-        <v>0.08975884440359547</v>
+        <v>0.08973058277504817</v>
       </c>
       <c r="T41">
         <v>1.014563112587717</v>
       </c>
       <c r="U41">
-        <v>0.0605</v>
+        <v>0.0578</v>
       </c>
       <c r="V41">
         <v>0.146</v>
       </c>
       <c r="W41">
-        <v>0.051667</v>
+        <v>0.0493612</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4693,7 +4693,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>2.613673928547066</v>
+        <v>2.735765963271583</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4704,13 +4704,13 @@
         <v>0.4</v>
       </c>
       <c r="B42">
-        <v>0.07492018155913679</v>
+        <v>0.07398064865522985</v>
       </c>
       <c r="C42">
-        <v>9420.539382997007</v>
+        <v>9908.964872103094</v>
       </c>
       <c r="D42">
-        <v>14941.17938299701</v>
+        <v>15429.60487210309</v>
       </c>
       <c r="E42">
         <v>2348.14</v>
@@ -4737,37 +4737,37 @@
         <v>1031.4</v>
       </c>
       <c r="M42">
-        <v>404.73532</v>
+        <v>386.6727520000001</v>
       </c>
       <c r="N42">
-        <v>626.6646800000001</v>
+        <v>644.727248</v>
       </c>
       <c r="O42">
-        <v>91.49304328000001</v>
+        <v>94.130178208</v>
       </c>
       <c r="P42">
-        <v>535.17163672</v>
+        <v>550.5970697920001</v>
       </c>
       <c r="Q42">
-        <v>874.97163672</v>
+        <v>890.397069792</v>
       </c>
       <c r="R42">
         <v>0.6666666666666667</v>
       </c>
       <c r="S42">
-        <v>0.09042230259856134</v>
+        <v>0.0903936144253831</v>
       </c>
       <c r="T42">
         <v>1.029875621833328</v>
       </c>
       <c r="U42">
-        <v>0.0605</v>
+        <v>0.0578</v>
       </c>
       <c r="V42">
         <v>0.146</v>
       </c>
       <c r="W42">
-        <v>0.051667</v>
+        <v>0.0493612</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4775,7 +4775,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>2.54833208033339</v>
+        <v>2.667371814189793</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4786,13 +4786,13 @@
         <v>0.41</v>
       </c>
       <c r="B43">
-        <v>0.07588271603208037</v>
+        <v>0.07397477381768033</v>
       </c>
       <c r="C43">
-        <v>8775.231488345209</v>
+        <v>9744.936162245809</v>
       </c>
       <c r="D43">
-        <v>14463.11748834521</v>
+        <v>15432.82216224581</v>
       </c>
       <c r="E43">
         <v>2515.386</v>
@@ -4819,45 +4819,45 @@
         <v>1031.4</v>
       </c>
       <c r="M43">
-        <v>433.3678352000001</v>
+        <v>396.3395708</v>
       </c>
       <c r="N43">
-        <v>598.0321648</v>
+        <v>635.0604292</v>
       </c>
       <c r="O43">
-        <v>87.31269606079999</v>
+        <v>92.7188226632</v>
       </c>
       <c r="P43">
-        <v>510.7194687392</v>
+        <v>542.3416065368001</v>
       </c>
       <c r="Q43">
-        <v>850.5194687392</v>
+        <v>882.1416065368001</v>
       </c>
       <c r="R43">
         <v>0.6949152542372882</v>
       </c>
       <c r="S43">
-        <v>0.09110825090183114</v>
+        <v>0.09107912172488192</v>
       </c>
       <c r="T43">
         <v>1.045707199188959</v>
       </c>
       <c r="U43">
-        <v>0.06320000000000001</v>
+        <v>0.0578</v>
       </c>
       <c r="V43">
         <v>0.146</v>
       </c>
       <c r="W43">
-        <v>0.0539728</v>
+        <v>0.0493612</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y43">
-        <v>2.379964354124267</v>
+        <v>2.602313965063213</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4868,13 +4868,13 @@
         <v>0.42</v>
       </c>
       <c r="B44">
-        <v>0.07592293050502394</v>
+        <v>0.07396889898013081</v>
       </c>
       <c r="C44">
-        <v>8588.677053303745</v>
+        <v>9580.908794369054</v>
       </c>
       <c r="D44">
-        <v>14443.80905330374</v>
+        <v>15436.04079436905</v>
       </c>
       <c r="E44">
         <v>2682.632</v>
@@ -4901,45 +4901,45 @@
         <v>1031.4</v>
       </c>
       <c r="M44">
-        <v>443.9377824</v>
+        <v>406.0063896</v>
       </c>
       <c r="N44">
-        <v>587.4622176</v>
+        <v>625.3936104000002</v>
       </c>
       <c r="O44">
-        <v>85.7694837696</v>
+        <v>91.30746711840001</v>
       </c>
       <c r="P44">
-        <v>501.6927338304</v>
+        <v>534.0861432816001</v>
       </c>
       <c r="Q44">
-        <v>841.4927338304</v>
+        <v>873.8861432816001</v>
       </c>
       <c r="R44">
         <v>0.7241379310344827</v>
       </c>
       <c r="S44">
-        <v>0.09181785259486885</v>
+        <v>0.09178826720712208</v>
       </c>
       <c r="T44">
         <v>1.062084693005128</v>
       </c>
       <c r="U44">
-        <v>0.06320000000000001</v>
+        <v>0.0578</v>
       </c>
       <c r="V44">
         <v>0.146</v>
       </c>
       <c r="W44">
-        <v>0.0539728</v>
+        <v>0.0493612</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y44">
-        <v>2.323298536168928</v>
+        <v>2.540354108752185</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4950,13 +4950,13 @@
         <v>0.43</v>
       </c>
       <c r="B45">
-        <v>0.07596314497796749</v>
+        <v>0.07524829414258127</v>
       </c>
       <c r="C45">
-        <v>8402.174103512858</v>
+        <v>8743.036651337305</v>
       </c>
       <c r="D45">
-        <v>14424.55210351286</v>
+        <v>14765.4146513373</v>
       </c>
       <c r="E45">
         <v>2849.878</v>
@@ -4983,37 +4983,37 @@
         <v>1031.4</v>
       </c>
       <c r="M45">
-        <v>454.5077296</v>
+        <v>440.8437314</v>
       </c>
       <c r="N45">
-        <v>576.8922704000001</v>
+        <v>590.5562686000001</v>
       </c>
       <c r="O45">
-        <v>84.22627147840002</v>
+        <v>86.2212152156</v>
       </c>
       <c r="P45">
-        <v>492.6659989216001</v>
+        <v>504.3350533844001</v>
       </c>
       <c r="Q45">
-        <v>832.4659989216001</v>
+        <v>844.1350533844</v>
       </c>
       <c r="R45">
         <v>0.7543859649122806</v>
       </c>
       <c r="S45">
-        <v>0.09255235259292544</v>
+        <v>0.09252229498698469</v>
       </c>
       <c r="T45">
         <v>1.079036835727129</v>
       </c>
       <c r="U45">
-        <v>0.06320000000000001</v>
+        <v>0.0613</v>
       </c>
       <c r="V45">
         <v>0.146</v>
       </c>
       <c r="W45">
-        <v>0.0539728</v>
+        <v>0.0523502</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5021,7 +5021,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>2.269268337653371</v>
+        <v>2.339604550402823</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5032,13 +5032,13 @@
         <v>0.44</v>
       </c>
       <c r="B46">
-        <v>0.07776943145091107</v>
+        <v>0.07527230930503176</v>
       </c>
       <c r="C46">
-        <v>7419.934775187571</v>
+        <v>8563.759227948296</v>
       </c>
       <c r="D46">
-        <v>13609.55877518757</v>
+        <v>14753.3832279483</v>
       </c>
       <c r="E46">
         <v>3017.124</v>
@@ -5065,45 +5065,45 @@
         <v>1031.4</v>
       </c>
       <c r="M46">
-        <v>499.6641496</v>
+        <v>451.0959112</v>
       </c>
       <c r="N46">
-        <v>531.7358504000001</v>
+        <v>580.3040888</v>
       </c>
       <c r="O46">
-        <v>77.63343415840001</v>
+        <v>84.72439696480001</v>
       </c>
       <c r="P46">
-        <v>454.1024162416001</v>
+        <v>495.5796918352</v>
       </c>
       <c r="Q46">
-        <v>793.9024162416001</v>
+        <v>835.3796918352</v>
       </c>
       <c r="R46">
         <v>0.7857142857142857</v>
       </c>
       <c r="S46">
-        <v>0.09331308473376976</v>
+        <v>0.09328253804469955</v>
       </c>
       <c r="T46">
         <v>1.096594412117772</v>
       </c>
       <c r="U46">
-        <v>0.0679</v>
+        <v>0.0613</v>
       </c>
       <c r="V46">
         <v>0.146</v>
       </c>
       <c r="W46">
-        <v>0.0579866</v>
+        <v>0.0523502</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y46">
-        <v>2.064186515733968</v>
+        <v>2.28643171971185</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5114,13 +5114,13 @@
         <v>0.45</v>
       </c>
       <c r="B47">
-        <v>0.07784978392385464</v>
+        <v>0.07637236446748222</v>
       </c>
       <c r="C47">
-        <v>7218.568055189731</v>
+        <v>7865.656826547718</v>
       </c>
       <c r="D47">
-        <v>13575.43805518973</v>
+        <v>14222.52682654772</v>
       </c>
       <c r="E47">
         <v>3184.37</v>
@@ -5147,37 +5147,37 @@
         <v>1031.4</v>
       </c>
       <c r="M47">
-        <v>511.020153</v>
+        <v>482.421087</v>
       </c>
       <c r="N47">
-        <v>520.3798470000002</v>
+        <v>548.9789130000001</v>
       </c>
       <c r="O47">
-        <v>75.97545766200001</v>
+        <v>80.15092129800001</v>
       </c>
       <c r="P47">
-        <v>444.4043893380002</v>
+        <v>468.8279917020001</v>
       </c>
       <c r="Q47">
-        <v>784.2043893380001</v>
+        <v>808.6279917020001</v>
       </c>
       <c r="R47">
         <v>0.8181818181818181</v>
       </c>
       <c r="S47">
-        <v>0.09410147986155387</v>
+        <v>0.09407042630451312</v>
       </c>
       <c r="T47">
         <v>1.114790445831712</v>
       </c>
       <c r="U47">
-        <v>0.0679</v>
+        <v>0.0641</v>
       </c>
       <c r="V47">
         <v>0.146</v>
       </c>
       <c r="W47">
-        <v>0.0579866</v>
+        <v>0.0547414</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5185,7 +5185,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>2.018315704273213</v>
+        <v>2.137966245244168</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5196,13 +5196,13 @@
         <v>0.46</v>
       </c>
       <c r="B48">
-        <v>0.08342989639679818</v>
+        <v>0.07642029162993269</v>
       </c>
       <c r="C48">
-        <v>5038.229315878279</v>
+        <v>7676.149596579357</v>
       </c>
       <c r="D48">
-        <v>11562.34531587828</v>
+        <v>14200.26559657936</v>
       </c>
       <c r="E48">
         <v>3351.616</v>
@@ -5229,45 +5229,45 @@
         <v>1031.4</v>
       </c>
       <c r="M48">
-        <v>630.0825804</v>
+        <v>493.1415556</v>
       </c>
       <c r="N48">
-        <v>401.3174196000001</v>
+        <v>538.2584444000001</v>
       </c>
       <c r="O48">
-        <v>58.59234326160001</v>
+        <v>78.58573288240001</v>
       </c>
       <c r="P48">
-        <v>342.7250763384001</v>
+        <v>459.6727115176001</v>
       </c>
       <c r="Q48">
-        <v>682.5250763384</v>
+        <v>799.4727115176001</v>
       </c>
       <c r="R48">
         <v>0.8518518518518519</v>
       </c>
       <c r="S48">
-        <v>0.09491907480888553</v>
+        <v>0.09488749561098646</v>
       </c>
       <c r="T48">
         <v>1.133660406720241</v>
       </c>
       <c r="U48">
-        <v>0.0819</v>
+        <v>0.0641</v>
       </c>
       <c r="V48">
         <v>0.146</v>
       </c>
       <c r="W48">
-        <v>0.06994259999999999</v>
+        <v>0.0547414</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y48">
-        <v>1.63692828858279</v>
+        <v>2.091488718173642</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5278,13 +5278,13 @@
         <v>0.47</v>
       </c>
       <c r="B49">
-        <v>0.08362980886974175</v>
+        <v>0.07646821879238316</v>
       </c>
       <c r="C49">
-        <v>4809.881842881581</v>
+        <v>7486.711944671091</v>
       </c>
       <c r="D49">
-        <v>11501.24384288158</v>
+        <v>14178.07394467109</v>
       </c>
       <c r="E49">
         <v>3518.862</v>
@@ -5311,45 +5311,45 @@
         <v>1031.4</v>
       </c>
       <c r="M49">
-        <v>643.7800278</v>
+        <v>503.8620242</v>
       </c>
       <c r="N49">
-        <v>387.6199722000001</v>
+        <v>527.5379758000001</v>
       </c>
       <c r="O49">
-        <v>56.59251594120001</v>
+        <v>77.02054446680002</v>
       </c>
       <c r="P49">
-        <v>331.0274562588001</v>
+        <v>450.5174313332001</v>
       </c>
       <c r="Q49">
-        <v>670.8274562588001</v>
+        <v>790.3174313332001</v>
       </c>
       <c r="R49">
         <v>0.8867924528301887</v>
       </c>
       <c r="S49">
-        <v>0.09576752239573916</v>
+        <v>0.09573539772147766</v>
       </c>
       <c r="T49">
         <v>1.153242441604565</v>
       </c>
       <c r="U49">
-        <v>0.0819</v>
+        <v>0.0641</v>
       </c>
       <c r="V49">
         <v>0.146</v>
       </c>
       <c r="W49">
-        <v>0.06994259999999999</v>
+        <v>0.0547414</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y49">
-        <v>1.602100027123582</v>
+        <v>2.046988958212501</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5360,13 +5360,13 @@
         <v>0.48</v>
       </c>
       <c r="B50">
-        <v>0.08382972134268532</v>
+        <v>0.07651614595483364</v>
       </c>
       <c r="C50">
-        <v>4582.176759370583</v>
+        <v>7297.343545129812</v>
       </c>
       <c r="D50">
-        <v>11440.78475937058</v>
+        <v>14155.95154512981</v>
       </c>
       <c r="E50">
         <v>3686.107999999999</v>
@@ -5393,45 +5393,45 @@
         <v>1031.4</v>
       </c>
       <c r="M50">
-        <v>657.4774752</v>
+        <v>514.5824928</v>
       </c>
       <c r="N50">
-        <v>373.9225248000001</v>
+        <v>516.8175072000001</v>
       </c>
       <c r="O50">
-        <v>54.59268862080002</v>
+        <v>75.45535605120001</v>
       </c>
       <c r="P50">
-        <v>319.3298361792001</v>
+        <v>441.3621511488001</v>
       </c>
       <c r="Q50">
-        <v>659.1298361792001</v>
+        <v>781.1621511488001</v>
       </c>
       <c r="R50">
         <v>0.923076923076923</v>
       </c>
       <c r="S50">
-        <v>0.09664860258208716</v>
+        <v>0.09661591145160314</v>
       </c>
       <c r="T50">
         <v>1.173577631676747</v>
       </c>
       <c r="U50">
-        <v>0.0819</v>
+        <v>0.0641</v>
       </c>
       <c r="V50">
         <v>0.146</v>
       </c>
       <c r="W50">
-        <v>0.06994259999999999</v>
+        <v>0.0547414</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y50">
-        <v>1.568722943225174</v>
+        <v>2.004343354916408</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5442,13 +5442,13 @@
         <v>0.49</v>
       </c>
       <c r="B51">
-        <v>0.08402963381562889</v>
+        <v>0.0798280611172841</v>
       </c>
       <c r="C51">
-        <v>4355.103987691546</v>
+        <v>5752.313768392214</v>
       </c>
       <c r="D51">
-        <v>11380.95798769154</v>
+        <v>12778.16776839221</v>
       </c>
       <c r="E51">
         <v>3853.353999999998</v>
@@ -5475,45 +5475,45 @@
         <v>1031.4</v>
       </c>
       <c r="M51">
-        <v>671.1749225999998</v>
+        <v>589.2243825999999</v>
       </c>
       <c r="N51">
-        <v>360.2250774000003</v>
+        <v>442.1756174000002</v>
       </c>
       <c r="O51">
-        <v>52.59286130040003</v>
+        <v>64.55764014040003</v>
       </c>
       <c r="P51">
-        <v>307.6322160996002</v>
+        <v>377.6179772596001</v>
       </c>
       <c r="Q51">
-        <v>647.4322160996002</v>
+        <v>717.4179772596001</v>
       </c>
       <c r="R51">
         <v>0.9607843137254901</v>
       </c>
       <c r="S51">
-        <v>0.09756423493260566</v>
+        <v>0.09753095513192962</v>
       </c>
       <c r="T51">
         <v>1.194710280183132</v>
       </c>
       <c r="U51">
-        <v>0.0819</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V51">
         <v>0.146</v>
       </c>
       <c r="W51">
-        <v>0.06994259999999999</v>
+        <v>0.0614026</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y51">
-        <v>1.536708189281803</v>
+        <v>1.750436727429481</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5524,13 +5524,13 @@
         <v>0.5</v>
       </c>
       <c r="B52">
-        <v>0.08422954628857245</v>
+        <v>0.08160790027973458</v>
       </c>
       <c r="C52">
-        <v>4128.653659888623</v>
+        <v>4949.926270541855</v>
       </c>
       <c r="D52">
-        <v>11321.75365988862</v>
+        <v>12143.02627054185</v>
       </c>
       <c r="E52">
         <v>4020.599999999999</v>
@@ -5557,37 +5557,37 @@
         <v>1031.4</v>
       </c>
       <c r="M52">
-        <v>684.8723699999999</v>
+        <v>633.86234</v>
       </c>
       <c r="N52">
-        <v>346.5276300000002</v>
+        <v>397.5376600000001</v>
       </c>
       <c r="O52">
-        <v>50.59303398000002</v>
+        <v>58.04049836000001</v>
       </c>
       <c r="P52">
-        <v>295.9345960200001</v>
+        <v>339.4971616400001</v>
       </c>
       <c r="Q52">
-        <v>635.73459602</v>
+        <v>679.29716164</v>
       </c>
       <c r="R52">
         <v>1</v>
       </c>
       <c r="S52">
-        <v>0.0985164925771449</v>
+        <v>0.09848260055946916</v>
       </c>
       <c r="T52">
         <v>1.216688234629772</v>
       </c>
       <c r="U52">
-        <v>0.0819</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V52">
         <v>0.146</v>
       </c>
       <c r="W52">
-        <v>0.06994259999999999</v>
+        <v>0.0647332</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5595,7 +5595,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>1.505974025496167</v>
+        <v>1.627167185859315</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5606,13 +5606,13 @@
         <v>0.51</v>
       </c>
       <c r="B53">
-        <v>0.1066753695495759</v>
+        <v>0.08175574544218504</v>
       </c>
       <c r="C53">
-        <v>-213.1227542146171</v>
+        <v>4732.749788791858</v>
       </c>
       <c r="D53">
-        <v>7147.223245785383</v>
+        <v>12093.09578879186</v>
       </c>
       <c r="E53">
         <v>4187.846</v>
@@ -5639,45 +5639,45 @@
         <v>1031.4</v>
       </c>
       <c r="M53">
-        <v>1116.5175714</v>
+        <v>646.5395868000001</v>
       </c>
       <c r="N53">
-        <v>-85.11757139999986</v>
+        <v>384.8604132</v>
       </c>
       <c r="O53">
-        <v>-12.42716542439998</v>
+        <v>56.1896203272</v>
       </c>
       <c r="P53">
-        <v>-72.69040597559989</v>
+        <v>328.6707928728</v>
       </c>
       <c r="Q53">
-        <v>267.1095940244001</v>
+        <v>668.4707928728</v>
       </c>
       <c r="R53">
         <v>1.040816326530612</v>
       </c>
       <c r="S53">
-        <v>0.09983701317512204</v>
+        <v>0.0994730886575205</v>
       </c>
       <c r="T53">
-        <v>1.24716563926351</v>
+        <v>1.239563248441582</v>
       </c>
       <c r="U53">
-        <v>0.1309</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V53">
-        <v>0.1348697090464796</v>
+        <v>0.146</v>
       </c>
       <c r="W53">
-        <v>0.1132455550858158</v>
+        <v>0.0647332</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y53">
-        <v>0.9237651304553398</v>
+        <v>1.595261946920897</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5688,13 +5688,13 @@
         <v>0.52</v>
       </c>
       <c r="B54">
-        <v>0.1075263695495759</v>
+        <v>0.08190359060463552</v>
       </c>
       <c r="C54">
-        <v>-478.9050366259507</v>
+        <v>4515.982240339736</v>
       </c>
       <c r="D54">
-        <v>7048.686963374048</v>
+        <v>12043.57424033973</v>
       </c>
       <c r="E54">
         <v>4355.092</v>
@@ -5721,45 +5721,45 @@
         <v>1031.4</v>
       </c>
       <c r="M54">
-        <v>1138.4100728</v>
+        <v>659.2168336</v>
       </c>
       <c r="N54">
-        <v>-107.0100727999998</v>
+        <v>372.1831664000001</v>
       </c>
       <c r="O54">
-        <v>-15.62347062879996</v>
+        <v>54.33874229440001</v>
       </c>
       <c r="P54">
-        <v>-91.3866021711998</v>
+        <v>317.8444241056001</v>
       </c>
       <c r="Q54">
-        <v>248.4133978288002</v>
+        <v>657.6444241056001</v>
       </c>
       <c r="R54">
         <v>1.083333333333333</v>
       </c>
       <c r="S54">
-        <v>0.1009627842829371</v>
+        <v>0.1005048470929907</v>
       </c>
       <c r="T54">
-        <v>1.273148256748167</v>
+        <v>1.263391387828884</v>
       </c>
       <c r="U54">
-        <v>0.1309</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V54">
-        <v>0.1322760607955858</v>
+        <v>0.146</v>
       </c>
       <c r="W54">
-        <v>0.1135850636418578</v>
+        <v>0.0647332</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y54">
-        <v>0.9060004164081218</v>
+        <v>1.564583832557033</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5770,13 +5770,13 @@
         <v>0.53</v>
       </c>
       <c r="B55">
-        <v>0.1083773695495759</v>
+        <v>0.082051435767086</v>
       </c>
       <c r="C55">
-        <v>-742.0072966286853</v>
+        <v>4299.618621895941</v>
       </c>
       <c r="D55">
-        <v>6952.830703371315</v>
+        <v>11994.45662189594</v>
       </c>
       <c r="E55">
         <v>4522.338000000001</v>
@@ -5803,45 +5803,45 @@
         <v>1031.4</v>
       </c>
       <c r="M55">
-        <v>1160.3025742</v>
+        <v>671.8940804000001</v>
       </c>
       <c r="N55">
-        <v>-128.9025741999999</v>
+        <v>359.5059196</v>
       </c>
       <c r="O55">
-        <v>-18.81977583319998</v>
+        <v>52.4878642616</v>
       </c>
       <c r="P55">
-        <v>-110.0827983667999</v>
+        <v>307.0180553384</v>
       </c>
       <c r="Q55">
-        <v>229.7172016332</v>
+        <v>646.8180553384</v>
       </c>
       <c r="R55">
         <v>1.127659574468085</v>
       </c>
       <c r="S55">
-        <v>0.1021364605442762</v>
+        <v>0.1015805101427362</v>
       </c>
       <c r="T55">
-        <v>1.300236517530043</v>
+        <v>1.288233490594368</v>
       </c>
       <c r="U55">
-        <v>0.1309</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V55">
-        <v>0.1297802860635936</v>
+        <v>0.146</v>
       </c>
       <c r="W55">
-        <v>0.1139117605542756</v>
+        <v>0.0647332</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y55">
-        <v>0.8889060689287231</v>
+        <v>1.535063382886146</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5852,13 +5852,13 @@
         <v>0.54</v>
       </c>
       <c r="B56">
-        <v>0.1092283695495759</v>
+        <v>0.08219928092953646</v>
       </c>
       <c r="C56">
-        <v>-1002.537405468098</v>
+        <v>4083.654011459595</v>
       </c>
       <c r="D56">
-        <v>6859.546594531902</v>
+        <v>11945.73801145959</v>
       </c>
       <c r="E56">
         <v>4689.584</v>
@@ -5885,45 +5885,45 @@
         <v>1031.4</v>
       </c>
       <c r="M56">
-        <v>1182.1950756</v>
+        <v>684.5713272</v>
       </c>
       <c r="N56">
-        <v>-150.7950755999998</v>
+        <v>346.8286728</v>
       </c>
       <c r="O56">
-        <v>-22.01608103759997</v>
+        <v>50.6369862288</v>
       </c>
       <c r="P56">
-        <v>-128.7789945623998</v>
+        <v>296.1916865712</v>
       </c>
       <c r="Q56">
-        <v>211.0210054376001</v>
+        <v>635.9916865712</v>
       </c>
       <c r="R56">
         <v>1.173913043478261</v>
       </c>
       <c r="S56">
-        <v>0.1033611662082822</v>
+        <v>0.1027029411511662</v>
       </c>
       <c r="T56">
-        <v>1.328502528780696</v>
+        <v>1.314155684784439</v>
       </c>
       <c r="U56">
-        <v>0.1309</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V56">
-        <v>0.1273769474327863</v>
+        <v>0.146</v>
       </c>
       <c r="W56">
-        <v>0.1142263575810483</v>
+        <v>0.0647332</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y56">
-        <v>0.8724448454300432</v>
+        <v>1.506636283203069</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5934,13 +5934,13 @@
         <v>0.55</v>
       </c>
       <c r="B57">
-        <v>0.1100793695495759</v>
+        <v>0.1030946423801973</v>
       </c>
       <c r="C57">
-        <v>-1260.597521923369</v>
+        <v>-440.2037619061339</v>
       </c>
       <c r="D57">
-        <v>6768.732478076632</v>
+        <v>7589.126238093867</v>
       </c>
       <c r="E57">
         <v>4856.830000000001</v>
@@ -5967,37 +5967,37 @@
         <v>1031.4</v>
       </c>
       <c r="M57">
-        <v>1204.087577</v>
+        <v>1090.945658</v>
       </c>
       <c r="N57">
-        <v>-172.6875769999999</v>
+        <v>-59.545658</v>
       </c>
       <c r="O57">
-        <v>-25.21238624199999</v>
+        <v>-8.693666068000001</v>
       </c>
       <c r="P57">
-        <v>-147.4751907579999</v>
+        <v>-50.851991932</v>
       </c>
       <c r="Q57">
-        <v>192.324809242</v>
+        <v>288.9480080679999</v>
       </c>
       <c r="R57">
         <v>1.222222222222223</v>
       </c>
       <c r="S57">
-        <v>0.1046403032351329</v>
+        <v>0.1041520206365138</v>
       </c>
       <c r="T57">
-        <v>1.358024807198045</v>
+        <v>1.347621723707015</v>
       </c>
       <c r="U57">
-        <v>0.1309</v>
+        <v>0.1186</v>
       </c>
       <c r="V57">
-        <v>0.1250610029340083</v>
+        <v>0.1380310732214308</v>
       </c>
       <c r="W57">
-        <v>0.1145295147159383</v>
+        <v>0.1022295147159383</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -6005,7 +6005,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.8565822118767695</v>
+        <v>0.9454183097358274</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6016,13 +6016,13 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1109303695495759</v>
+        <v>0.1038226423801973</v>
       </c>
       <c r="C58">
-        <v>-1516.284465505897</v>
+        <v>-702.6692085685245</v>
       </c>
       <c r="D58">
-        <v>6680.291534494103</v>
+        <v>7493.906791431475</v>
       </c>
       <c r="E58">
         <v>5024.076</v>
@@ -6049,37 +6049,37 @@
         <v>1031.4</v>
       </c>
       <c r="M58">
-        <v>1225.9800784</v>
+        <v>1110.7810336</v>
       </c>
       <c r="N58">
-        <v>-194.5800783999998</v>
+        <v>-79.38103359999991</v>
       </c>
       <c r="O58">
-        <v>-28.40869144639997</v>
+        <v>-11.58963090559999</v>
       </c>
       <c r="P58">
-        <v>-166.1713869535998</v>
+        <v>-67.79140269439992</v>
       </c>
       <c r="Q58">
-        <v>173.6286130464001</v>
+        <v>272.0085973056</v>
       </c>
       <c r="R58">
         <v>1.272727272727273</v>
       </c>
       <c r="S58">
-        <v>0.1059775828541132</v>
+        <v>0.1054782029237073</v>
       </c>
       <c r="T58">
-        <v>1.388889007361636</v>
+        <v>1.378249490154902</v>
       </c>
       <c r="U58">
-        <v>0.1309</v>
+        <v>0.1186</v>
       </c>
       <c r="V58">
-        <v>0.1228277707387582</v>
+        <v>0.135566232628191</v>
       </c>
       <c r="W58">
-        <v>0.1148218448102965</v>
+        <v>0.1025218448102966</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6087,7 +6087,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.8412861009503987</v>
+        <v>0.9285358399191163</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6098,13 +6098,13 @@
         <v>0.5700000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1117813695495759</v>
+        <v>0.1045506423801973</v>
       </c>
       <c r="C59">
-        <v>-1769.690060777455</v>
+        <v>-962.7748595125449</v>
       </c>
       <c r="D59">
-        <v>6594.131939222546</v>
+        <v>7401.047140487455</v>
       </c>
       <c r="E59">
         <v>5191.322000000001</v>
@@ -6131,37 +6131,37 @@
         <v>1031.4</v>
       </c>
       <c r="M59">
-        <v>1247.8725798</v>
+        <v>1130.6164092</v>
       </c>
       <c r="N59">
-        <v>-216.4725797999999</v>
+        <v>-99.21640920000004</v>
       </c>
       <c r="O59">
-        <v>-31.60499665079999</v>
+        <v>-14.4855957432</v>
       </c>
       <c r="P59">
-        <v>-184.8675831492</v>
+        <v>-84.73081345680004</v>
       </c>
       <c r="Q59">
-        <v>154.9324168508</v>
+        <v>255.0691865431999</v>
       </c>
       <c r="R59">
         <v>1.325581395348838</v>
       </c>
       <c r="S59">
-        <v>0.1073770615251391</v>
+        <v>0.1068660681079795</v>
       </c>
       <c r="T59">
-        <v>1.421188751718884</v>
+        <v>1.410301803879435</v>
       </c>
       <c r="U59">
-        <v>0.1309</v>
+        <v>0.1186</v>
       </c>
       <c r="V59">
-        <v>0.1206728975679028</v>
+        <v>0.1331878776698016</v>
       </c>
       <c r="W59">
-        <v>0.1151039177083615</v>
+        <v>0.1028039177083615</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6169,7 +6169,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.8265266956705671</v>
+        <v>0.9122457374643949</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6180,13 +6180,13 @@
         <v>0.58</v>
       </c>
       <c r="B60">
-        <v>0.1126323695495759</v>
+        <v>0.1052786423801973</v>
       </c>
       <c r="C60">
-        <v>-2020.901455362417</v>
+        <v>-1220.607364225179</v>
       </c>
       <c r="D60">
-        <v>6510.166544637581</v>
+        <v>7310.460635774818</v>
       </c>
       <c r="E60">
         <v>5358.567999999998</v>
@@ -6213,37 +6213,37 @@
         <v>1031.4</v>
       </c>
       <c r="M60">
-        <v>1269.7650812</v>
+        <v>1150.4517848</v>
       </c>
       <c r="N60">
-        <v>-238.3650811999996</v>
+        <v>-119.0517847999997</v>
       </c>
       <c r="O60">
-        <v>-34.80130185519995</v>
+        <v>-17.38156058079996</v>
       </c>
       <c r="P60">
-        <v>-203.5637793447997</v>
+        <v>-101.6702242191998</v>
       </c>
       <c r="Q60">
-        <v>136.2362206552003</v>
+        <v>238.1297757808002</v>
       </c>
       <c r="R60">
         <v>1.380952380952381</v>
       </c>
       <c r="S60">
-        <v>0.1088431820376424</v>
+        <v>0.1083200221105505</v>
       </c>
       <c r="T60">
-        <v>1.455026579140762</v>
+        <v>1.443880418257516</v>
       </c>
       <c r="U60">
-        <v>0.1309</v>
+        <v>0.1186</v>
       </c>
       <c r="V60">
-        <v>0.1185923303684562</v>
+        <v>0.1308915349513568</v>
       </c>
       <c r="W60">
-        <v>0.1153762639547691</v>
+        <v>0.1030762639547691</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6251,7 +6251,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.8122762354003852</v>
+        <v>0.8965173626805262</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6262,13 +6262,13 @@
         <v>0.59</v>
       </c>
       <c r="B61">
-        <v>0.164343814624442</v>
+        <v>0.1060066423801973</v>
       </c>
       <c r="C61">
-        <v>-5028.02670817537</v>
+        <v>-1476.249181238796</v>
       </c>
       <c r="D61">
-        <v>3670.287291824629</v>
+        <v>7222.064818761203</v>
       </c>
       <c r="E61">
         <v>5525.813999999999</v>
@@ -6295,45 +6295,45 @@
         <v>1031.4</v>
       </c>
       <c r="M61">
-        <v>2129.4095212</v>
+        <v>1170.2871604</v>
       </c>
       <c r="N61">
-        <v>-1098.0095212</v>
+        <v>-138.8871603999999</v>
       </c>
       <c r="O61">
-        <v>-160.3093900952</v>
+        <v>-20.27752541839998</v>
       </c>
       <c r="P61">
-        <v>-937.7001311048001</v>
+        <v>-118.6096349815999</v>
       </c>
       <c r="Q61">
-        <v>-597.9001311048002</v>
+        <v>221.1903650184001</v>
       </c>
       <c r="R61">
         <v>1.439024390243902</v>
       </c>
       <c r="S61">
-        <v>0.112257515928478</v>
+        <v>0.1098449006986127</v>
       </c>
       <c r="T61">
-        <v>1.53382886038127</v>
+        <v>1.479097013824773</v>
       </c>
       <c r="U61">
-        <v>0.2158</v>
+        <v>0.1186</v>
       </c>
       <c r="V61">
-        <v>0.07071650544473013</v>
+        <v>0.1286730343589609</v>
       </c>
       <c r="W61">
-        <v>0.2005393781250273</v>
+        <v>0.1033393781250272</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y61">
-        <v>0.4843596263337681</v>
+        <v>0.881322153143568</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6344,13 +6344,13 @@
         <v>0.6</v>
       </c>
       <c r="B62">
-        <v>0.166043814624442</v>
+        <v>0.1067346423801973</v>
       </c>
       <c r="C62">
-        <v>-5247.163014679614</v>
+        <v>-1729.778828482566</v>
       </c>
       <c r="D62">
-        <v>3618.396985320384</v>
+        <v>7135.781171517433</v>
       </c>
       <c r="E62">
         <v>5693.059999999999</v>
@@ -6377,45 +6377,45 @@
         <v>1031.4</v>
       </c>
       <c r="M62">
-        <v>2165.501208</v>
+        <v>1190.122536</v>
       </c>
       <c r="N62">
-        <v>-1134.101208</v>
+        <v>-158.7225359999998</v>
       </c>
       <c r="O62">
-        <v>-165.5787763679999</v>
+        <v>-23.17349025599997</v>
       </c>
       <c r="P62">
-        <v>-968.5224316319997</v>
+        <v>-135.5490457439998</v>
       </c>
       <c r="Q62">
-        <v>-628.7224316319997</v>
+        <v>204.2509542560002</v>
       </c>
       <c r="R62">
         <v>1.5</v>
       </c>
       <c r="S62">
-        <v>0.1139189538266899</v>
+        <v>0.111446023216078</v>
       </c>
       <c r="T62">
-        <v>1.572174581890802</v>
+        <v>1.516074439170392</v>
       </c>
       <c r="U62">
-        <v>0.2158</v>
+        <v>0.1186</v>
       </c>
       <c r="V62">
-        <v>0.06953789702065132</v>
+        <v>0.1265284837863116</v>
       </c>
       <c r="W62">
-        <v>0.2007937218229435</v>
+        <v>0.1035937218229435</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y62">
-        <v>0.4762869658948721</v>
+        <v>0.8666334505911752</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6426,13 +6426,13 @@
         <v>0.61</v>
       </c>
       <c r="B63">
-        <v>0.167743814624442</v>
+        <v>0.1074626423801973</v>
       </c>
       <c r="C63">
-        <v>-5464.852531589343</v>
+        <v>-1981.271115899741</v>
       </c>
       <c r="D63">
-        <v>3567.953468410657</v>
+        <v>7051.534884100258</v>
       </c>
       <c r="E63">
         <v>5860.306</v>
@@ -6459,45 +6459,45 @@
         <v>1031.4</v>
       </c>
       <c r="M63">
-        <v>2201.5928948</v>
+        <v>1209.9579116</v>
       </c>
       <c r="N63">
-        <v>-1170.1928948</v>
+        <v>-178.5579115999999</v>
       </c>
       <c r="O63">
-        <v>-170.8481626408</v>
+        <v>-26.06945509359998</v>
       </c>
       <c r="P63">
-        <v>-999.3447321592</v>
+        <v>-152.4884565063999</v>
       </c>
       <c r="Q63">
-        <v>-659.5447321592001</v>
+        <v>187.3115434936</v>
       </c>
       <c r="R63">
         <v>1.564102564102564</v>
       </c>
       <c r="S63">
-        <v>0.1156655936683999</v>
+        <v>0.1131292545805928</v>
       </c>
       <c r="T63">
-        <v>1.612486750657233</v>
+        <v>1.554948142738864</v>
       </c>
       <c r="U63">
-        <v>0.2158</v>
+        <v>0.1186</v>
       </c>
       <c r="V63">
-        <v>0.0683979314957226</v>
+        <v>0.1244542463471917</v>
       </c>
       <c r="W63">
-        <v>0.2010397263832231</v>
+        <v>0.1038397263832231</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y63">
-        <v>0.4684789828474151</v>
+        <v>0.8524263448437789</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6508,13 +6508,13 @@
         <v>0.62</v>
       </c>
       <c r="B64">
-        <v>0.1694438146244421</v>
+        <v>0.1081906423801973</v>
       </c>
       <c r="C64">
-        <v>-5681.154935378902</v>
+        <v>-2230.79736177928</v>
       </c>
       <c r="D64">
-        <v>3518.897064621096</v>
+        <v>6969.254638220719</v>
       </c>
       <c r="E64">
         <v>6027.551999999999</v>
@@ -6541,45 +6541,45 @@
         <v>1031.4</v>
       </c>
       <c r="M64">
-        <v>2237.6845816</v>
+        <v>1229.7932872</v>
       </c>
       <c r="N64">
-        <v>-1206.2845816</v>
+        <v>-198.3932871999998</v>
       </c>
       <c r="O64">
-        <v>-176.1175489136</v>
+        <v>-28.96541993119997</v>
       </c>
       <c r="P64">
-        <v>-1030.1670326864</v>
+        <v>-169.4278672687998</v>
       </c>
       <c r="Q64">
-        <v>-690.3670326864001</v>
+        <v>170.3721327312001</v>
       </c>
       <c r="R64">
         <v>1.631578947368421</v>
       </c>
       <c r="S64">
-        <v>0.1175041619228315</v>
+        <v>0.1149010770695558</v>
       </c>
       <c r="T64">
-        <v>1.654920612516634</v>
+        <v>1.595867830705676</v>
       </c>
       <c r="U64">
-        <v>0.2158</v>
+        <v>0.1186</v>
       </c>
       <c r="V64">
-        <v>0.0672947390522432</v>
+        <v>0.1224469197932048</v>
       </c>
       <c r="W64">
-        <v>0.201277795312526</v>
+        <v>0.1040777953125259</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y64">
-        <v>0.4609228702208439</v>
+        <v>0.8386775328301697</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6590,13 +6590,13 @@
         <v>0.63</v>
       </c>
       <c r="B65">
-        <v>0.171143814624442</v>
+        <v>0.1089186423801973</v>
       </c>
       <c r="C65">
-        <v>-5896.126665027226</v>
+        <v>-2478.425594116657</v>
       </c>
       <c r="D65">
-        <v>3471.171334972773</v>
+        <v>6888.872405883343</v>
       </c>
       <c r="E65">
         <v>6194.798</v>
@@ -6623,45 +6623,45 @@
         <v>1031.4</v>
       </c>
       <c r="M65">
-        <v>2273.7762684</v>
+        <v>1249.6286628</v>
       </c>
       <c r="N65">
-        <v>-1242.3762684</v>
+        <v>-218.2286627999999</v>
       </c>
       <c r="O65">
-        <v>-181.3869351864</v>
+        <v>-31.86138476879999</v>
       </c>
       <c r="P65">
-        <v>-1060.9893332136</v>
+        <v>-186.3672780312</v>
       </c>
       <c r="Q65">
-        <v>-721.1893332135999</v>
+        <v>153.4327219688</v>
       </c>
       <c r="R65">
         <v>1.702702702702703</v>
       </c>
       <c r="S65">
-        <v>0.1194421122450702</v>
+        <v>0.1167686737471114</v>
       </c>
       <c r="T65">
-        <v>1.699648196638704</v>
+        <v>1.638999393697722</v>
       </c>
       <c r="U65">
-        <v>0.2158</v>
+        <v>0.1186</v>
       </c>
       <c r="V65">
-        <v>0.06622656859109649</v>
+        <v>0.1205033178917253</v>
       </c>
       <c r="W65">
-        <v>0.2015083064980414</v>
+        <v>0.1043083064980414</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y65">
-        <v>0.4536066341855923</v>
+        <v>0.8253651910392145</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6672,13 +6672,13 @@
         <v>0.64</v>
       </c>
       <c r="B66">
-        <v>0.172843814624442</v>
+        <v>0.1096466423801973</v>
       </c>
       <c r="C66">
-        <v>-6109.821138625864</v>
+        <v>-2724.220738198795</v>
       </c>
       <c r="D66">
-        <v>3424.722861374134</v>
+        <v>6810.323261801204</v>
       </c>
       <c r="E66">
         <v>6362.043999999999</v>
@@ -6705,45 +6705,45 @@
         <v>1031.4</v>
       </c>
       <c r="M66">
-        <v>2309.8679552</v>
+        <v>1269.4640384</v>
       </c>
       <c r="N66">
-        <v>-1278.4679552</v>
+        <v>-238.0640383999998</v>
       </c>
       <c r="O66">
-        <v>-186.6563214591999</v>
+        <v>-34.75734960639998</v>
       </c>
       <c r="P66">
-        <v>-1091.8116337408</v>
+        <v>-203.3066887935999</v>
       </c>
       <c r="Q66">
-        <v>-752.0116337407999</v>
+        <v>136.4933112064001</v>
       </c>
       <c r="R66">
         <v>1.777777777777778</v>
       </c>
       <c r="S66">
-        <v>0.1214877264740999</v>
+        <v>0.1187400257956422</v>
       </c>
       <c r="T66">
-        <v>1.746860646545335</v>
+        <v>1.684527154633769</v>
       </c>
       <c r="U66">
-        <v>0.2158</v>
+        <v>0.1186</v>
       </c>
       <c r="V66">
-        <v>0.06519177845686061</v>
+        <v>0.1186204535496671</v>
       </c>
       <c r="W66">
-        <v>0.2017316142090095</v>
+        <v>0.1045316142090095</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y66">
-        <v>0.4465190305264425</v>
+        <v>0.8124688599292268</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6754,13 +6754,13 @@
         <v>0.65</v>
       </c>
       <c r="B67">
-        <v>0.1745438146244421</v>
+        <v>0.1646877327286938</v>
       </c>
       <c r="C67">
-        <v>-6322.288952825791</v>
+        <v>-6044.421289116877</v>
       </c>
       <c r="D67">
-        <v>3379.501047174208</v>
+        <v>3657.368710883123</v>
       </c>
       <c r="E67">
         <v>6529.29</v>
@@ -6787,37 +6787,37 @@
         <v>1031.4</v>
       </c>
       <c r="M67">
-        <v>2345.959642</v>
+        <v>2182.894792</v>
       </c>
       <c r="N67">
-        <v>-1314.559642</v>
+        <v>-1151.494792</v>
       </c>
       <c r="O67">
-        <v>-191.925707732</v>
+        <v>-168.118239632</v>
       </c>
       <c r="P67">
-        <v>-1122.633934268</v>
+        <v>-983.3765523679999</v>
       </c>
       <c r="Q67">
-        <v>-782.8339342680001</v>
+        <v>-643.576552368</v>
       </c>
       <c r="R67">
         <v>1.857142857142857</v>
       </c>
       <c r="S67">
-        <v>0.1236502329447885</v>
+        <v>0.1233471418140792</v>
       </c>
       <c r="T67">
-        <v>1.796770950732345</v>
+        <v>1.790927062680812</v>
       </c>
       <c r="U67">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V67">
-        <v>0.06418882801906274</v>
+        <v>0.06898381019180148</v>
       </c>
       <c r="W67">
-        <v>0.2019480509134863</v>
+        <v>0.1869480509134863</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6825,7 +6825,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.4396495069798818</v>
+        <v>0.4724918506287774</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6836,13 +6836,13 @@
         <v>0.66</v>
       </c>
       <c r="B68">
-        <v>0.1762438146244421</v>
+        <v>0.1662377327286938</v>
       </c>
       <c r="C68">
-        <v>-6533.578066688543</v>
+        <v>-6258.736603470702</v>
       </c>
       <c r="D68">
-        <v>3335.457933311456</v>
+        <v>3610.299396529297</v>
       </c>
       <c r="E68">
         <v>6696.535999999999</v>
@@ -6869,37 +6869,37 @@
         <v>1031.4</v>
       </c>
       <c r="M68">
-        <v>2382.0513288</v>
+        <v>2216.4777888</v>
       </c>
       <c r="N68">
-        <v>-1350.6513288</v>
+        <v>-1185.0777888</v>
       </c>
       <c r="O68">
-        <v>-197.1950940048</v>
+        <v>-173.0213571648</v>
       </c>
       <c r="P68">
-        <v>-1153.4562347952</v>
+        <v>-1012.0564316352</v>
       </c>
       <c r="Q68">
-        <v>-813.6562347952001</v>
+        <v>-672.2564316351999</v>
       </c>
       <c r="R68">
         <v>1.941176470588236</v>
       </c>
       <c r="S68">
-        <v>0.1259399456784587</v>
+        <v>0.1256279401027285</v>
       </c>
       <c r="T68">
-        <v>1.849617155165649</v>
+        <v>1.843601388053777</v>
       </c>
       <c r="U68">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V68">
-        <v>0.0632162700187739</v>
+        <v>0.06793860094647117</v>
       </c>
       <c r="W68">
-        <v>0.2021579289299486</v>
+        <v>0.1871579289299486</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6907,7 +6907,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.4329881508135199</v>
+        <v>0.4653328831950081</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6918,13 +6918,13 @@
         <v>0.67</v>
       </c>
       <c r="B69">
-        <v>0.177943814624442</v>
+        <v>0.1677877327286938</v>
       </c>
       <c r="C69">
-        <v>-6743.733971346167</v>
+        <v>-6471.855773989136</v>
       </c>
       <c r="D69">
-        <v>3292.548028653833</v>
+        <v>3564.426226010864</v>
       </c>
       <c r="E69">
         <v>6863.782</v>
@@ -6951,37 +6951,37 @@
         <v>1031.4</v>
       </c>
       <c r="M69">
-        <v>2418.1430156</v>
+        <v>2250.0607856</v>
       </c>
       <c r="N69">
-        <v>-1386.7430156</v>
+        <v>-1218.6607856</v>
       </c>
       <c r="O69">
-        <v>-202.4644802776</v>
+        <v>-177.9244746976</v>
       </c>
       <c r="P69">
-        <v>-1184.2785353224</v>
+        <v>-1040.7363109024</v>
       </c>
       <c r="Q69">
-        <v>-844.4785353224001</v>
+        <v>-700.9363109024</v>
       </c>
       <c r="R69">
         <v>2.030303030303031</v>
       </c>
       <c r="S69">
-        <v>0.1283684288808363</v>
+        <v>0.12804696859069</v>
       </c>
       <c r="T69">
-        <v>1.905666159867639</v>
+        <v>1.899468096782679</v>
       </c>
       <c r="U69">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V69">
-        <v>0.06227274360058326</v>
+        <v>0.06692459197712085</v>
       </c>
       <c r="W69">
-        <v>0.2023615419309941</v>
+        <v>0.1873615419309941</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6989,7 +6989,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.4265256410998853</v>
+        <v>0.4583876162816497</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7000,13 +7000,13 @@
         <v>0.68</v>
       </c>
       <c r="B70">
-        <v>0.1796438146244421</v>
+        <v>0.1693377327286938</v>
       </c>
       <c r="C70">
-        <v>-6952.799846731647</v>
+        <v>-6683.823823910921</v>
       </c>
       <c r="D70">
-        <v>3250.728153268352</v>
+        <v>3519.704176089078</v>
       </c>
       <c r="E70">
         <v>7031.027999999999</v>
@@ -7033,37 +7033,37 @@
         <v>1031.4</v>
       </c>
       <c r="M70">
-        <v>2454.2347024</v>
+        <v>2283.6437824</v>
       </c>
       <c r="N70">
-        <v>-1422.8347024</v>
+        <v>-1252.2437824</v>
       </c>
       <c r="O70">
-        <v>-207.7338665504</v>
+        <v>-182.8275922304</v>
       </c>
       <c r="P70">
-        <v>-1215.1008358496</v>
+        <v>-1069.4161901696</v>
       </c>
       <c r="Q70">
-        <v>-875.3008358495999</v>
+        <v>-729.6161901696</v>
       </c>
       <c r="R70">
         <v>2.125</v>
       </c>
       <c r="S70">
-        <v>0.1309486922833624</v>
+        <v>0.1306171863591491</v>
       </c>
       <c r="T70">
-        <v>1.965218227363503</v>
+        <v>1.958826474807138</v>
       </c>
       <c r="U70">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V70">
-        <v>0.06135696795939821</v>
+        <v>0.06594040680098673</v>
       </c>
       <c r="W70">
-        <v>0.2025591663143619</v>
+        <v>0.1875591663143619</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7071,7 +7071,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.4202532052013577</v>
+        <v>0.4516466219245666</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7082,13 +7082,13 @@
         <v>0.6900000000000001</v>
       </c>
       <c r="B71">
-        <v>0.181343814624442</v>
+        <v>0.1708877327286938</v>
       </c>
       <c r="C71">
-        <v>-7160.816706515017</v>
+        <v>-6894.683544888429</v>
       </c>
       <c r="D71">
-        <v>3209.957293484983</v>
+        <v>3476.090455111572</v>
       </c>
       <c r="E71">
         <v>7198.274</v>
@@ -7115,37 +7115,37 @@
         <v>1031.4</v>
       </c>
       <c r="M71">
-        <v>2490.3263892</v>
+        <v>2317.2267792</v>
       </c>
       <c r="N71">
-        <v>-1458.9263892</v>
+        <v>-1285.8267792</v>
       </c>
       <c r="O71">
-        <v>-213.0032528232</v>
+        <v>-187.7307097632</v>
       </c>
       <c r="P71">
-        <v>-1245.9231363768</v>
+        <v>-1098.0960694368</v>
       </c>
       <c r="Q71">
-        <v>-906.1231363768004</v>
+        <v>-758.2960694368003</v>
       </c>
       <c r="R71">
         <v>2.225806451612904</v>
       </c>
       <c r="S71">
-        <v>0.1336954242925031</v>
+        <v>0.1333532246287991</v>
       </c>
       <c r="T71">
-        <v>2.028612363730067</v>
+        <v>2.022014425607368</v>
       </c>
       <c r="U71">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V71">
-        <v>0.06046773653969677</v>
+        <v>0.06498474873140719</v>
       </c>
       <c r="W71">
-        <v>0.2027510624547335</v>
+        <v>0.1877510624547334</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7153,7 +7153,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.4141625790390191</v>
+        <v>0.4451010187082685</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7164,13 +7164,13 @@
         <v>0.7000000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1830438146244421</v>
+        <v>0.1724377327286938</v>
       </c>
       <c r="C72">
-        <v>-7367.823532267762</v>
+        <v>-7104.475633556691</v>
       </c>
       <c r="D72">
-        <v>3170.196467732238</v>
+        <v>3433.544366443309</v>
       </c>
       <c r="E72">
         <v>7365.52</v>
@@ -7197,37 +7197,37 @@
         <v>1031.4</v>
       </c>
       <c r="M72">
-        <v>2526.418076</v>
+        <v>2350.809776</v>
       </c>
       <c r="N72">
-        <v>-1495.018076</v>
+        <v>-1319.409776</v>
       </c>
       <c r="O72">
-        <v>-218.2726390959999</v>
+        <v>-192.633827296</v>
       </c>
       <c r="P72">
-        <v>-1276.745436904</v>
+        <v>-1126.775948704</v>
       </c>
       <c r="Q72">
-        <v>-936.945436904</v>
+        <v>-786.9759487040001</v>
       </c>
       <c r="R72">
         <v>2.333333333333334</v>
       </c>
       <c r="S72">
-        <v>0.1366252717689199</v>
+        <v>0.136271665449759</v>
       </c>
       <c r="T72">
-        <v>2.096232775854403</v>
+        <v>2.089414906460947</v>
       </c>
       <c r="U72">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V72">
-        <v>0.05960391173198683</v>
+        <v>0.06405639517810138</v>
       </c>
       <c r="W72">
-        <v>0.2029374758482373</v>
+        <v>0.1879374758482373</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7235,7 +7235,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.4082459707670332</v>
+        <v>0.4387424327267219</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7246,13 +7246,13 @@
         <v>0.71</v>
       </c>
       <c r="B73">
-        <v>0.184743814624442</v>
+        <v>0.1739877327286938</v>
       </c>
       <c r="C73">
-        <v>-7573.857397778088</v>
+        <v>-7313.238818194404</v>
       </c>
       <c r="D73">
-        <v>3131.40860222191</v>
+        <v>3392.027181805594</v>
       </c>
       <c r="E73">
         <v>7532.765999999999</v>
@@ -7279,37 +7279,37 @@
         <v>1031.4</v>
       </c>
       <c r="M73">
-        <v>2562.5097628</v>
+        <v>2384.3927728</v>
       </c>
       <c r="N73">
-        <v>-1531.1097628</v>
+        <v>-1352.9927728</v>
       </c>
       <c r="O73">
-        <v>-223.5420253688</v>
+        <v>-197.5369448288</v>
       </c>
       <c r="P73">
-        <v>-1307.5677374312</v>
+        <v>-1155.4558279712</v>
       </c>
       <c r="Q73">
-        <v>-967.7677374312</v>
+        <v>-815.6558279711999</v>
       </c>
       <c r="R73">
         <v>2.448275862068965</v>
       </c>
       <c r="S73">
-        <v>0.1397571776919861</v>
+        <v>0.1393913780514748</v>
       </c>
       <c r="T73">
-        <v>2.168516664676968</v>
+        <v>2.16146369633891</v>
       </c>
       <c r="U73">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V73">
-        <v>0.05876442001745181</v>
+        <v>0.06315419242911405</v>
       </c>
       <c r="W73">
-        <v>0.2031186381602339</v>
+        <v>0.1881186381602339</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7317,7 +7317,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.4024960275167933</v>
+        <v>0.4325629618432469</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7328,13 +7328,13 @@
         <v>0.72</v>
       </c>
       <c r="B74">
-        <v>0.1864438146244421</v>
+        <v>0.1755377327286938</v>
       </c>
       <c r="C74">
-        <v>-7778.953584350404</v>
+        <v>-7521.009976305447</v>
       </c>
       <c r="D74">
-        <v>3093.558415649594</v>
+        <v>3351.502023694551</v>
       </c>
       <c r="E74">
         <v>7700.011999999998</v>
@@ -7361,37 +7361,37 @@
         <v>1031.4</v>
       </c>
       <c r="M74">
-        <v>2598.6014496</v>
+        <v>2417.9757696</v>
       </c>
       <c r="N74">
-        <v>-1567.2014496</v>
+        <v>-1386.5757696</v>
       </c>
       <c r="O74">
-        <v>-228.8114116415999</v>
+        <v>-202.4400623615999</v>
       </c>
       <c r="P74">
-        <v>-1338.3900379584</v>
+        <v>-1184.1357072384</v>
       </c>
       <c r="Q74">
-        <v>-998.5900379583998</v>
+        <v>-844.3357072383997</v>
       </c>
       <c r="R74">
         <v>2.571428571428571</v>
       </c>
       <c r="S74">
-        <v>0.1431127911809856</v>
+        <v>0.1427339272675989</v>
       </c>
       <c r="T74">
-        <v>2.245963688415431</v>
+        <v>2.238658828351014</v>
       </c>
       <c r="U74">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V74">
-        <v>0.05794824751720943</v>
+        <v>0.06227705086759858</v>
       </c>
       <c r="W74">
-        <v>0.2032947681857862</v>
+        <v>0.1882947681857862</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7399,7 +7399,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.3969058049123934</v>
+        <v>0.4265551429287574</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7410,13 +7410,13 @@
         <v>0.73</v>
       </c>
       <c r="B75">
-        <v>0.1881438146244421</v>
+        <v>0.1770877327286938</v>
       </c>
       <c r="C75">
-        <v>-7983.145687842712</v>
+        <v>-7727.824243871327</v>
       </c>
       <c r="D75">
-        <v>3056.612312157287</v>
+        <v>3311.933756128672</v>
       </c>
       <c r="E75">
         <v>7867.257999999999</v>
@@ -7443,37 +7443,37 @@
         <v>1031.4</v>
       </c>
       <c r="M75">
-        <v>2634.6931364</v>
+        <v>2451.5587664</v>
       </c>
       <c r="N75">
-        <v>-1603.2931364</v>
+        <v>-1420.1587664</v>
       </c>
       <c r="O75">
-        <v>-234.0807979144</v>
+        <v>-207.3431798944</v>
       </c>
       <c r="P75">
-        <v>-1369.2123384856</v>
+        <v>-1212.8155865056</v>
       </c>
       <c r="Q75">
-        <v>-1029.4123384856</v>
+        <v>-873.0155865055999</v>
       </c>
       <c r="R75">
         <v>2.703703703703703</v>
       </c>
       <c r="S75">
-        <v>0.1467169686321332</v>
+        <v>0.1463240727219544</v>
       </c>
       <c r="T75">
-        <v>2.329147528727114</v>
+        <v>2.321572118289941</v>
       </c>
       <c r="U75">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V75">
-        <v>0.05715443590738463</v>
+        <v>0.06142394058174106</v>
       </c>
       <c r="W75">
-        <v>0.2034660727311864</v>
+        <v>0.1884660727311864</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7481,7 +7481,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.3914687390916756</v>
+        <v>0.420711921792747</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7492,13 +7492,13 @@
         <v>0.74</v>
       </c>
       <c r="B76">
-        <v>0.1898438146244421</v>
+        <v>0.1786377327286938</v>
       </c>
       <c r="C76">
-        <v>-8186.465718124506</v>
+        <v>-7933.71511695482</v>
       </c>
       <c r="D76">
-        <v>3020.538281875492</v>
+        <v>3273.288883045178</v>
       </c>
       <c r="E76">
         <v>8034.503999999998</v>
@@ -7525,37 +7525,37 @@
         <v>1031.4</v>
       </c>
       <c r="M76">
-        <v>2670.7848232</v>
+        <v>2485.1417632</v>
       </c>
       <c r="N76">
-        <v>-1639.3848232</v>
+        <v>-1453.7417632</v>
       </c>
       <c r="O76">
-        <v>-239.3501841871999</v>
+        <v>-212.2462974271999</v>
       </c>
       <c r="P76">
-        <v>-1400.0346390128</v>
+        <v>-1241.4954657728</v>
       </c>
       <c r="Q76">
-        <v>-1060.2346390128</v>
+        <v>-901.6954657727997</v>
       </c>
       <c r="R76">
         <v>2.846153846153846</v>
       </c>
       <c r="S76">
-        <v>0.1505983905025999</v>
+        <v>0.1501903832112604</v>
       </c>
       <c r="T76">
-        <v>2.418730125985849</v>
+        <v>2.410863353608784</v>
       </c>
       <c r="U76">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V76">
-        <v>0.05638207866539296</v>
+        <v>0.06059388733063645</v>
       </c>
       <c r="W76">
-        <v>0.2036327474240082</v>
+        <v>0.1886327474240082</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7563,7 +7563,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.3861786209958422</v>
+        <v>0.4150266255523045</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7574,13 +7574,13 @@
         <v>0.75</v>
       </c>
       <c r="B77">
-        <v>0.1915438146244421</v>
+        <v>0.1801877327286938</v>
       </c>
       <c r="C77">
-        <v>-8388.944191574032</v>
+        <v>-8138.714546272381</v>
       </c>
       <c r="D77">
-        <v>2985.305808425967</v>
+        <v>3235.535453727618</v>
       </c>
       <c r="E77">
         <v>8201.75</v>
@@ -7607,37 +7607,37 @@
         <v>1031.4</v>
       </c>
       <c r="M77">
-        <v>2706.87651</v>
+        <v>2518.72476</v>
       </c>
       <c r="N77">
-        <v>-1675.47651</v>
+        <v>-1487.32476</v>
       </c>
       <c r="O77">
-        <v>-244.61957046</v>
+        <v>-217.14941496</v>
       </c>
       <c r="P77">
-        <v>-1430.85693954</v>
+        <v>-1270.17534504</v>
       </c>
       <c r="Q77">
-        <v>-1091.05693954</v>
+        <v>-930.37534504</v>
       </c>
       <c r="R77">
         <v>3</v>
       </c>
       <c r="S77">
-        <v>0.1547903261227039</v>
+        <v>0.1543659985397108</v>
       </c>
       <c r="T77">
-        <v>2.515479331025283</v>
+        <v>2.507297887753136</v>
       </c>
       <c r="U77">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V77">
-        <v>0.05563031761652105</v>
+        <v>0.05978596883289463</v>
       </c>
       <c r="W77">
-        <v>0.2037949774583548</v>
+        <v>0.1887949774583547</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.3810295727158975</v>
+        <v>0.4094929372116071</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7656,13 +7656,13 @@
         <v>0.76</v>
       </c>
       <c r="B78">
-        <v>0.1932438146244421</v>
+        <v>0.1817377327286938</v>
       </c>
       <c r="C78">
-        <v>-8590.610217176672</v>
+        <v>-8342.853025296488</v>
       </c>
       <c r="D78">
-        <v>2950.885782823326</v>
+        <v>3198.642974703512</v>
       </c>
       <c r="E78">
         <v>8368.995999999999</v>
@@ -7689,37 +7689,37 @@
         <v>1031.4</v>
       </c>
       <c r="M78">
-        <v>2742.9681968</v>
+        <v>2552.3077568</v>
       </c>
       <c r="N78">
-        <v>-1711.5681968</v>
+        <v>-1520.9077568</v>
       </c>
       <c r="O78">
-        <v>-249.8889567328</v>
+        <v>-222.0525324928</v>
       </c>
       <c r="P78">
-        <v>-1461.6792400672</v>
+        <v>-1298.8552243072</v>
       </c>
       <c r="Q78">
-        <v>-1121.8792400672</v>
+        <v>-959.0552243072</v>
       </c>
       <c r="R78">
         <v>3.166666666666667</v>
       </c>
       <c r="S78">
-        <v>0.1593315897111499</v>
+        <v>0.1588895818121988</v>
       </c>
       <c r="T78">
-        <v>2.620290969818003</v>
+        <v>2.611768633076184</v>
       </c>
       <c r="U78">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V78">
-        <v>0.05489833975314577</v>
+        <v>0.05899931134825129</v>
       </c>
       <c r="W78">
-        <v>0.2039529382812712</v>
+        <v>0.1889529382812711</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7727,7 +7727,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.3760160257064779</v>
+        <v>0.4041048722482965</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7738,13 +7738,13 @@
         <v>0.77</v>
       </c>
       <c r="B79">
-        <v>0.194943814624442</v>
+        <v>0.1832877327286938</v>
       </c>
       <c r="C79">
-        <v>-8791.491576735039</v>
+        <v>-8546.159672398539</v>
       </c>
       <c r="D79">
-        <v>2917.250423264959</v>
+        <v>3162.582327601461</v>
       </c>
       <c r="E79">
         <v>8536.241999999998</v>
@@ -7771,37 +7771,37 @@
         <v>1031.4</v>
       </c>
       <c r="M79">
-        <v>2779.0598836</v>
+        <v>2585.8907536</v>
       </c>
       <c r="N79">
-        <v>-1747.6598836</v>
+        <v>-1554.4907536</v>
       </c>
       <c r="O79">
-        <v>-255.1583430056</v>
+        <v>-226.9556500255999</v>
       </c>
       <c r="P79">
-        <v>-1492.5015405944</v>
+        <v>-1327.5351035744</v>
       </c>
       <c r="Q79">
-        <v>-1152.7015405944</v>
+        <v>-987.7351035743998</v>
       </c>
       <c r="R79">
         <v>3.347826086956522</v>
       </c>
       <c r="S79">
-        <v>0.1642677457855477</v>
+        <v>0.1638065201518596</v>
       </c>
       <c r="T79">
-        <v>2.734216664157917</v>
+        <v>2.725323791036018</v>
       </c>
       <c r="U79">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V79">
-        <v>0.05418537430180621</v>
+        <v>0.05823308652554672</v>
       </c>
       <c r="W79">
-        <v>0.2041067962256702</v>
+        <v>0.1891067962256702</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7809,7 +7809,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.3711327006973029</v>
+        <v>0.3988567570242927</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7820,13 +7820,13 @@
         <v>0.78</v>
       </c>
       <c r="B80">
-        <v>0.1966438146244421</v>
+        <v>0.1848377327286937</v>
       </c>
       <c r="C80">
-        <v>-8991.614799655305</v>
+        <v>-8748.662307497354</v>
       </c>
       <c r="D80">
-        <v>2884.373200344697</v>
+        <v>3127.325692502645</v>
       </c>
       <c r="E80">
         <v>8703.488000000001</v>
@@ -7853,37 +7853,37 @@
         <v>1031.4</v>
       </c>
       <c r="M80">
-        <v>2815.1515704</v>
+        <v>2619.4737504</v>
       </c>
       <c r="N80">
-        <v>-1783.7515704</v>
+        <v>-1588.0737504</v>
       </c>
       <c r="O80">
-        <v>-260.4277292784</v>
+        <v>-231.8587675584</v>
       </c>
       <c r="P80">
-        <v>-1523.3238411216</v>
+        <v>-1356.2149828416</v>
       </c>
       <c r="Q80">
-        <v>-1183.5238411216</v>
+        <v>-1016.4149828416</v>
       </c>
       <c r="R80">
         <v>3.545454545454546</v>
       </c>
       <c r="S80">
-        <v>0.1696526433212544</v>
+        <v>0.169170452886035</v>
       </c>
       <c r="T80">
-        <v>2.858499239801458</v>
+        <v>2.849202145174018</v>
       </c>
       <c r="U80">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V80">
-        <v>0.05349069001588562</v>
+        <v>0.05748650849316791</v>
       </c>
       <c r="W80">
-        <v>0.2042567090945719</v>
+        <v>0.1892567090945719</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7891,7 +7891,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.3663745891499015</v>
+        <v>0.3937432088573145</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7902,13 +7902,13 @@
         <v>0.79</v>
       </c>
       <c r="B81">
-        <v>0.1983438146244421</v>
+        <v>0.1863877327286938</v>
       </c>
       <c r="C81">
-        <v>-9191.005232732827</v>
+        <v>-8950.387523637311</v>
       </c>
       <c r="D81">
-        <v>2852.228767267171</v>
+        <v>3092.846476362688</v>
       </c>
       <c r="E81">
         <v>8870.734</v>
@@ -7935,37 +7935,37 @@
         <v>1031.4</v>
       </c>
       <c r="M81">
-        <v>2851.2432572</v>
+        <v>2653.0567472</v>
       </c>
       <c r="N81">
-        <v>-1819.8432572</v>
+        <v>-1621.6567472</v>
       </c>
       <c r="O81">
-        <v>-265.6971155512</v>
+        <v>-236.7618850911999</v>
       </c>
       <c r="P81">
-        <v>-1554.1461416488</v>
+        <v>-1384.8948621088</v>
       </c>
       <c r="Q81">
-        <v>-1214.3461416488</v>
+        <v>-1045.0948621088</v>
       </c>
       <c r="R81">
         <v>3.761904761904763</v>
       </c>
       <c r="S81">
-        <v>0.1755503882413142</v>
+        <v>0.1750452363567986</v>
       </c>
       <c r="T81">
-        <v>2.994618251220576</v>
+        <v>2.984878437801354</v>
       </c>
       <c r="U81">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V81">
-        <v>0.05281359267391238</v>
+        <v>0.05675883117046959</v>
       </c>
       <c r="W81">
-        <v>0.2044028267009697</v>
+        <v>0.1894028267009697</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7973,7 +7973,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.3617369361226875</v>
+        <v>0.3887591176059562</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7984,13 +7984,13 @@
         <v>0.8</v>
       </c>
       <c r="B82">
-        <v>0.200043814624442</v>
+        <v>0.1879377327286938</v>
       </c>
       <c r="C82">
-        <v>-9389.687105322992</v>
+        <v>-9151.360753883151</v>
       </c>
       <c r="D82">
-        <v>2820.792894677009</v>
+        <v>3059.119246116849</v>
       </c>
       <c r="E82">
         <v>9037.98</v>
@@ -8017,37 +8017,37 @@
         <v>1031.4</v>
       </c>
       <c r="M82">
-        <v>2887.334944</v>
+        <v>2686.639744</v>
       </c>
       <c r="N82">
-        <v>-1855.934944</v>
+        <v>-1655.239744</v>
       </c>
       <c r="O82">
-        <v>-270.966501824</v>
+        <v>-241.665002624</v>
       </c>
       <c r="P82">
-        <v>-1584.968442176</v>
+        <v>-1413.574741376</v>
       </c>
       <c r="Q82">
-        <v>-1245.168442176</v>
+        <v>-1073.774741376</v>
       </c>
       <c r="R82">
         <v>4.000000000000001</v>
       </c>
       <c r="S82">
-        <v>0.1820379076533798</v>
+        <v>0.1815074981746386</v>
       </c>
       <c r="T82">
-        <v>3.144349163781604</v>
+        <v>3.134122359691421</v>
       </c>
       <c r="U82">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V82">
-        <v>0.05215342276548847</v>
+        <v>0.05604934578083871</v>
       </c>
       <c r="W82">
-        <v>0.2045452913672076</v>
+        <v>0.1895452913672076</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8055,7 +8055,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.3572152244211539</v>
+        <v>0.3838996286358817</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8066,13 +8066,13 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="B83">
-        <v>0.201743814624442</v>
+        <v>0.1894877327286938</v>
       </c>
       <c r="C83">
-        <v>-9587.683590249238</v>
+        <v>-9351.606333885113</v>
       </c>
       <c r="D83">
-        <v>2790.042409750762</v>
+        <v>3026.119666114886</v>
       </c>
       <c r="E83">
         <v>9205.225999999999</v>
@@ -8099,37 +8099,37 @@
         <v>1031.4</v>
       </c>
       <c r="M83">
-        <v>2923.4266308</v>
+        <v>2720.2227408</v>
       </c>
       <c r="N83">
-        <v>-1892.0266308</v>
+        <v>-1688.8227408</v>
       </c>
       <c r="O83">
-        <v>-276.2358880968</v>
+        <v>-246.5681201567999</v>
       </c>
       <c r="P83">
-        <v>-1615.7907427032</v>
+        <v>-1442.2546206432</v>
       </c>
       <c r="Q83">
-        <v>-1275.9907427032</v>
+        <v>-1102.4546206432</v>
       </c>
       <c r="R83">
         <v>4.263157894736843</v>
       </c>
       <c r="S83">
-        <v>0.189208323845663</v>
+        <v>0.1886499980785669</v>
       </c>
       <c r="T83">
-        <v>3.309841225033268</v>
+        <v>3.299076168096233</v>
       </c>
       <c r="U83">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V83">
-        <v>0.0515095533486306</v>
+        <v>0.05535737854897651</v>
       </c>
       <c r="W83">
-        <v>0.2046842383873655</v>
+        <v>0.1896842383873655</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8137,7 +8137,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.3528051599221274</v>
+        <v>0.3791601270477843</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8148,13 +8148,13 @@
         <v>0.8200000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2034438146244421</v>
+        <v>0.1910377327286938</v>
       </c>
       <c r="C84">
-        <v>-9785.016860770293</v>
+        <v>-9551.147560437843</v>
       </c>
       <c r="D84">
-        <v>2759.955139229708</v>
+        <v>2993.824439562157</v>
       </c>
       <c r="E84">
         <v>9372.472000000002</v>
@@ -8181,37 +8181,37 @@
         <v>1031.4</v>
       </c>
       <c r="M84">
-        <v>2959.518317600001</v>
+        <v>2753.8057376</v>
       </c>
       <c r="N84">
-        <v>-1928.1183176</v>
+        <v>-1722.4057376</v>
       </c>
       <c r="O84">
-        <v>-281.5052743696</v>
+        <v>-251.4712376896</v>
       </c>
       <c r="P84">
-        <v>-1646.6130432304</v>
+        <v>-1470.9344999104</v>
       </c>
       <c r="Q84">
-        <v>-1306.8130432304</v>
+        <v>-1131.1344999104</v>
       </c>
       <c r="R84">
         <v>4.555555555555557</v>
       </c>
       <c r="S84">
-        <v>0.1971754529481999</v>
+        <v>0.1965861090829318</v>
       </c>
       <c r="T84">
-        <v>3.493721293090672</v>
+        <v>3.482358177434913</v>
       </c>
       <c r="U84">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V84">
-        <v>0.05088138806389119</v>
+        <v>0.05468228856667191</v>
       </c>
       <c r="W84">
-        <v>0.2048197964558123</v>
+        <v>0.1898197964558123</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8219,7 +8219,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.3485026579718575</v>
+        <v>0.3745362230593967</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8230,13 +8230,13 @@
         <v>0.8300000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2051438146244421</v>
+        <v>0.1925877327286938</v>
       </c>
       <c r="C85">
-        <v>-9981.708143900665</v>
+        <v>-9750.006746329189</v>
       </c>
       <c r="D85">
-        <v>2730.509856099336</v>
+        <v>2962.211253670811</v>
       </c>
       <c r="E85">
         <v>9539.718000000001</v>
@@ -8263,37 +8263,37 @@
         <v>1031.4</v>
       </c>
       <c r="M85">
-        <v>2995.6100044</v>
+        <v>2787.3887344</v>
       </c>
       <c r="N85">
-        <v>-1964.2100044</v>
+        <v>-1755.9887344</v>
       </c>
       <c r="O85">
-        <v>-286.7746606424</v>
+        <v>-256.3743552224</v>
       </c>
       <c r="P85">
-        <v>-1677.4353437576</v>
+        <v>-1499.6143791776</v>
       </c>
       <c r="Q85">
-        <v>-1337.6353437576</v>
+        <v>-1159.8143791776</v>
       </c>
       <c r="R85">
         <v>4.882352941176473</v>
       </c>
       <c r="S85">
-        <v>0.2060798913569175</v>
+        <v>0.2054558802054571</v>
       </c>
       <c r="T85">
-        <v>3.6992343103313</v>
+        <v>3.687202776107554</v>
       </c>
       <c r="U85">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V85">
-        <v>0.05026835929203709</v>
+        <v>0.05402346581285659</v>
       </c>
       <c r="W85">
-        <v>0.2049520880647784</v>
+        <v>0.1899520880647784</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8301,7 +8301,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.3443038307673774</v>
+        <v>0.3700237384442233</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8312,13 +8312,13 @@
         <v>0.84</v>
       </c>
       <c r="B86">
-        <v>0.206843814624442</v>
+        <v>0.1941377327286938</v>
       </c>
       <c r="C86">
-        <v>-10177.77777035409</v>
+        <v>-9948.205271750265</v>
       </c>
       <c r="D86">
-        <v>2701.686229645914</v>
+        <v>2931.258728249734</v>
       </c>
       <c r="E86">
         <v>9706.964</v>
@@ -8345,37 +8345,37 @@
         <v>1031.4</v>
       </c>
       <c r="M86">
-        <v>3031.7016912</v>
+        <v>2820.9717312</v>
       </c>
       <c r="N86">
-        <v>-2000.3016912</v>
+        <v>-1789.5717312</v>
       </c>
       <c r="O86">
-        <v>-292.0440469151999</v>
+        <v>-261.2774727551999</v>
       </c>
       <c r="P86">
-        <v>-1708.2576442848</v>
+        <v>-1528.2942584448</v>
       </c>
       <c r="Q86">
-        <v>-1368.4576442848</v>
+        <v>-1188.4942584448</v>
       </c>
       <c r="R86">
         <v>5.249999999999999</v>
       </c>
       <c r="S86">
-        <v>0.2160973845667248</v>
+        <v>0.2154343727182981</v>
       </c>
       <c r="T86">
-        <v>3.930436454727004</v>
+        <v>3.917652949614275</v>
       </c>
       <c r="U86">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V86">
-        <v>0.04966992644332236</v>
+        <v>0.0533803293150845</v>
       </c>
       <c r="W86">
-        <v>0.2050812298735311</v>
+        <v>0.190081229873531</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8383,7 +8383,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.3402049756391943</v>
+        <v>0.3656186939389349</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8394,13 +8394,13 @@
         <v>0.85</v>
       </c>
       <c r="B87">
-        <v>0.208543814624442</v>
+        <v>0.1956877327286938</v>
       </c>
       <c r="C87">
-        <v>-10373.24522135668</v>
+        <v>-10145.76363251571</v>
       </c>
       <c r="D87">
-        <v>2673.464778643323</v>
+        <v>2900.946367484288</v>
       </c>
       <c r="E87">
         <v>9874.209999999999</v>
@@ -8427,37 +8427,37 @@
         <v>1031.4</v>
       </c>
       <c r="M87">
-        <v>3067.793378</v>
+        <v>2854.554728</v>
       </c>
       <c r="N87">
-        <v>-2036.393378</v>
+        <v>-1823.154728</v>
       </c>
       <c r="O87">
-        <v>-297.3134331879999</v>
+        <v>-266.1805902879999</v>
       </c>
       <c r="P87">
-        <v>-1739.079944812</v>
+        <v>-1556.974137712</v>
       </c>
       <c r="Q87">
-        <v>-1399.279944812</v>
+        <v>-1217.174137712</v>
       </c>
       <c r="R87">
         <v>5.666666666666666</v>
       </c>
       <c r="S87">
-        <v>0.2274505435378397</v>
+        <v>0.226743330899518</v>
       </c>
       <c r="T87">
-        <v>4.192465551708804</v>
+        <v>4.178829812921894</v>
       </c>
       <c r="U87">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V87">
-        <v>0.04908557436751857</v>
+        <v>0.05275232544078939</v>
       </c>
       <c r="W87">
-        <v>0.2052073330514895</v>
+        <v>0.1902073330514895</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8465,7 +8465,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.3362025641610861</v>
+        <v>0.3613172975396534</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8476,13 +8476,13 @@
         <v>0.86</v>
       </c>
       <c r="B88">
-        <v>0.210243814624442</v>
+        <v>0.1972377327286938</v>
       </c>
       <c r="C88">
-        <v>-10568.12917255644</v>
+        <v>-10342.70148532268</v>
       </c>
       <c r="D88">
-        <v>2645.826827443559</v>
+        <v>2871.254514677324</v>
       </c>
       <c r="E88">
         <v>10041.456</v>
@@ -8509,37 +8509,37 @@
         <v>1031.4</v>
       </c>
       <c r="M88">
-        <v>3103.8850648</v>
+        <v>2888.1377248</v>
       </c>
       <c r="N88">
-        <v>-2072.4850648</v>
+        <v>-1856.7377248</v>
       </c>
       <c r="O88">
-        <v>-302.5828194608</v>
+        <v>-271.0837078207999</v>
       </c>
       <c r="P88">
-        <v>-1769.9022453392</v>
+        <v>-1585.6540169792</v>
       </c>
       <c r="Q88">
-        <v>-1430.1022453392</v>
+        <v>-1245.8540169792</v>
       </c>
       <c r="R88">
         <v>6.142857142857142</v>
       </c>
       <c r="S88">
-        <v>0.2404255823619712</v>
+        <v>0.2396678545351979</v>
       </c>
       <c r="T88">
-        <v>4.491927376830862</v>
+        <v>4.477317656702029</v>
       </c>
       <c r="U88">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V88">
-        <v>0.048514811874873</v>
+        <v>0.05213892630775695</v>
       </c>
       <c r="W88">
-        <v>0.2053305035974024</v>
+        <v>0.1903305035974024</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8547,7 +8547,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.3322932320196781</v>
+        <v>0.3571159336147737</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8558,13 +8558,13 @@
         <v>0.87</v>
       </c>
       <c r="B89">
-        <v>0.211943814624442</v>
+        <v>0.1987877327286938</v>
       </c>
       <c r="C89">
-        <v>-10762.44753523705</v>
+        <v>-10539.03769025853</v>
       </c>
       <c r="D89">
-        <v>2618.754464762943</v>
+        <v>2842.164309741466</v>
       </c>
       <c r="E89">
         <v>10208.702</v>
@@ -8591,37 +8591,37 @@
         <v>1031.4</v>
       </c>
       <c r="M89">
-        <v>3139.9767516</v>
+        <v>2921.7207216</v>
       </c>
       <c r="N89">
-        <v>-2108.5767516</v>
+        <v>-1890.3207216</v>
       </c>
       <c r="O89">
-        <v>-307.8522057335999</v>
+        <v>-275.9868253536</v>
       </c>
       <c r="P89">
-        <v>-1800.7245458664</v>
+        <v>-1614.3338962464</v>
       </c>
       <c r="Q89">
-        <v>-1460.9245458664</v>
+        <v>-1274.5338962464</v>
       </c>
       <c r="R89">
         <v>6.692307692307692</v>
       </c>
       <c r="S89">
-        <v>0.2553967810051997</v>
+        <v>0.2545807664225208</v>
       </c>
       <c r="T89">
-        <v>4.837460251971697</v>
+        <v>4.821726707217569</v>
       </c>
       <c r="U89">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V89">
-        <v>0.04795717035906987</v>
+        <v>0.05153962830421951</v>
       </c>
       <c r="W89">
-        <v>0.2054508426365127</v>
+        <v>0.1904508426365127</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8629,7 +8629,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.3284737695826704</v>
+        <v>0.3530111527686268</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8640,13 +8640,13 @@
         <v>0.88</v>
       </c>
       <c r="B90">
-        <v>0.2136438146244421</v>
+        <v>0.2003377327286938</v>
       </c>
       <c r="C90">
-        <v>-10956.21749502705</v>
+        <v>-10734.79035075053</v>
       </c>
       <c r="D90">
-        <v>2592.230504972954</v>
+        <v>2813.657649249473</v>
       </c>
       <c r="E90">
         <v>10375.948</v>
@@ -8673,37 +8673,37 @@
         <v>1031.4</v>
       </c>
       <c r="M90">
-        <v>3176.0684384</v>
+        <v>2955.3037184</v>
       </c>
       <c r="N90">
-        <v>-2144.6684384</v>
+        <v>-1923.9037184</v>
       </c>
       <c r="O90">
-        <v>-313.1215920064</v>
+        <v>-280.8899428864</v>
       </c>
       <c r="P90">
-        <v>-1831.5468463936</v>
+        <v>-1643.0137755136</v>
       </c>
       <c r="Q90">
-        <v>-1491.7468463936</v>
+        <v>-1303.2137755136</v>
       </c>
       <c r="R90">
         <v>7.333333333333334</v>
       </c>
       <c r="S90">
-        <v>0.2728631794222998</v>
+        <v>0.2719791636243975</v>
       </c>
       <c r="T90">
-        <v>5.240581939636007</v>
+        <v>5.223537266152367</v>
       </c>
       <c r="U90">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V90">
-        <v>0.04741220251408043</v>
+        <v>0.05095395070985338</v>
       </c>
       <c r="W90">
-        <v>0.2055684466974615</v>
+        <v>0.1905684466974615</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8711,7 +8711,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.32474111311014</v>
+        <v>0.348999662396256</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8722,13 +8722,13 @@
         <v>0.89</v>
       </c>
       <c r="B91">
-        <v>0.215343814624442</v>
+        <v>0.2018877327286938</v>
       </c>
       <c r="C91">
-        <v>-11149.45554828016</v>
+        <v>-10929.97685113512</v>
       </c>
       <c r="D91">
-        <v>2566.238451719843</v>
+        <v>2785.717148864876</v>
       </c>
       <c r="E91">
         <v>10543.194</v>
@@ -8755,37 +8755,37 @@
         <v>1031.4</v>
       </c>
       <c r="M91">
-        <v>3212.1601252</v>
+        <v>2988.8867152</v>
       </c>
       <c r="N91">
-        <v>-2180.7601252</v>
+        <v>-1957.4867152</v>
       </c>
       <c r="O91">
-        <v>-318.3909782792</v>
+        <v>-285.7930604191999</v>
       </c>
       <c r="P91">
-        <v>-1862.3691469208</v>
+        <v>-1671.6936547808</v>
       </c>
       <c r="Q91">
-        <v>-1522.5691469208</v>
+        <v>-1331.8936547808</v>
       </c>
       <c r="R91">
         <v>8.090909090909092</v>
       </c>
       <c r="S91">
-        <v>0.2935052866425088</v>
+        <v>0.2925409057720701</v>
       </c>
       <c r="T91">
-        <v>5.716998479602916</v>
+        <v>5.698404290348038</v>
       </c>
       <c r="U91">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V91">
-        <v>0.04687948113751773</v>
+        <v>0.05038143440974267</v>
       </c>
       <c r="W91">
-        <v>0.2056834079705237</v>
+        <v>0.1906834079705237</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8793,7 +8793,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.3210923365583407</v>
+        <v>0.3450783178749498</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8804,13 +8804,13 @@
         <v>0.9</v>
       </c>
       <c r="B92">
-        <v>0.2170438146244421</v>
+        <v>0.2034377327286938</v>
       </c>
       <c r="C92">
-        <v>-11342.17753628878</v>
+        <v>-11124.61389201092</v>
       </c>
       <c r="D92">
-        <v>2540.762463711217</v>
+        <v>2758.326107989075</v>
       </c>
       <c r="E92">
         <v>10710.44</v>
@@ -8837,37 +8837,37 @@
         <v>1031.4</v>
       </c>
       <c r="M92">
-        <v>3248.251812</v>
+        <v>3022.469712</v>
       </c>
       <c r="N92">
-        <v>-2216.851812</v>
+        <v>-1991.069712</v>
       </c>
       <c r="O92">
-        <v>-323.660364552</v>
+        <v>-290.696177952</v>
       </c>
       <c r="P92">
-        <v>-1893.191447448</v>
+        <v>-1700.373534048</v>
       </c>
       <c r="Q92">
-        <v>-1553.391447448</v>
+        <v>-1360.573534048</v>
       </c>
       <c r="R92">
         <v>9.000000000000002</v>
       </c>
       <c r="S92">
-        <v>0.3182758153067597</v>
+        <v>0.317214996349277</v>
       </c>
       <c r="T92">
-        <v>6.288698327563208</v>
+        <v>6.268244719382841</v>
       </c>
       <c r="U92">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V92">
-        <v>0.04635859801376754</v>
+        <v>0.04982164069407886</v>
       </c>
       <c r="W92">
-        <v>0.205795814548629</v>
+        <v>0.190795814548629</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8875,7 +8875,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.3175246439299146</v>
+        <v>0.3412441143430058</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8886,13 +8886,13 @@
         <v>0.91</v>
       </c>
       <c r="B93">
-        <v>0.218743814624442</v>
+        <v>0.2049877327286938</v>
       </c>
       <c r="C93">
-        <v>-11534.39867747952</v>
+        <v>-11318.71752352622</v>
       </c>
       <c r="D93">
-        <v>2515.787322520484</v>
+        <v>2731.468476473776</v>
       </c>
       <c r="E93">
         <v>10877.686</v>
@@ -8919,37 +8919,37 @@
         <v>1031.4</v>
       </c>
       <c r="M93">
-        <v>3284.3434988</v>
+        <v>3056.0527088</v>
       </c>
       <c r="N93">
-        <v>-2252.9434988</v>
+        <v>-2024.6527088</v>
       </c>
       <c r="O93">
-        <v>-328.9297508248</v>
+        <v>-295.5992954847999</v>
       </c>
       <c r="P93">
-        <v>-1924.0137479752</v>
+        <v>-1729.0534133152</v>
       </c>
       <c r="Q93">
-        <v>-1584.2137479752</v>
+        <v>-1389.2534133152</v>
       </c>
       <c r="R93">
         <v>10.11111111111111</v>
       </c>
       <c r="S93">
-        <v>0.3485509058963997</v>
+        <v>0.3473722181658634</v>
       </c>
       <c r="T93">
-        <v>6.987442586181343</v>
+        <v>6.964716354869824</v>
       </c>
       <c r="U93">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V93">
-        <v>0.0458491628707591</v>
+        <v>0.04927415013700107</v>
       </c>
       <c r="W93">
-        <v>0.2059057506524902</v>
+        <v>0.1909057506524902</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8957,7 +8957,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.314035362128487</v>
+        <v>0.3374941790205553</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8968,13 +8968,13 @@
         <v>0.92</v>
       </c>
       <c r="B94">
-        <v>0.220443814624442</v>
+        <v>0.2065377327286938</v>
       </c>
       <c r="C94">
-        <v>-11726.13359772832</v>
+        <v>-11512.30317674057</v>
       </c>
       <c r="D94">
-        <v>2491.298402271684</v>
+        <v>2705.128823259429</v>
       </c>
       <c r="E94">
         <v>11044.932</v>
@@ -9001,37 +9001,37 @@
         <v>1031.4</v>
       </c>
       <c r="M94">
-        <v>3320.4351856</v>
+        <v>3089.6357056</v>
       </c>
       <c r="N94">
-        <v>-2289.0351856</v>
+        <v>-2058.2357056</v>
       </c>
       <c r="O94">
-        <v>-334.1991370976</v>
+        <v>-300.5024130176</v>
       </c>
       <c r="P94">
-        <v>-1954.8360485024</v>
+        <v>-1757.7332925824</v>
       </c>
       <c r="Q94">
-        <v>-1615.0360485024</v>
+        <v>-1417.9332925824</v>
       </c>
       <c r="R94">
         <v>11.50000000000001</v>
       </c>
       <c r="S94">
-        <v>0.3863947691334498</v>
+        <v>0.3850687454365965</v>
       </c>
       <c r="T94">
-        <v>7.860872909454013</v>
+        <v>7.835305899228555</v>
       </c>
       <c r="U94">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V94">
-        <v>0.04535080240477259</v>
+        <v>0.0487385615485554</v>
       </c>
       <c r="W94">
-        <v>0.2060132968410501</v>
+        <v>0.1910132968410501</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9039,7 +9039,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.3106219342792643</v>
+        <v>0.3338257640312013</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9050,13 +9050,13 @@
         <v>0.93</v>
       </c>
       <c r="B95">
-        <v>0.222143814624442</v>
+        <v>0.2080877327286938</v>
       </c>
       <c r="C95">
-        <v>-11917.39635892225</v>
+        <v>-11705.38569318918</v>
       </c>
       <c r="D95">
-        <v>2467.281641077751</v>
+        <v>2679.292306810822</v>
       </c>
       <c r="E95">
         <v>11212.178</v>
@@ -9083,37 +9083,37 @@
         <v>1031.4</v>
       </c>
       <c r="M95">
-        <v>3356.5268724</v>
+        <v>3123.2187024</v>
       </c>
       <c r="N95">
-        <v>-2325.1268724</v>
+        <v>-2091.8187024</v>
       </c>
       <c r="O95">
-        <v>-339.4685233704</v>
+        <v>-305.4055305504</v>
       </c>
       <c r="P95">
-        <v>-1985.6583490296</v>
+        <v>-1786.4131718496</v>
       </c>
       <c r="Q95">
-        <v>-1645.8583490296</v>
+        <v>-1446.6131718496</v>
       </c>
       <c r="R95">
         <v>13.2857142857143</v>
       </c>
       <c r="S95">
-        <v>0.4350511647239427</v>
+        <v>0.433535709070396</v>
       </c>
       <c r="T95">
-        <v>8.983854753661731</v>
+        <v>8.954635313404063</v>
       </c>
       <c r="U95">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V95">
-        <v>0.04486315936816213</v>
+        <v>0.04821449099426986</v>
       </c>
       <c r="W95">
-        <v>0.2061185302083506</v>
+        <v>0.1911185302083506</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9121,7 +9121,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.3072819134805626</v>
+        <v>0.33023623968678</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9132,13 +9132,13 @@
         <v>0.9400000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2238438146244421</v>
+        <v>0.2096377327286938</v>
       </c>
       <c r="C96">
-        <v>-12108.20048588487</v>
+        <v>-11897.97935276912</v>
       </c>
       <c r="D96">
-        <v>2443.723514115127</v>
+        <v>2653.944647230876</v>
       </c>
       <c r="E96">
         <v>11379.424</v>
@@ -9165,37 +9165,37 @@
         <v>1031.4</v>
       </c>
       <c r="M96">
-        <v>3392.6185592</v>
+        <v>3156.8016992</v>
       </c>
       <c r="N96">
-        <v>-2361.2185592</v>
+        <v>-2125.4016992</v>
       </c>
       <c r="O96">
-        <v>-344.7379096432</v>
+        <v>-310.3086480832</v>
       </c>
       <c r="P96">
-        <v>-2016.4806495568</v>
+        <v>-1815.0930511168</v>
       </c>
       <c r="Q96">
-        <v>-1676.6806495568</v>
+        <v>-1475.2930511168</v>
       </c>
       <c r="R96">
         <v>15.66666666666668</v>
       </c>
       <c r="S96">
-        <v>0.4999263588445998</v>
+        <v>0.4981583272487954</v>
       </c>
       <c r="T96">
-        <v>10.48116387927202</v>
+        <v>10.44707453230474</v>
       </c>
       <c r="U96">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V96">
-        <v>0.04438589171530934</v>
+        <v>0.04770157087730954</v>
       </c>
       <c r="W96">
-        <v>0.2062215245678363</v>
+        <v>0.1912215245678363</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9203,7 +9203,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.3040129569541736</v>
+        <v>0.3267230882007502</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9214,13 +9214,13 @@
         <v>0.9500000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2255438146244421</v>
+        <v>0.2111877327286938</v>
       </c>
       <c r="C97">
-        <v>-12298.55899177374</v>
+        <v>-12090.09790005747</v>
       </c>
       <c r="D97">
-        <v>2420.611008226257</v>
+        <v>2629.072099942524</v>
       </c>
       <c r="E97">
         <v>11546.67</v>
@@ -9247,37 +9247,37 @@
         <v>1031.4</v>
       </c>
       <c r="M97">
-        <v>3428.710246</v>
+        <v>3190.384696</v>
       </c>
       <c r="N97">
-        <v>-2397.310246</v>
+        <v>-2158.984696</v>
       </c>
       <c r="O97">
-        <v>-350.007295916</v>
+        <v>-315.211765616</v>
       </c>
       <c r="P97">
-        <v>-2047.302950084</v>
+        <v>-1843.772930384</v>
       </c>
       <c r="Q97">
-        <v>-1707.502950084</v>
+        <v>-1503.972930384</v>
       </c>
       <c r="R97">
         <v>19.00000000000003</v>
       </c>
       <c r="S97">
-        <v>0.5907516306135201</v>
+        <v>0.5886299926985549</v>
       </c>
       <c r="T97">
-        <v>12.57739665512643</v>
+        <v>12.5364894387657</v>
       </c>
       <c r="U97">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V97">
-        <v>0.04391867180251662</v>
+        <v>0.04719944907860102</v>
       </c>
       <c r="W97">
-        <v>0.2063223506250169</v>
+        <v>0.1913223506250169</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9285,7 +9285,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.3008128205651823</v>
+        <v>0.3232838977986372</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9296,13 +9296,13 @@
         <v>0.96</v>
       </c>
       <c r="B98">
-        <v>0.2272438146244421</v>
+        <v>0.2127377327286938</v>
       </c>
       <c r="C98">
-        <v>-12488.48440205015</v>
+        <v>-12281.75456916326</v>
       </c>
       <c r="D98">
-        <v>2397.931597949848</v>
+        <v>2604.661430836734</v>
       </c>
       <c r="E98">
         <v>11713.916</v>
@@ -9329,37 +9329,37 @@
         <v>1031.4</v>
       </c>
       <c r="M98">
-        <v>3464.8019328</v>
+        <v>3223.9676928</v>
       </c>
       <c r="N98">
-        <v>-2433.4019328</v>
+        <v>-2192.5676928</v>
       </c>
       <c r="O98">
-        <v>-355.2766821888</v>
+        <v>-320.1148831487999</v>
       </c>
       <c r="P98">
-        <v>-2078.1252506112</v>
+        <v>-1872.4528096512</v>
       </c>
       <c r="Q98">
-        <v>-1738.3252506112</v>
+        <v>-1532.6528096512</v>
       </c>
       <c r="R98">
         <v>23.99999999999998</v>
       </c>
       <c r="S98">
-        <v>0.7269895382668985</v>
+        <v>0.7243374908731919</v>
       </c>
       <c r="T98">
-        <v>15.721745818908</v>
+        <v>15.67061179845709</v>
       </c>
       <c r="U98">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V98">
-        <v>0.04346118563790707</v>
+        <v>0.04670778815069893</v>
       </c>
       <c r="W98">
-        <v>0.2064210761393397</v>
+        <v>0.1914210761393396</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9367,7 +9367,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.297679353684295</v>
+        <v>0.3199163571965681</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9378,13 +9378,13 @@
         <v>0.97</v>
       </c>
       <c r="B99">
-        <v>0.228943814624442</v>
+        <v>0.2142877327286938</v>
       </c>
       <c r="C99">
-        <v>-12677.98877711389</v>
+        <v>-12472.96210720768</v>
       </c>
       <c r="D99">
-        <v>2375.673222886108</v>
+        <v>2580.699892792314</v>
       </c>
       <c r="E99">
         <v>11881.162</v>
@@ -9411,37 +9411,37 @@
         <v>1031.4</v>
       </c>
       <c r="M99">
-        <v>3500.8936196</v>
+        <v>3257.5506896</v>
       </c>
       <c r="N99">
-        <v>-2469.4936196</v>
+        <v>-2226.1506896</v>
       </c>
       <c r="O99">
-        <v>-360.5460684616</v>
+        <v>-325.0180006815999</v>
       </c>
       <c r="P99">
-        <v>-2108.9475511384</v>
+        <v>-1901.1326889184</v>
       </c>
       <c r="Q99">
-        <v>-1769.1475511384</v>
+        <v>-1561.3326889184</v>
       </c>
       <c r="R99">
         <v>32.33333333333331</v>
       </c>
       <c r="S99">
-        <v>0.9540527176891981</v>
+        <v>0.9505166544975893</v>
       </c>
       <c r="T99">
-        <v>20.96232775854401</v>
+        <v>20.89414906460945</v>
       </c>
       <c r="U99">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V99">
-        <v>0.04301313217772246</v>
+        <v>0.04622626456151648</v>
       </c>
       <c r="W99">
-        <v>0.2065177660760475</v>
+        <v>0.1915177660760475</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9449,7 +9449,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.2946104943679621</v>
+        <v>0.3166182504213457</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9460,13 +9460,13 @@
         <v>0.98</v>
       </c>
       <c r="B100">
-        <v>0.2306438146244421</v>
+        <v>0.2158377327286937</v>
       </c>
       <c r="C100">
-        <v>-12867.083733689</v>
+        <v>-12663.73279652009</v>
       </c>
       <c r="D100">
-        <v>2353.824266311001</v>
+        <v>2557.175203479909</v>
       </c>
       <c r="E100">
         <v>12048.408</v>
@@ -9493,37 +9493,37 @@
         <v>1031.4</v>
       </c>
       <c r="M100">
-        <v>3536.985306399999</v>
+        <v>3291.1336864</v>
       </c>
       <c r="N100">
-        <v>-2505.585306399999</v>
+        <v>-2259.733686399999</v>
       </c>
       <c r="O100">
-        <v>-365.8154547343999</v>
+        <v>-329.9211182143999</v>
       </c>
       <c r="P100">
-        <v>-2139.7698516656</v>
+        <v>-1929.8125681856</v>
       </c>
       <c r="Q100">
-        <v>-1799.9698516656</v>
+        <v>-1590.0125681856</v>
       </c>
       <c r="R100">
         <v>48.99999999999996</v>
       </c>
       <c r="S100">
-        <v>1.408179076533797</v>
+        <v>1.402874981746384</v>
       </c>
       <c r="T100">
-        <v>31.44349163781601</v>
+        <v>31.34122359691417</v>
       </c>
       <c r="U100">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V100">
-        <v>0.04257422266570489</v>
+        <v>0.04575456798435814</v>
       </c>
       <c r="W100">
-        <v>0.2066124827487409</v>
+        <v>0.1916124827487409</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9531,7 +9531,7 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.2916042648335951</v>
+        <v>0.3133874519476585</v>
       </c>
       <c r="Z100">
         <v>0</v>
@@ -9542,13 +9542,13 @@
         <v>0.99</v>
       </c>
       <c r="B101">
-        <v>0.232343814624442</v>
+        <v>0.2173877327286937</v>
       </c>
       <c r="C101">
-        <v>-13055.78046504015</v>
+        <v>-12854.07847563095</v>
       </c>
       <c r="D101">
-        <v>2332.373534959846</v>
+        <v>2534.075524369044</v>
       </c>
       <c r="E101">
         <v>12215.654</v>
@@ -9575,37 +9575,37 @@
         <v>1031.4</v>
       </c>
       <c r="M101">
-        <v>3573.0769932</v>
+        <v>3324.7166832</v>
       </c>
       <c r="N101">
-        <v>-2541.6769932</v>
+        <v>-2293.3166832</v>
       </c>
       <c r="O101">
-        <v>-371.0848410072</v>
+        <v>-334.8242357472</v>
       </c>
       <c r="P101">
-        <v>-2170.5921521928</v>
+        <v>-1958.4924474528</v>
       </c>
       <c r="Q101">
-        <v>-1830.7921521928</v>
+        <v>-1618.6924474528</v>
       </c>
       <c r="R101">
         <v>98.99999999999991</v>
       </c>
       <c r="S101">
-        <v>2.770558153067594</v>
+        <v>2.759949963492768</v>
       </c>
       <c r="T101">
-        <v>62.88698327563202</v>
+        <v>62.68244719382835</v>
       </c>
       <c r="U101">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V101">
-        <v>0.04214418001251594</v>
+        <v>0.04529240063098079</v>
       </c>
       <c r="W101">
-        <v>0.2067052859532991</v>
+        <v>0.1917052859532991</v>
       </c>
       <c r="X101" t="inlineStr">
         <is>
@@ -9613,7 +9613,7 @@
         </is>
       </c>
       <c r="Y101">
-        <v>0.2886587672090133</v>
+        <v>0.3102219221300053</v>
       </c>
       <c r="Z101">
         <v>0</v>

--- a/research/traditional_assets/database/data/switzerland/switzerland_beverage_soft.xlsx
+++ b/research/traditional_assets/database/data/switzerland/switzerland_beverage_soft.xlsx
@@ -1284,7 +1284,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1421,22 +1421,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.07421564215721098</v>
+        <v>0.07414571731966144</v>
       </c>
       <c r="C2">
-        <v>16471.20413505058</v>
+        <v>16341.70599449825</v>
       </c>
       <c r="D2">
-        <v>15302.00413505058</v>
+        <v>15339.75199449825</v>
       </c>
       <c r="E2">
-        <v>-4341.7</v>
+        <v>-4174.454</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>167.246</v>
       </c>
       <c r="G2">
         <v>1169.2</v>
@@ -1457,28 +1457,28 @@
         <v>1031.4</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>8.412473799999999</v>
       </c>
       <c r="N2">
-        <v>1031.4</v>
+        <v>1022.9875262</v>
       </c>
       <c r="O2">
-        <v>150.5844</v>
+        <v>149.3561788252</v>
       </c>
       <c r="P2">
-        <v>880.8156000000001</v>
+        <v>873.6313473748</v>
       </c>
       <c r="Q2">
-        <v>1220.6156</v>
+        <v>1213.4313473748</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.07421564215721098</v>
+        <v>0.07446076294915298</v>
       </c>
       <c r="T2">
-        <v>0.6562503962404382</v>
+        <v>0.6619113845069972</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1495,7 +1495,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>122.6036507834354</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1503,22 +1503,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.07414571731966144</v>
+        <v>0.07407579248211192</v>
       </c>
       <c r="C3">
-        <v>16341.70599449825</v>
+        <v>16212.39455166207</v>
       </c>
       <c r="D3">
-        <v>15339.75199449825</v>
+        <v>15377.68655166207</v>
       </c>
       <c r="E3">
-        <v>-4174.454</v>
+        <v>-4007.208</v>
       </c>
       <c r="F3">
-        <v>167.246</v>
+        <v>334.492</v>
       </c>
       <c r="G3">
         <v>1169.2</v>
@@ -1539,28 +1539,28 @@
         <v>1031.4</v>
       </c>
       <c r="M3">
-        <v>8.412473799999999</v>
+        <v>16.8249476</v>
       </c>
       <c r="N3">
-        <v>1022.9875262</v>
+        <v>1014.5750524</v>
       </c>
       <c r="O3">
-        <v>149.3561788252</v>
+        <v>148.1279576504</v>
       </c>
       <c r="P3">
-        <v>873.6313473748</v>
+        <v>866.4470947496001</v>
       </c>
       <c r="Q3">
-        <v>1213.4313473748</v>
+        <v>1206.2470947496</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.07446076294915298</v>
+        <v>0.07471088620623666</v>
       </c>
       <c r="T3">
-        <v>0.6619113845069972</v>
+        <v>0.667687903146343</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>122.6036507834354</v>
+        <v>61.30182539171773</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1585,22 +1585,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.07407579248211192</v>
+        <v>0.07400586764456239</v>
       </c>
       <c r="C4">
-        <v>16212.39455166207</v>
+        <v>16083.27119506247</v>
       </c>
       <c r="D4">
-        <v>15377.68655166207</v>
+        <v>15415.80919506247</v>
       </c>
       <c r="E4">
-        <v>-4007.208</v>
+        <v>-3839.962</v>
       </c>
       <c r="F4">
-        <v>334.492</v>
+        <v>501.7379999999999</v>
       </c>
       <c r="G4">
         <v>1169.2</v>
@@ -1621,28 +1621,28 @@
         <v>1031.4</v>
       </c>
       <c r="M4">
-        <v>16.8249476</v>
+        <v>25.2374214</v>
       </c>
       <c r="N4">
-        <v>1014.5750524</v>
+        <v>1006.1625786</v>
       </c>
       <c r="O4">
-        <v>148.1279576504</v>
+        <v>146.8997364756</v>
       </c>
       <c r="P4">
-        <v>866.4470947496001</v>
+        <v>859.2628421244001</v>
       </c>
       <c r="Q4">
-        <v>1206.2470947496</v>
+        <v>1199.0628421244</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.07471088620623666</v>
+        <v>0.07496616664387876</v>
       </c>
       <c r="T4">
-        <v>0.667687903146343</v>
+        <v>0.6735835252627888</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>61.30182539171773</v>
+        <v>40.86788359447849</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1667,22 +1667,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.07400586764456239</v>
+        <v>0.07393594280701286</v>
       </c>
       <c r="C5">
-        <v>16083.27119506247</v>
+        <v>15954.33732702311</v>
       </c>
       <c r="D5">
-        <v>15415.80919506247</v>
+        <v>15454.12132702311</v>
       </c>
       <c r="E5">
-        <v>-3839.962</v>
+        <v>-3672.716</v>
       </c>
       <c r="F5">
-        <v>501.7379999999999</v>
+        <v>668.9839999999999</v>
       </c>
       <c r="G5">
         <v>1169.2</v>
@@ -1703,28 +1703,28 @@
         <v>1031.4</v>
       </c>
       <c r="M5">
-        <v>25.2374214</v>
+        <v>33.6498952</v>
       </c>
       <c r="N5">
-        <v>1006.1625786</v>
+        <v>997.7501048000001</v>
       </c>
       <c r="O5">
-        <v>146.8997364756</v>
+        <v>145.6715153008</v>
       </c>
       <c r="P5">
-        <v>859.2628421244001</v>
+        <v>852.0785894992001</v>
       </c>
       <c r="Q5">
-        <v>1199.0628421244</v>
+        <v>1191.8785894992</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.07496616664387876</v>
+        <v>0.07522676542397173</v>
       </c>
       <c r="T5">
-        <v>0.6735835252627888</v>
+        <v>0.6796019728399938</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>40.86788359447849</v>
+        <v>30.65091269585886</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1749,22 +1749,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.07393594280701286</v>
+        <v>0.07386601796946332</v>
       </c>
       <c r="C6">
-        <v>15954.33732702311</v>
+        <v>15825.5943638429</v>
       </c>
       <c r="D6">
-        <v>15454.12132702311</v>
+        <v>15492.6243638429</v>
       </c>
       <c r="E6">
-        <v>-3672.716</v>
+        <v>-3505.47</v>
       </c>
       <c r="F6">
-        <v>668.9839999999999</v>
+        <v>836.23</v>
       </c>
       <c r="G6">
         <v>1169.2</v>
@@ -1785,28 +1785,28 @@
         <v>1031.4</v>
       </c>
       <c r="M6">
-        <v>33.6498952</v>
+        <v>42.062369</v>
       </c>
       <c r="N6">
-        <v>997.7501048000001</v>
+        <v>989.3376310000001</v>
       </c>
       <c r="O6">
-        <v>145.6715153008</v>
+        <v>144.443294126</v>
       </c>
       <c r="P6">
-        <v>852.0785894992001</v>
+        <v>844.8943368740001</v>
       </c>
       <c r="Q6">
-        <v>1191.8785894992</v>
+        <v>1184.694336874</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.07522676542397173</v>
+        <v>0.07549285049417193</v>
       </c>
       <c r="T6">
-        <v>0.6796019728399938</v>
+        <v>0.6857471245767189</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1823,7 +1823,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>30.65091269585886</v>
+        <v>24.52073015668709</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1831,22 +1831,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.07386601796946332</v>
+        <v>0.07379609313191381</v>
       </c>
       <c r="C7">
-        <v>15825.5943638429</v>
+        <v>15697.04373597046</v>
       </c>
       <c r="D7">
-        <v>15492.6243638429</v>
+        <v>15531.31973597046</v>
       </c>
       <c r="E7">
-        <v>-3505.47</v>
+        <v>-3338.224</v>
       </c>
       <c r="F7">
-        <v>836.23</v>
+        <v>1003.476</v>
       </c>
       <c r="G7">
         <v>1169.2</v>
@@ -1867,28 +1867,28 @@
         <v>1031.4</v>
       </c>
       <c r="M7">
-        <v>42.062369</v>
+        <v>50.4748428</v>
       </c>
       <c r="N7">
-        <v>989.3376310000001</v>
+        <v>980.9251572000001</v>
       </c>
       <c r="O7">
-        <v>144.443294126</v>
+        <v>143.2150729512</v>
       </c>
       <c r="P7">
-        <v>844.8943368740001</v>
+        <v>837.7100842488001</v>
       </c>
       <c r="Q7">
-        <v>1184.694336874</v>
+        <v>1177.5100842488</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.07549285049417193</v>
+        <v>0.07576459694884448</v>
       </c>
       <c r="T7">
-        <v>0.6857471245767189</v>
+        <v>0.6920230242227362</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1905,7 +1905,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>24.52073015668709</v>
+        <v>20.43394179723924</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1913,22 +1913,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.07379609313191381</v>
+        <v>0.07372616829436429</v>
       </c>
       <c r="C8">
-        <v>15697.04373597046</v>
+        <v>15568.68688818138</v>
       </c>
       <c r="D8">
-        <v>15531.31973597046</v>
+        <v>15570.20888818138</v>
       </c>
       <c r="E8">
-        <v>-3338.224</v>
+        <v>-3170.978</v>
       </c>
       <c r="F8">
-        <v>1003.476</v>
+        <v>1170.722</v>
       </c>
       <c r="G8">
         <v>1169.2</v>
@@ -1949,28 +1949,28 @@
         <v>1031.4</v>
       </c>
       <c r="M8">
-        <v>50.47484279999999</v>
+        <v>58.88731659999998</v>
       </c>
       <c r="N8">
-        <v>980.9251572000001</v>
+        <v>972.5126834000001</v>
       </c>
       <c r="O8">
-        <v>143.2150729512</v>
+        <v>141.9868517764</v>
       </c>
       <c r="P8">
-        <v>837.7100842488001</v>
+        <v>830.5258316236001</v>
       </c>
       <c r="Q8">
-        <v>1177.5100842488</v>
+        <v>1170.3258316236</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.07576459694884448</v>
+        <v>0.07604218741329494</v>
       </c>
       <c r="T8">
-        <v>0.6920230242227362</v>
+        <v>0.6984338894525387</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1987,7 +1987,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>20.43394179723924</v>
+        <v>17.5148072547765</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1995,22 +1995,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.07372616829436429</v>
+        <v>0.07365624345681475</v>
       </c>
       <c r="C9">
-        <v>15568.68688818138</v>
+        <v>15440.52527975796</v>
       </c>
       <c r="D9">
-        <v>15570.20888818138</v>
+        <v>15609.29327975796</v>
       </c>
       <c r="E9">
-        <v>-3170.978</v>
+        <v>-3003.732</v>
       </c>
       <c r="F9">
-        <v>1170.722</v>
+        <v>1337.968</v>
       </c>
       <c r="G9">
         <v>1169.2</v>
@@ -2031,28 +2031,28 @@
         <v>1031.4</v>
       </c>
       <c r="M9">
-        <v>58.8873166</v>
+        <v>67.29979039999999</v>
       </c>
       <c r="N9">
-        <v>972.5126834000001</v>
+        <v>964.1002096000001</v>
       </c>
       <c r="O9">
-        <v>141.9868517764</v>
+        <v>140.7586306016</v>
       </c>
       <c r="P9">
-        <v>830.5258316236001</v>
+        <v>823.3415789984001</v>
       </c>
       <c r="Q9">
-        <v>1170.3258316236</v>
+        <v>1163.1415789984</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.07604218741329494</v>
+        <v>0.07632581245305951</v>
       </c>
       <c r="T9">
-        <v>0.6984338894525387</v>
+        <v>0.7049841213177717</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2069,7 +2069,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>17.51480725477649</v>
+        <v>15.32545634792943</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2077,22 +2077,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.07365624345681475</v>
+        <v>0.07358631861926523</v>
       </c>
       <c r="C10">
-        <v>15440.52527975796</v>
+        <v>15312.56038467169</v>
       </c>
       <c r="D10">
-        <v>15609.29327975796</v>
+        <v>15648.57438467169</v>
       </c>
       <c r="E10">
-        <v>-3003.732</v>
+        <v>-2836.486</v>
       </c>
       <c r="F10">
-        <v>1337.968</v>
+        <v>1505.214</v>
       </c>
       <c r="G10">
         <v>1169.2</v>
@@ -2113,28 +2113,28 @@
         <v>1031.4</v>
       </c>
       <c r="M10">
-        <v>67.29979039999999</v>
+        <v>75.71226419999998</v>
       </c>
       <c r="N10">
-        <v>964.1002096000001</v>
+        <v>955.6877358000002</v>
       </c>
       <c r="O10">
-        <v>140.7586306016</v>
+        <v>139.5304094268</v>
       </c>
       <c r="P10">
-        <v>823.3415789984001</v>
+        <v>816.1573263732001</v>
       </c>
       <c r="Q10">
-        <v>1163.1415789984</v>
+        <v>1155.9573263732</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.07632581245305951</v>
+        <v>0.07661567101018157</v>
       </c>
       <c r="T10">
-        <v>0.7049841213177717</v>
+        <v>0.7116783143228999</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2151,7 +2151,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>15.32545634792943</v>
+        <v>13.62262786482616</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2159,22 +2159,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.07358631861926523</v>
+        <v>0.07351639378171571</v>
       </c>
       <c r="C11">
-        <v>15312.56038467169</v>
+        <v>15184.7936917687</v>
       </c>
       <c r="D11">
-        <v>15648.57438467169</v>
+        <v>15688.05369176869</v>
       </c>
       <c r="E11">
-        <v>-2836.486</v>
+        <v>-2669.24</v>
       </c>
       <c r="F11">
-        <v>1505.214</v>
+        <v>1672.46</v>
       </c>
       <c r="G11">
         <v>1169.2</v>
@@ -2195,28 +2195,28 @@
         <v>1031.4</v>
       </c>
       <c r="M11">
-        <v>75.71226419999998</v>
+        <v>84.12473799999998</v>
       </c>
       <c r="N11">
-        <v>955.6877358000002</v>
+        <v>947.2752620000001</v>
       </c>
       <c r="O11">
-        <v>139.5304094268</v>
+        <v>138.302188252</v>
       </c>
       <c r="P11">
-        <v>816.1573263732001</v>
+        <v>808.9730737480002</v>
       </c>
       <c r="Q11">
-        <v>1155.9573263732</v>
+        <v>1148.773073748</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.07661567101018157</v>
+        <v>0.076911970868573</v>
       </c>
       <c r="T11">
-        <v>0.7116783143228999</v>
+        <v>0.7185212671725865</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2233,7 +2233,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>13.62262786482616</v>
+        <v>12.26036507834355</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2241,22 +2241,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.07351639378171571</v>
+        <v>0.07344646894416618</v>
       </c>
       <c r="C12">
-        <v>15184.7936917687</v>
+        <v>15057.22670495771</v>
       </c>
       <c r="D12">
-        <v>15688.05369176869</v>
+        <v>15727.73270495771</v>
       </c>
       <c r="E12">
-        <v>-2669.24</v>
+        <v>-2501.994</v>
       </c>
       <c r="F12">
-        <v>1672.46</v>
+        <v>1839.706</v>
       </c>
       <c r="G12">
         <v>1169.2</v>
@@ -2277,28 +2277,28 @@
         <v>1031.4</v>
       </c>
       <c r="M12">
-        <v>84.12473799999999</v>
+        <v>92.53721179999999</v>
       </c>
       <c r="N12">
-        <v>947.2752620000001</v>
+        <v>938.8627882000001</v>
       </c>
       <c r="O12">
-        <v>138.302188252</v>
+        <v>137.0739670772</v>
       </c>
       <c r="P12">
-        <v>808.9730737480002</v>
+        <v>801.7888211228001</v>
       </c>
       <c r="Q12">
-        <v>1148.773073748</v>
+        <v>1141.5888211228</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.076911970868573</v>
+        <v>0.07721492915074851</v>
       </c>
       <c r="T12">
-        <v>0.7185212671725865</v>
+        <v>0.7255179942436144</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2315,7 +2315,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>12.26036507834355</v>
+        <v>11.14578643485777</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2323,22 +2323,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.07344646894416618</v>
+        <v>0.07337654410661665</v>
       </c>
       <c r="C13">
-        <v>15057.22670495771</v>
+        <v>14929.8609434011</v>
       </c>
       <c r="D13">
-        <v>15727.73270495771</v>
+        <v>15767.6129434011</v>
       </c>
       <c r="E13">
-        <v>-2501.994</v>
+        <v>-2334.748</v>
       </c>
       <c r="F13">
-        <v>1839.706</v>
+        <v>2006.952</v>
       </c>
       <c r="G13">
         <v>1169.2</v>
@@ -2359,28 +2359,28 @@
         <v>1031.4</v>
       </c>
       <c r="M13">
-        <v>92.53721179999999</v>
+        <v>100.9496856</v>
       </c>
       <c r="N13">
-        <v>938.8627882000001</v>
+        <v>930.4503144000001</v>
       </c>
       <c r="O13">
-        <v>137.0739670772</v>
+        <v>135.8457459024</v>
       </c>
       <c r="P13">
-        <v>801.7888211228001</v>
+        <v>794.6045684976001</v>
       </c>
       <c r="Q13">
-        <v>1141.5888211228</v>
+        <v>1134.4045684976</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.07721492915074851</v>
+        <v>0.077524772848428</v>
       </c>
       <c r="T13">
-        <v>0.7255179942436144</v>
+        <v>0.7326737378389837</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2397,7 +2397,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>11.14578643485777</v>
+        <v>10.21697089861962</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2405,22 +2405,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.07337654410661665</v>
+        <v>0.07330661926906712</v>
       </c>
       <c r="C14">
-        <v>14929.8609434011</v>
+        <v>14802.69794170875</v>
       </c>
       <c r="D14">
-        <v>15767.6129434011</v>
+        <v>15807.69594170875</v>
       </c>
       <c r="E14">
-        <v>-2334.748</v>
+        <v>-2167.502</v>
       </c>
       <c r="F14">
-        <v>2006.952</v>
+        <v>2174.198</v>
       </c>
       <c r="G14">
         <v>1169.2</v>
@@ -2441,28 +2441,28 @@
         <v>1031.4</v>
       </c>
       <c r="M14">
-        <v>100.9496856</v>
+        <v>109.3621594</v>
       </c>
       <c r="N14">
-        <v>930.4503144000001</v>
+        <v>922.0378406000001</v>
       </c>
       <c r="O14">
-        <v>135.8457459024</v>
+        <v>134.6175247276</v>
       </c>
       <c r="P14">
-        <v>794.6045684976001</v>
+        <v>787.4203158724001</v>
       </c>
       <c r="Q14">
-        <v>1134.4045684976</v>
+        <v>1127.2203158724</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.077524772848428</v>
+        <v>0.07784173938973232</v>
       </c>
       <c r="T14">
-        <v>0.7326737378389837</v>
+        <v>0.7399939812871204</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2479,7 +2479,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>10.21697089861962</v>
+        <v>9.431050060264266</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2487,22 +2487,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.07330661926906712</v>
+        <v>0.07323669443151759</v>
       </c>
       <c r="C15">
-        <v>14802.69794170875</v>
+        <v>14675.73925013489</v>
       </c>
       <c r="D15">
-        <v>15807.69594170875</v>
+        <v>15847.98325013489</v>
       </c>
       <c r="E15">
-        <v>-2167.502</v>
+        <v>-2000.256</v>
       </c>
       <c r="F15">
-        <v>2174.198</v>
+        <v>2341.444</v>
       </c>
       <c r="G15">
         <v>1169.2</v>
@@ -2523,28 +2523,28 @@
         <v>1031.4</v>
       </c>
       <c r="M15">
-        <v>109.3621594</v>
+        <v>117.7746332</v>
       </c>
       <c r="N15">
-        <v>922.0378406000001</v>
+        <v>913.6253668000001</v>
       </c>
       <c r="O15">
-        <v>134.6175247276</v>
+        <v>133.3893035528</v>
       </c>
       <c r="P15">
-        <v>787.4203158724001</v>
+        <v>780.2360632472</v>
       </c>
       <c r="Q15">
-        <v>1127.2203158724</v>
+        <v>1120.0360632472</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.07784173938973232</v>
+        <v>0.07816607724595068</v>
       </c>
       <c r="T15">
-        <v>0.7399939812871204</v>
+        <v>0.7474844629549811</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2561,7 +2561,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>9.431050060264266</v>
+        <v>8.757403627388246</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2569,22 +2569,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.07323669443151759</v>
+        <v>0.07335891959396806</v>
       </c>
       <c r="C16">
-        <v>14675.73925013489</v>
+        <v>14438.20666576225</v>
       </c>
       <c r="D16">
-        <v>15847.98325013489</v>
+        <v>15777.69666576225</v>
       </c>
       <c r="E16">
-        <v>-2000.256</v>
+        <v>-1833.01</v>
       </c>
       <c r="F16">
-        <v>2341.444</v>
+        <v>2508.69</v>
       </c>
       <c r="G16">
         <v>1169.2</v>
@@ -2605,45 +2605,45 @@
         <v>1031.4</v>
       </c>
       <c r="M16">
-        <v>117.7746332</v>
+        <v>129.950142</v>
       </c>
       <c r="N16">
-        <v>913.6253668000001</v>
+        <v>901.4498580000001</v>
       </c>
       <c r="O16">
-        <v>133.3893035528</v>
+        <v>131.611679268</v>
       </c>
       <c r="P16">
-        <v>780.2360632472</v>
+        <v>769.8381787320001</v>
       </c>
       <c r="Q16">
-        <v>1120.0360632472</v>
+        <v>1109.638178732</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.07816607724595068</v>
+        <v>0.0784980465811389</v>
       </c>
       <c r="T16">
-        <v>0.7474844629549811</v>
+        <v>0.7551511912503208</v>
       </c>
       <c r="U16">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V16">
         <v>0.146</v>
       </c>
       <c r="W16">
-        <v>0.0429562</v>
+        <v>0.0442372</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y16">
-        <v>8.757403627388246</v>
+        <v>7.936890134371689</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2651,22 +2651,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.07335891959396806</v>
+        <v>0.07330180475641852</v>
       </c>
       <c r="C17">
-        <v>14438.20666576226</v>
+        <v>14303.72726380745</v>
       </c>
       <c r="D17">
-        <v>15777.69666576225</v>
+        <v>15810.46326380745</v>
       </c>
       <c r="E17">
-        <v>-1833.01</v>
+        <v>-1665.764</v>
       </c>
       <c r="F17">
-        <v>2508.69</v>
+        <v>2675.936</v>
       </c>
       <c r="G17">
         <v>1169.2</v>
@@ -2687,28 +2687,28 @@
         <v>1031.4</v>
       </c>
       <c r="M17">
-        <v>129.950142</v>
+        <v>138.6134848</v>
       </c>
       <c r="N17">
-        <v>901.4498580000002</v>
+        <v>892.7865152000002</v>
       </c>
       <c r="O17">
-        <v>131.611679268</v>
+        <v>130.3468312192</v>
       </c>
       <c r="P17">
-        <v>769.8381787320002</v>
+        <v>762.4396839808002</v>
       </c>
       <c r="Q17">
-        <v>1109.638178732</v>
+        <v>1102.2396839808</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.0784980465811389</v>
+        <v>0.0788379199481173</v>
       </c>
       <c r="T17">
-        <v>0.7551511912503208</v>
+        <v>0.7630004606955496</v>
       </c>
       <c r="U17">
         <v>0.0518</v>
@@ -2725,7 +2725,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>7.936890134371692</v>
+        <v>7.44083450097346</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2733,22 +2733,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.07330180475641852</v>
+        <v>0.073244689918869</v>
       </c>
       <c r="C18">
-        <v>14303.72726380745</v>
+        <v>14169.38424225481</v>
       </c>
       <c r="D18">
-        <v>15810.46326380745</v>
+        <v>15843.36624225481</v>
       </c>
       <c r="E18">
-        <v>-1665.764</v>
+        <v>-1498.518</v>
       </c>
       <c r="F18">
-        <v>2675.936</v>
+        <v>2843.182</v>
       </c>
       <c r="G18">
         <v>1169.2</v>
@@ -2769,28 +2769,28 @@
         <v>1031.4</v>
       </c>
       <c r="M18">
-        <v>138.6134848</v>
+        <v>147.2768276</v>
       </c>
       <c r="N18">
-        <v>892.7865152000002</v>
+        <v>884.1231724000002</v>
       </c>
       <c r="O18">
-        <v>130.3468312192</v>
+        <v>129.0819831704</v>
       </c>
       <c r="P18">
-        <v>762.4396839808002</v>
+        <v>755.0411892296001</v>
       </c>
       <c r="Q18">
-        <v>1102.2396839808</v>
+        <v>1094.8411892296</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.0788379199481173</v>
+        <v>0.07918598303478193</v>
       </c>
       <c r="T18">
-        <v>0.7630004606955496</v>
+        <v>0.7710388691635548</v>
       </c>
       <c r="U18">
         <v>0.0518</v>
@@ -2807,7 +2807,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>7.44083450097346</v>
+        <v>7.003138353857373</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2815,22 +2815,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.073244689918869</v>
+        <v>0.07344889908131946</v>
       </c>
       <c r="C19">
-        <v>14169.38424225481</v>
+        <v>13885.1223516325</v>
       </c>
       <c r="D19">
-        <v>15843.36624225481</v>
+        <v>15726.35035163251</v>
       </c>
       <c r="E19">
-        <v>-1498.518</v>
+        <v>-1331.272</v>
       </c>
       <c r="F19">
-        <v>2843.182</v>
+        <v>3010.428</v>
       </c>
       <c r="G19">
         <v>1169.2</v>
@@ -2851,45 +2851,45 @@
         <v>1031.4</v>
       </c>
       <c r="M19">
-        <v>147.2768276</v>
+        <v>161.057898</v>
       </c>
       <c r="N19">
-        <v>884.1231724000002</v>
+        <v>870.3421020000001</v>
       </c>
       <c r="O19">
-        <v>129.0819831704</v>
+        <v>127.069946892</v>
       </c>
       <c r="P19">
-        <v>755.0411892296001</v>
+        <v>743.2721551080001</v>
       </c>
       <c r="Q19">
-        <v>1094.8411892296</v>
+        <v>1083.072155108</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.07918598303478193</v>
+        <v>0.07954253546502374</v>
       </c>
       <c r="T19">
-        <v>0.7710388691635548</v>
+        <v>0.7792733363746823</v>
       </c>
       <c r="U19">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V19">
         <v>0.146</v>
       </c>
       <c r="W19">
-        <v>0.0442372</v>
+        <v>0.045689</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y19">
-        <v>7.003138353857373</v>
+        <v>6.4039082392594</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2897,22 +2897,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.07344889908131946</v>
+        <v>0.07340630224376996</v>
       </c>
       <c r="C20">
-        <v>13885.1223516325</v>
+        <v>13742.14228863703</v>
       </c>
       <c r="D20">
-        <v>15726.35035163251</v>
+        <v>15750.61628863703</v>
       </c>
       <c r="E20">
-        <v>-1331.272</v>
+        <v>-1164.026</v>
       </c>
       <c r="F20">
-        <v>3010.427999999999</v>
+        <v>3177.674</v>
       </c>
       <c r="G20">
         <v>1169.2</v>
@@ -2933,28 +2933,28 @@
         <v>1031.4</v>
       </c>
       <c r="M20">
-        <v>161.057898</v>
+        <v>170.005559</v>
       </c>
       <c r="N20">
-        <v>870.3421020000001</v>
+        <v>861.3944410000001</v>
       </c>
       <c r="O20">
-        <v>127.069946892</v>
+        <v>125.763588386</v>
       </c>
       <c r="P20">
-        <v>743.2721551080001</v>
+        <v>735.6308526140001</v>
       </c>
       <c r="Q20">
-        <v>1083.072155108</v>
+        <v>1075.430852614</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.07954253546502374</v>
+        <v>0.07990789165897524</v>
       </c>
       <c r="T20">
-        <v>0.7792733363746823</v>
+        <v>0.7877111237638623</v>
       </c>
       <c r="U20">
         <v>0.0535</v>
@@ -2971,7 +2971,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>6.403908239259401</v>
+        <v>6.066860437193117</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2979,22 +2979,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.07340630224376996</v>
+        <v>0.07336370540622042</v>
       </c>
       <c r="C21">
-        <v>13742.14228863703</v>
+        <v>13599.23722660108</v>
       </c>
       <c r="D21">
-        <v>15750.61628863703</v>
+        <v>15774.95722660108</v>
       </c>
       <c r="E21">
-        <v>-1164.026</v>
+        <v>-996.7799999999997</v>
       </c>
       <c r="F21">
-        <v>3177.674</v>
+        <v>3344.92</v>
       </c>
       <c r="G21">
         <v>1169.2</v>
@@ -3015,28 +3015,28 @@
         <v>1031.4</v>
       </c>
       <c r="M21">
-        <v>170.005559</v>
+        <v>178.95322</v>
       </c>
       <c r="N21">
-        <v>861.3944410000001</v>
+        <v>852.4467800000001</v>
       </c>
       <c r="O21">
-        <v>125.763588386</v>
+        <v>124.45722988</v>
       </c>
       <c r="P21">
-        <v>735.6308526140001</v>
+        <v>727.9895501200001</v>
       </c>
       <c r="Q21">
-        <v>1075.430852614</v>
+        <v>1067.78955012</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.07990789165897524</v>
+        <v>0.08028238175777552</v>
       </c>
       <c r="T21">
-        <v>0.7877111237638623</v>
+        <v>0.7963598558377718</v>
       </c>
       <c r="U21">
         <v>0.0535</v>
@@ -3053,7 +3053,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>6.066860437193117</v>
+        <v>5.76351741533346</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3061,22 +3061,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.07336370540622042</v>
+        <v>0.07346458056867089</v>
       </c>
       <c r="C22">
-        <v>13599.23722660108</v>
+        <v>13374.46997234123</v>
       </c>
       <c r="D22">
-        <v>15774.95722660108</v>
+        <v>15717.43597234123</v>
       </c>
       <c r="E22">
-        <v>-996.7799999999997</v>
+        <v>-829.5339999999997</v>
       </c>
       <c r="F22">
-        <v>3344.92</v>
+        <v>3512.166</v>
       </c>
       <c r="G22">
         <v>1169.2</v>
@@ -3097,45 +3097,45 @@
         <v>1031.4</v>
       </c>
       <c r="M22">
-        <v>178.95322</v>
+        <v>190.7106138</v>
       </c>
       <c r="N22">
-        <v>852.4467800000001</v>
+        <v>840.6893862000001</v>
       </c>
       <c r="O22">
-        <v>124.45722988</v>
+        <v>122.7406503852</v>
       </c>
       <c r="P22">
-        <v>727.9895501200001</v>
+        <v>717.9487358148001</v>
       </c>
       <c r="Q22">
-        <v>1067.78955012</v>
+        <v>1057.7487358148</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.08028238175777552</v>
+        <v>0.08066635261857075</v>
       </c>
       <c r="T22">
-        <v>0.7963598558377718</v>
+        <v>0.8052275431540586</v>
       </c>
       <c r="U22">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V22">
         <v>0.146</v>
       </c>
       <c r="W22">
-        <v>0.045689</v>
+        <v>0.0463722</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y22">
-        <v>5.76351741533346</v>
+        <v>5.408194014212753</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3143,22 +3143,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.07346458056867089</v>
+        <v>0.07342881573112137</v>
       </c>
       <c r="C23">
-        <v>13374.46997234123</v>
+        <v>13227.56981523643</v>
       </c>
       <c r="D23">
-        <v>15717.43597234123</v>
+        <v>15737.78181523643</v>
       </c>
       <c r="E23">
-        <v>-829.5340000000001</v>
+        <v>-662.288</v>
       </c>
       <c r="F23">
-        <v>3512.166</v>
+        <v>3679.412</v>
       </c>
       <c r="G23">
         <v>1169.2</v>
@@ -3179,28 +3179,28 @@
         <v>1031.4</v>
       </c>
       <c r="M23">
-        <v>190.7106138</v>
+        <v>199.7920716</v>
       </c>
       <c r="N23">
-        <v>840.6893862000002</v>
+        <v>831.6079284000001</v>
       </c>
       <c r="O23">
-        <v>122.7406503852</v>
+        <v>121.4147575464</v>
       </c>
       <c r="P23">
-        <v>717.9487358148001</v>
+        <v>710.1931708536001</v>
       </c>
       <c r="Q23">
-        <v>1057.7487358148</v>
+        <v>1049.9931708536</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.08066635261857075</v>
+        <v>0.08106016888605302</v>
       </c>
       <c r="T23">
-        <v>0.8052275431540586</v>
+        <v>0.8143226070681991</v>
       </c>
       <c r="U23">
         <v>0.0543</v>
@@ -3217,7 +3217,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>5.408194014212754</v>
+        <v>5.162367013566719</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3225,22 +3225,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.07342881573112137</v>
+        <v>0.07339305089357184</v>
       </c>
       <c r="C24">
-        <v>13227.56981523643</v>
+        <v>13080.72240081447</v>
       </c>
       <c r="D24">
-        <v>15737.78181523643</v>
+        <v>15758.18040081447</v>
       </c>
       <c r="E24">
-        <v>-662.288</v>
+        <v>-495.0419999999999</v>
       </c>
       <c r="F24">
-        <v>3679.412</v>
+        <v>3846.658</v>
       </c>
       <c r="G24">
         <v>1169.2</v>
@@ -3261,28 +3261,28 @@
         <v>1031.4</v>
       </c>
       <c r="M24">
-        <v>199.7920716</v>
+        <v>208.8735294</v>
       </c>
       <c r="N24">
-        <v>831.6079284000001</v>
+        <v>822.5264706</v>
       </c>
       <c r="O24">
-        <v>121.4147575464</v>
+        <v>120.0888647076</v>
       </c>
       <c r="P24">
-        <v>710.1931708536001</v>
+        <v>702.4376058924</v>
       </c>
       <c r="Q24">
-        <v>1049.9931708536</v>
+        <v>1042.2376058924</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.08106016888605302</v>
+        <v>0.08146421414749588</v>
       </c>
       <c r="T24">
-        <v>0.8143226070681991</v>
+        <v>0.8236539064086809</v>
       </c>
       <c r="U24">
         <v>0.0543</v>
@@ -3299,7 +3299,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>5.162367013566719</v>
+        <v>4.937916273846427</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3307,22 +3307,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.07339305089357184</v>
+        <v>0.07335728605602231</v>
       </c>
       <c r="C25">
-        <v>13080.72240081447</v>
+        <v>12933.92793442941</v>
       </c>
       <c r="D25">
-        <v>15758.18040081447</v>
+        <v>15778.63193442942</v>
       </c>
       <c r="E25">
-        <v>-495.0419999999999</v>
+        <v>-327.7959999999998</v>
       </c>
       <c r="F25">
-        <v>3846.658</v>
+        <v>4013.904</v>
       </c>
       <c r="G25">
         <v>1169.2</v>
@@ -3343,28 +3343,28 @@
         <v>1031.4</v>
       </c>
       <c r="M25">
-        <v>208.8735294</v>
+        <v>217.9549872</v>
       </c>
       <c r="N25">
-        <v>822.5264706</v>
+        <v>813.4450128000001</v>
       </c>
       <c r="O25">
-        <v>120.0888647076</v>
+        <v>118.7629718688</v>
       </c>
       <c r="P25">
-        <v>702.4376058924</v>
+        <v>694.6820409312</v>
       </c>
       <c r="Q25">
-        <v>1042.2376058924</v>
+        <v>1034.4820409312</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.08146421414749588</v>
+        <v>0.08187889217897672</v>
       </c>
       <c r="T25">
-        <v>0.8236539064086809</v>
+        <v>0.8332307662581228</v>
       </c>
       <c r="U25">
         <v>0.0543</v>
@@ -3381,7 +3381,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>4.937916273846427</v>
+        <v>4.732169762436159</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3389,22 +3389,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.07335728605602231</v>
+        <v>0.07332152121847277</v>
       </c>
       <c r="C26">
-        <v>12933.92793442942</v>
+        <v>12787.18662250276</v>
       </c>
       <c r="D26">
-        <v>15778.63193442942</v>
+        <v>15799.13662250277</v>
       </c>
       <c r="E26">
-        <v>-327.7960000000003</v>
+        <v>-160.5500000000002</v>
       </c>
       <c r="F26">
-        <v>4013.904</v>
+        <v>4181.15</v>
       </c>
       <c r="G26">
         <v>1169.2</v>
@@ -3425,28 +3425,28 @@
         <v>1031.4</v>
       </c>
       <c r="M26">
-        <v>217.9549872</v>
+        <v>227.036445</v>
       </c>
       <c r="N26">
-        <v>813.4450128000001</v>
+        <v>804.3635550000001</v>
       </c>
       <c r="O26">
-        <v>118.7629718688</v>
+        <v>117.43707903</v>
       </c>
       <c r="P26">
-        <v>694.6820409312</v>
+        <v>686.9264759700002</v>
       </c>
       <c r="Q26">
-        <v>1034.4820409312</v>
+        <v>1026.72647597</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.08187889217897672</v>
+        <v>0.08230462829129703</v>
       </c>
       <c r="T26">
-        <v>0.8332307662581228</v>
+        <v>0.8430630090368829</v>
       </c>
       <c r="U26">
         <v>0.0543</v>
@@ -3463,7 +3463,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>4.732169762436159</v>
+        <v>4.542882971938713</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3471,22 +3471,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.07332152121847277</v>
+        <v>0.07328575638092324</v>
       </c>
       <c r="C27">
-        <v>12787.18662250276</v>
+        <v>12640.4986725304</v>
       </c>
       <c r="D27">
-        <v>15799.13662250277</v>
+        <v>15819.6946725304</v>
       </c>
       <c r="E27">
-        <v>-160.5500000000002</v>
+        <v>6.695999999999913</v>
       </c>
       <c r="F27">
-        <v>4181.15</v>
+        <v>4348.396</v>
       </c>
       <c r="G27">
         <v>1169.2</v>
@@ -3507,28 +3507,28 @@
         <v>1031.4</v>
       </c>
       <c r="M27">
-        <v>227.036445</v>
+        <v>236.1179028</v>
       </c>
       <c r="N27">
-        <v>804.3635550000001</v>
+        <v>795.2820972000001</v>
       </c>
       <c r="O27">
-        <v>117.43707903</v>
+        <v>116.1111861912</v>
       </c>
       <c r="P27">
-        <v>686.9264759700002</v>
+        <v>679.1709110088001</v>
       </c>
       <c r="Q27">
-        <v>1026.72647597</v>
+        <v>1018.9709110088</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.08230462829129703</v>
+        <v>0.08274187078503142</v>
       </c>
       <c r="T27">
-        <v>0.8430630090368829</v>
+        <v>0.8531609881069611</v>
       </c>
       <c r="U27">
         <v>0.0543</v>
@@ -3545,7 +3545,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>4.542882971938713</v>
+        <v>4.368156703787223</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3553,22 +3553,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.07328575638092324</v>
+        <v>0.07348057154337373</v>
       </c>
       <c r="C28">
-        <v>12640.4986725304</v>
+        <v>12361.91406152243</v>
       </c>
       <c r="D28">
-        <v>15819.6946725304</v>
+        <v>15708.35606152243</v>
       </c>
       <c r="E28">
-        <v>6.695999999999913</v>
+        <v>173.942</v>
       </c>
       <c r="F28">
-        <v>4348.396</v>
+        <v>4515.642</v>
       </c>
       <c r="G28">
         <v>1169.2</v>
@@ -3589,45 +3589,45 @@
         <v>1031.4</v>
       </c>
       <c r="M28">
-        <v>236.1179028</v>
+        <v>249.7150026</v>
       </c>
       <c r="N28">
-        <v>795.2820972000001</v>
+        <v>781.6849974000002</v>
       </c>
       <c r="O28">
-        <v>116.1111861912</v>
+        <v>114.1260096204</v>
       </c>
       <c r="P28">
-        <v>679.1709110088001</v>
+        <v>667.5589877796001</v>
       </c>
       <c r="Q28">
-        <v>1018.9709110088</v>
+        <v>1007.3589877796</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.08274187078503142</v>
+        <v>0.08319109252516949</v>
       </c>
       <c r="T28">
-        <v>0.8531609881069611</v>
+        <v>0.8635356241378633</v>
       </c>
       <c r="U28">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V28">
         <v>0.146</v>
       </c>
       <c r="W28">
-        <v>0.0463722</v>
+        <v>0.0472262</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y28">
-        <v>4.368156703787223</v>
+        <v>4.130308508744761</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3635,22 +3635,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.07348057154337373</v>
+        <v>0.07345334670582421</v>
       </c>
       <c r="C29">
-        <v>12361.91406152243</v>
+        <v>12210.13300493396</v>
       </c>
       <c r="D29">
-        <v>15708.35606152243</v>
+        <v>15723.82100493396</v>
       </c>
       <c r="E29">
-        <v>173.942</v>
+        <v>341.1880000000001</v>
       </c>
       <c r="F29">
-        <v>4515.642</v>
+        <v>4682.888</v>
       </c>
       <c r="G29">
         <v>1169.2</v>
@@ -3671,28 +3671,28 @@
         <v>1031.4</v>
       </c>
       <c r="M29">
-        <v>249.7150026</v>
+        <v>258.9637064</v>
       </c>
       <c r="N29">
-        <v>781.6849974000002</v>
+        <v>772.4362936000001</v>
       </c>
       <c r="O29">
-        <v>114.1260096204</v>
+        <v>112.7756988656</v>
       </c>
       <c r="P29">
-        <v>667.5589877796001</v>
+        <v>659.6605947344001</v>
       </c>
       <c r="Q29">
-        <v>1007.3589877796</v>
+        <v>999.4605947344</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.08319109252516949</v>
+        <v>0.08365279264697806</v>
       </c>
       <c r="T29">
-        <v>0.8635356241378633</v>
+        <v>0.8741984445029573</v>
       </c>
       <c r="U29">
         <v>0.0553</v>
@@ -3709,7 +3709,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>4.130308508744761</v>
+        <v>3.982797490575305</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3717,22 +3717,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.07345334670582421</v>
+        <v>0.07342612186827466</v>
       </c>
       <c r="C30">
-        <v>12210.13300493396</v>
+        <v>12058.38242895904</v>
       </c>
       <c r="D30">
-        <v>15723.82100493396</v>
+        <v>15739.31642895904</v>
       </c>
       <c r="E30">
-        <v>341.1880000000001</v>
+        <v>508.4340000000002</v>
       </c>
       <c r="F30">
-        <v>4682.888</v>
+        <v>4850.134</v>
       </c>
       <c r="G30">
         <v>1169.2</v>
@@ -3753,28 +3753,28 @@
         <v>1031.4</v>
       </c>
       <c r="M30">
-        <v>258.9637064</v>
+        <v>268.2124102</v>
       </c>
       <c r="N30">
-        <v>772.4362936000001</v>
+        <v>763.1875898000001</v>
       </c>
       <c r="O30">
-        <v>112.7756988656</v>
+        <v>111.4253881108</v>
       </c>
       <c r="P30">
-        <v>659.6605947344001</v>
+        <v>651.7622016892001</v>
       </c>
       <c r="Q30">
-        <v>999.4605947344</v>
+        <v>991.5622016892</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.08365279264697806</v>
+        <v>0.08412749840602066</v>
       </c>
       <c r="T30">
-        <v>0.8741984445029573</v>
+        <v>0.885161626005096</v>
       </c>
       <c r="U30">
         <v>0.0553</v>
@@ -3791,7 +3791,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>3.982797490575305</v>
+        <v>3.845459646072708</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3799,22 +3799,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.07342612186827466</v>
+        <v>0.07339889703072514</v>
       </c>
       <c r="C31">
-        <v>12058.38242895904</v>
+        <v>11906.66242380014</v>
       </c>
       <c r="D31">
-        <v>15739.31642895904</v>
+        <v>15754.84242380014</v>
       </c>
       <c r="E31">
-        <v>508.4339999999993</v>
+        <v>675.6799999999994</v>
       </c>
       <c r="F31">
-        <v>4850.133999999999</v>
+        <v>5017.379999999999</v>
       </c>
       <c r="G31">
         <v>1169.2</v>
@@ -3835,28 +3835,28 @@
         <v>1031.4</v>
       </c>
       <c r="M31">
-        <v>268.2124102</v>
+        <v>277.461114</v>
       </c>
       <c r="N31">
-        <v>763.1875898000001</v>
+        <v>753.9388860000001</v>
       </c>
       <c r="O31">
-        <v>111.4253881108</v>
+        <v>110.075077356</v>
       </c>
       <c r="P31">
-        <v>651.7622016892001</v>
+        <v>643.8638086440001</v>
       </c>
       <c r="Q31">
-        <v>991.5622016892</v>
+        <v>983.663808644</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.08412749840602066</v>
+        <v>0.08461576718675021</v>
       </c>
       <c r="T31">
-        <v>0.885161626005096</v>
+        <v>0.8964380412644387</v>
       </c>
       <c r="U31">
         <v>0.0553</v>
@@ -3873,7 +3873,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>3.845459646072709</v>
+        <v>3.717277657870286</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3881,22 +3881,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.07339889703072514</v>
+        <v>0.07337167219317561</v>
       </c>
       <c r="C32">
-        <v>11906.66242380014</v>
+        <v>11754.97308001602</v>
       </c>
       <c r="D32">
-        <v>15754.84242380014</v>
+        <v>15770.39908001602</v>
       </c>
       <c r="E32">
-        <v>675.6799999999994</v>
+        <v>842.9259999999995</v>
       </c>
       <c r="F32">
-        <v>5017.379999999999</v>
+        <v>5184.625999999999</v>
       </c>
       <c r="G32">
         <v>1169.2</v>
@@ -3917,28 +3917,28 @@
         <v>1031.4</v>
       </c>
       <c r="M32">
-        <v>277.461114</v>
+        <v>286.7098178</v>
       </c>
       <c r="N32">
-        <v>753.9388860000001</v>
+        <v>744.6901822000001</v>
       </c>
       <c r="O32">
-        <v>110.075077356</v>
+        <v>108.7247666012</v>
       </c>
       <c r="P32">
-        <v>643.8638086440001</v>
+        <v>635.9654155988001</v>
       </c>
       <c r="Q32">
-        <v>983.663808644</v>
+        <v>975.7654155988</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.08461576718675021</v>
+        <v>0.08511818868576176</v>
       </c>
       <c r="T32">
-        <v>0.8964380412644387</v>
+        <v>0.9080413091399944</v>
       </c>
       <c r="U32">
         <v>0.0553</v>
@@ -3955,7 +3955,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>3.717277657870286</v>
+        <v>3.59736547535834</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3963,22 +3963,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.07337167219317561</v>
+        <v>0.07334444735562608</v>
       </c>
       <c r="C33">
-        <v>11754.97308001602</v>
+        <v>11603.3144885235</v>
       </c>
       <c r="D33">
-        <v>15770.39908001602</v>
+        <v>15785.9864885235</v>
       </c>
       <c r="E33">
-        <v>842.9259999999995</v>
+        <v>1010.172</v>
       </c>
       <c r="F33">
-        <v>5184.625999999999</v>
+        <v>5351.871999999999</v>
       </c>
       <c r="G33">
         <v>1169.2</v>
@@ -3999,28 +3999,28 @@
         <v>1031.4</v>
       </c>
       <c r="M33">
-        <v>286.7098178</v>
+        <v>295.9585216</v>
       </c>
       <c r="N33">
-        <v>744.6901822000001</v>
+        <v>735.4414784000001</v>
       </c>
       <c r="O33">
-        <v>108.7247666012</v>
+        <v>107.3744558464</v>
       </c>
       <c r="P33">
-        <v>635.9654155988001</v>
+        <v>628.0670225536001</v>
       </c>
       <c r="Q33">
-        <v>975.7654155988</v>
+        <v>967.8670225536</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.08511818868576176</v>
+        <v>0.08563538728768541</v>
       </c>
       <c r="T33">
-        <v>0.9080413091399944</v>
+        <v>0.919985849600125</v>
       </c>
       <c r="U33">
         <v>0.0553</v>
@@ -4037,7 +4037,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>3.59736547535834</v>
+        <v>3.484947804253392</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4045,22 +4045,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.07334444735562608</v>
+        <v>0.07331722251807656</v>
       </c>
       <c r="C34">
-        <v>11603.3144885235</v>
+        <v>11451.68674059915</v>
       </c>
       <c r="D34">
-        <v>15785.9864885235</v>
+        <v>15801.60474059914</v>
       </c>
       <c r="E34">
-        <v>1010.172</v>
+        <v>1177.418</v>
       </c>
       <c r="F34">
-        <v>5351.871999999999</v>
+        <v>5519.117999999999</v>
       </c>
       <c r="G34">
         <v>1169.2</v>
@@ -4081,28 +4081,28 @@
         <v>1031.4</v>
       </c>
       <c r="M34">
-        <v>295.9585216</v>
+        <v>305.2072254</v>
       </c>
       <c r="N34">
-        <v>735.4414784000001</v>
+        <v>726.1927746000001</v>
       </c>
       <c r="O34">
-        <v>107.3744558464</v>
+        <v>106.0241450916</v>
       </c>
       <c r="P34">
-        <v>628.0670225536001</v>
+        <v>620.1686295084002</v>
       </c>
       <c r="Q34">
-        <v>967.8670225536</v>
+        <v>959.9686295084001</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.08563538728768541</v>
+        <v>0.0861680246538456</v>
       </c>
       <c r="T34">
-        <v>0.919985849600125</v>
+        <v>0.9322869435068268</v>
       </c>
       <c r="U34">
         <v>0.0553</v>
@@ -4119,7 +4119,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>3.484947804253392</v>
+        <v>3.379343325336623</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4127,22 +4127,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.07331722251807656</v>
+        <v>0.07328999768052702</v>
       </c>
       <c r="C35">
-        <v>11451.68674059915</v>
+        <v>11300.08992788116</v>
       </c>
       <c r="D35">
-        <v>15801.60474059914</v>
+        <v>15817.25392788116</v>
       </c>
       <c r="E35">
-        <v>1177.418</v>
+        <v>1344.664</v>
       </c>
       <c r="F35">
-        <v>5519.117999999999</v>
+        <v>5686.364</v>
       </c>
       <c r="G35">
         <v>1169.2</v>
@@ -4163,28 +4163,28 @@
         <v>1031.4</v>
       </c>
       <c r="M35">
-        <v>305.2072254</v>
+        <v>314.4559292</v>
       </c>
       <c r="N35">
-        <v>726.1927746000001</v>
+        <v>716.9440708000001</v>
       </c>
       <c r="O35">
-        <v>106.0241450916</v>
+        <v>104.6738343368</v>
       </c>
       <c r="P35">
-        <v>620.1686295084002</v>
+        <v>612.2702364632</v>
       </c>
       <c r="Q35">
-        <v>959.9686295084001</v>
+        <v>952.0702364632</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.0861680246538456</v>
+        <v>0.08671680254625308</v>
       </c>
       <c r="T35">
-        <v>0.9322869435068268</v>
+        <v>0.9449607978349438</v>
       </c>
       <c r="U35">
         <v>0.0553</v>
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>3.379343325336623</v>
+        <v>3.279950874591428</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4209,22 +4209,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.07328999768052702</v>
+        <v>0.0732627728429775</v>
       </c>
       <c r="C36">
-        <v>11300.08992788116</v>
+        <v>11148.52414237109</v>
       </c>
       <c r="D36">
-        <v>15817.25392788116</v>
+        <v>15832.93414237109</v>
       </c>
       <c r="E36">
-        <v>1344.664</v>
+        <v>1511.91</v>
       </c>
       <c r="F36">
-        <v>5686.364</v>
+        <v>5853.61</v>
       </c>
       <c r="G36">
         <v>1169.2</v>
@@ -4245,28 +4245,28 @@
         <v>1031.4</v>
       </c>
       <c r="M36">
-        <v>314.4559292</v>
+        <v>323.704633</v>
       </c>
       <c r="N36">
-        <v>716.9440708000001</v>
+        <v>707.695367</v>
       </c>
       <c r="O36">
-        <v>104.6738343368</v>
+        <v>103.323523582</v>
       </c>
       <c r="P36">
-        <v>612.2702364632</v>
+        <v>604.371843418</v>
       </c>
       <c r="Q36">
-        <v>952.0702364632</v>
+        <v>944.171843418</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.08671680254625308</v>
+        <v>0.08728246591227307</v>
       </c>
       <c r="T36">
-        <v>0.9449607978349438</v>
+        <v>0.9580246169116182</v>
       </c>
       <c r="U36">
         <v>0.0553</v>
@@ -4283,7 +4283,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>3.279950874591428</v>
+        <v>3.186237992460244</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4291,22 +4291,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.0732627728429775</v>
+        <v>0.07323554800542796</v>
       </c>
       <c r="C37">
-        <v>11148.52414237109</v>
+        <v>10996.98947643569</v>
       </c>
       <c r="D37">
-        <v>15832.93414237109</v>
+        <v>15848.64547643569</v>
       </c>
       <c r="E37">
-        <v>1511.91</v>
+        <v>1679.156</v>
       </c>
       <c r="F37">
-        <v>5853.61</v>
+        <v>6020.856</v>
       </c>
       <c r="G37">
         <v>1169.2</v>
@@ -4327,28 +4327,28 @@
         <v>1031.4</v>
       </c>
       <c r="M37">
-        <v>323.704633</v>
+        <v>332.9533368</v>
       </c>
       <c r="N37">
-        <v>707.695367</v>
+        <v>698.4466632000001</v>
       </c>
       <c r="O37">
-        <v>103.323523582</v>
+        <v>101.9732128272</v>
       </c>
       <c r="P37">
-        <v>604.371843418</v>
+        <v>596.4734503728001</v>
       </c>
       <c r="Q37">
-        <v>944.171843418</v>
+        <v>936.2734503728001</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.08728246591227307</v>
+        <v>0.0878658062584812</v>
       </c>
       <c r="T37">
-        <v>0.9580246169116182</v>
+        <v>0.9714966803344387</v>
       </c>
       <c r="U37">
         <v>0.0553</v>
@@ -4365,7 +4365,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>3.186237992460244</v>
+        <v>3.097731381558571</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4373,22 +4373,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.07323554800542798</v>
+        <v>0.07320832316787845</v>
       </c>
       <c r="C38">
-        <v>10996.98947643568</v>
+        <v>10845.48602280866</v>
       </c>
       <c r="D38">
-        <v>15848.64547643568</v>
+        <v>15864.38802280866</v>
       </c>
       <c r="E38">
-        <v>1679.155999999999</v>
+        <v>1846.401999999999</v>
       </c>
       <c r="F38">
-        <v>6020.855999999999</v>
+        <v>6188.101999999999</v>
       </c>
       <c r="G38">
         <v>1169.2</v>
@@ -4409,28 +4409,28 @@
         <v>1031.4</v>
       </c>
       <c r="M38">
-        <v>332.9533367999999</v>
+        <v>342.2020406</v>
       </c>
       <c r="N38">
-        <v>698.4466632000001</v>
+        <v>689.1979594000002</v>
       </c>
       <c r="O38">
-        <v>101.9732128272</v>
+        <v>100.6229020724</v>
       </c>
       <c r="P38">
-        <v>596.4734503728001</v>
+        <v>588.5750573276001</v>
       </c>
       <c r="Q38">
-        <v>936.2734503728001</v>
+        <v>928.3750573276001</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.0878658062584812</v>
+        <v>0.0884676653458388</v>
       </c>
       <c r="T38">
-        <v>0.9714966803344387</v>
+        <v>0.9853964283103647</v>
       </c>
       <c r="U38">
         <v>0.0553</v>
@@ -4447,7 +4447,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>3.097731381558571</v>
+        <v>3.014008911786718</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4455,22 +4455,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.07320832316787845</v>
+        <v>0.07399239833032892</v>
       </c>
       <c r="C39">
-        <v>10845.48602280866</v>
+        <v>10237.02631440346</v>
       </c>
       <c r="D39">
-        <v>15864.38802280866</v>
+        <v>15423.17431440346</v>
       </c>
       <c r="E39">
-        <v>1846.401999999999</v>
+        <v>2013.648</v>
       </c>
       <c r="F39">
-        <v>6188.101999999999</v>
+        <v>6355.348</v>
       </c>
       <c r="G39">
         <v>1169.2</v>
@@ -4491,45 +4491,45 @@
         <v>1031.4</v>
       </c>
       <c r="M39">
-        <v>342.2020406</v>
+        <v>367.3391144</v>
       </c>
       <c r="N39">
-        <v>689.1979594000002</v>
+        <v>664.0608856000001</v>
       </c>
       <c r="O39">
-        <v>100.6229020724</v>
+        <v>96.95288929760001</v>
       </c>
       <c r="P39">
-        <v>588.5750573276001</v>
+        <v>567.1079963024001</v>
       </c>
       <c r="Q39">
-        <v>928.3750573276001</v>
+        <v>906.9079963024001</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.0884676653458388</v>
+        <v>0.089088939242466</v>
       </c>
       <c r="T39">
-        <v>0.9853964283103647</v>
+        <v>0.999744555253256</v>
       </c>
       <c r="U39">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V39">
         <v>0.146</v>
       </c>
       <c r="W39">
-        <v>0.0472262</v>
+        <v>0.0493612</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y39">
-        <v>3.014008911786718</v>
+        <v>2.807759804410309</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4537,22 +4537,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.07399239833032892</v>
+        <v>0.07398652349277939</v>
       </c>
       <c r="C40">
-        <v>10237.02631440346</v>
+        <v>10072.99492310178</v>
       </c>
       <c r="D40">
-        <v>15423.17431440346</v>
+        <v>15426.38892310178</v>
       </c>
       <c r="E40">
-        <v>2013.648</v>
+        <v>2180.894</v>
       </c>
       <c r="F40">
-        <v>6355.348</v>
+        <v>6522.594</v>
       </c>
       <c r="G40">
         <v>1169.2</v>
@@ -4573,28 +4573,28 @@
         <v>1031.4</v>
       </c>
       <c r="M40">
-        <v>367.3391144</v>
+        <v>377.0059332</v>
       </c>
       <c r="N40">
-        <v>664.0608856000001</v>
+        <v>654.3940668</v>
       </c>
       <c r="O40">
-        <v>96.95288929760001</v>
+        <v>95.54153375279999</v>
       </c>
       <c r="P40">
-        <v>567.1079963024001</v>
+        <v>558.8525330472</v>
       </c>
       <c r="Q40">
-        <v>906.9079963024001</v>
+        <v>898.6525330472</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.089088939242466</v>
+        <v>0.08973058277504817</v>
       </c>
       <c r="T40">
-        <v>0.999744555253256</v>
+        <v>1.014563112587717</v>
       </c>
       <c r="U40">
         <v>0.0578</v>
@@ -4611,7 +4611,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>2.807759804410309</v>
+        <v>2.735765963271583</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4619,22 +4619,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.07398652349277939</v>
+        <v>0.07398064865522985</v>
       </c>
       <c r="C41">
-        <v>10072.99492310178</v>
+        <v>9908.964872103094</v>
       </c>
       <c r="D41">
-        <v>15426.38892310178</v>
+        <v>15429.60487210309</v>
       </c>
       <c r="E41">
-        <v>2180.894</v>
+        <v>2348.14</v>
       </c>
       <c r="F41">
-        <v>6522.594</v>
+        <v>6689.84</v>
       </c>
       <c r="G41">
         <v>1169.2</v>
@@ -4655,28 +4655,28 @@
         <v>1031.4</v>
       </c>
       <c r="M41">
-        <v>377.0059332</v>
+        <v>386.6727520000001</v>
       </c>
       <c r="N41">
-        <v>654.3940668</v>
+        <v>644.727248</v>
       </c>
       <c r="O41">
-        <v>95.54153375279999</v>
+        <v>94.130178208</v>
       </c>
       <c r="P41">
-        <v>558.8525330472</v>
+        <v>550.5970697920001</v>
       </c>
       <c r="Q41">
-        <v>898.6525330472</v>
+        <v>890.397069792</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.08973058277504817</v>
+        <v>0.0903936144253831</v>
       </c>
       <c r="T41">
-        <v>1.014563112587717</v>
+        <v>1.029875621833328</v>
       </c>
       <c r="U41">
         <v>0.0578</v>
@@ -4693,7 +4693,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>2.735765963271583</v>
+        <v>2.667371814189793</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4701,22 +4701,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.07398064865522985</v>
+        <v>0.07397477381768033</v>
       </c>
       <c r="C42">
-        <v>9908.964872103094</v>
+        <v>9744.936162245809</v>
       </c>
       <c r="D42">
-        <v>15429.60487210309</v>
+        <v>15432.82216224581</v>
       </c>
       <c r="E42">
-        <v>2348.14</v>
+        <v>2515.386</v>
       </c>
       <c r="F42">
-        <v>6689.84</v>
+        <v>6857.086</v>
       </c>
       <c r="G42">
         <v>1169.2</v>
@@ -4737,28 +4737,28 @@
         <v>1031.4</v>
       </c>
       <c r="M42">
-        <v>386.6727520000001</v>
+        <v>396.3395708</v>
       </c>
       <c r="N42">
-        <v>644.727248</v>
+        <v>635.0604292</v>
       </c>
       <c r="O42">
-        <v>94.130178208</v>
+        <v>92.7188226632</v>
       </c>
       <c r="P42">
-        <v>550.5970697920001</v>
+        <v>542.3416065368001</v>
       </c>
       <c r="Q42">
-        <v>890.397069792</v>
+        <v>882.1416065368001</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.0903936144253831</v>
+        <v>0.09107912172488192</v>
       </c>
       <c r="T42">
-        <v>1.029875621833328</v>
+        <v>1.045707199188959</v>
       </c>
       <c r="U42">
         <v>0.0578</v>
@@ -4775,7 +4775,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>2.667371814189793</v>
+        <v>2.602313965063213</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4783,22 +4783,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.07397477381768033</v>
+        <v>0.0739688989801308</v>
       </c>
       <c r="C43">
-        <v>9744.936162245809</v>
+        <v>9580.908794369059</v>
       </c>
       <c r="D43">
-        <v>15432.82216224581</v>
+        <v>15436.04079436906</v>
       </c>
       <c r="E43">
-        <v>2515.386</v>
+        <v>2682.632000000001</v>
       </c>
       <c r="F43">
-        <v>6857.086</v>
+        <v>7024.332</v>
       </c>
       <c r="G43">
         <v>1169.2</v>
@@ -4819,28 +4819,28 @@
         <v>1031.4</v>
       </c>
       <c r="M43">
-        <v>396.3395708</v>
+        <v>406.0063896</v>
       </c>
       <c r="N43">
-        <v>635.0604292</v>
+        <v>625.3936104000001</v>
       </c>
       <c r="O43">
-        <v>92.7188226632</v>
+        <v>91.3074671184</v>
       </c>
       <c r="P43">
-        <v>542.3416065368001</v>
+        <v>534.0861432816</v>
       </c>
       <c r="Q43">
-        <v>882.1416065368001</v>
+        <v>873.8861432816</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.09107912172488192</v>
+        <v>0.09178826720712208</v>
       </c>
       <c r="T43">
-        <v>1.045707199188959</v>
+        <v>1.062084693005129</v>
       </c>
       <c r="U43">
         <v>0.0578</v>
@@ -4857,7 +4857,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>2.602313965063213</v>
+        <v>2.540354108752184</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4865,22 +4865,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.07396889898013081</v>
+        <v>0.07524829414258127</v>
       </c>
       <c r="C44">
-        <v>9580.908794369054</v>
+        <v>8743.036651337305</v>
       </c>
       <c r="D44">
-        <v>15436.04079436905</v>
+        <v>14765.4146513373</v>
       </c>
       <c r="E44">
-        <v>2682.632</v>
+        <v>2849.878</v>
       </c>
       <c r="F44">
-        <v>7024.331999999999</v>
+        <v>7191.578</v>
       </c>
       <c r="G44">
         <v>1169.2</v>
@@ -4901,45 +4901,45 @@
         <v>1031.4</v>
       </c>
       <c r="M44">
-        <v>406.0063896</v>
+        <v>440.8437314</v>
       </c>
       <c r="N44">
-        <v>625.3936104000002</v>
+        <v>590.5562686000001</v>
       </c>
       <c r="O44">
-        <v>91.30746711840001</v>
+        <v>86.2212152156</v>
       </c>
       <c r="P44">
-        <v>534.0861432816001</v>
+        <v>504.3350533844001</v>
       </c>
       <c r="Q44">
-        <v>873.8861432816001</v>
+        <v>844.1350533844</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.09178826720712208</v>
+        <v>0.09252229498698469</v>
       </c>
       <c r="T44">
-        <v>1.062084693005128</v>
+        <v>1.079036835727129</v>
       </c>
       <c r="U44">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V44">
         <v>0.146</v>
       </c>
       <c r="W44">
-        <v>0.0493612</v>
+        <v>0.0523502</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y44">
-        <v>2.540354108752185</v>
+        <v>2.339604550402823</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4947,22 +4947,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.07524829414258127</v>
+        <v>0.07527230930503176</v>
       </c>
       <c r="C45">
-        <v>8743.036651337305</v>
+        <v>8563.759227948296</v>
       </c>
       <c r="D45">
-        <v>14765.4146513373</v>
+        <v>14753.3832279483</v>
       </c>
       <c r="E45">
-        <v>2849.878</v>
+        <v>3017.124</v>
       </c>
       <c r="F45">
-        <v>7191.578</v>
+        <v>7358.824</v>
       </c>
       <c r="G45">
         <v>1169.2</v>
@@ -4983,28 +4983,28 @@
         <v>1031.4</v>
       </c>
       <c r="M45">
-        <v>440.8437314</v>
+        <v>451.0959112</v>
       </c>
       <c r="N45">
-        <v>590.5562686000001</v>
+        <v>580.3040888</v>
       </c>
       <c r="O45">
-        <v>86.2212152156</v>
+        <v>84.72439696480001</v>
       </c>
       <c r="P45">
-        <v>504.3350533844001</v>
+        <v>495.5796918352</v>
       </c>
       <c r="Q45">
-        <v>844.1350533844</v>
+        <v>835.3796918352</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.09252229498698469</v>
+        <v>0.09328253804469955</v>
       </c>
       <c r="T45">
-        <v>1.079036835727129</v>
+        <v>1.096594412117772</v>
       </c>
       <c r="U45">
         <v>0.0613</v>
@@ -5021,7 +5021,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>2.339604550402823</v>
+        <v>2.28643171971185</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5029,22 +5029,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.07527230930503176</v>
+        <v>0.07637236446748222</v>
       </c>
       <c r="C46">
-        <v>8563.759227948296</v>
+        <v>7865.656826547718</v>
       </c>
       <c r="D46">
-        <v>14753.3832279483</v>
+        <v>14222.52682654772</v>
       </c>
       <c r="E46">
-        <v>3017.124</v>
+        <v>3184.37</v>
       </c>
       <c r="F46">
-        <v>7358.824</v>
+        <v>7526.07</v>
       </c>
       <c r="G46">
         <v>1169.2</v>
@@ -5065,45 +5065,45 @@
         <v>1031.4</v>
       </c>
       <c r="M46">
-        <v>451.0959112</v>
+        <v>482.421087</v>
       </c>
       <c r="N46">
-        <v>580.3040888</v>
+        <v>548.9789130000001</v>
       </c>
       <c r="O46">
-        <v>84.72439696480001</v>
+        <v>80.15092129800001</v>
       </c>
       <c r="P46">
-        <v>495.5796918352</v>
+        <v>468.8279917020001</v>
       </c>
       <c r="Q46">
-        <v>835.3796918352</v>
+        <v>808.6279917020001</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.09328253804469955</v>
+        <v>0.09407042630451312</v>
       </c>
       <c r="T46">
-        <v>1.096594412117772</v>
+        <v>1.114790445831712</v>
       </c>
       <c r="U46">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V46">
         <v>0.146</v>
       </c>
       <c r="W46">
-        <v>0.0523502</v>
+        <v>0.0547414</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y46">
-        <v>2.28643171971185</v>
+        <v>2.137966245244168</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5111,22 +5111,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.07637236446748222</v>
+        <v>0.07642029162993269</v>
       </c>
       <c r="C47">
-        <v>7865.656826547718</v>
+        <v>7676.149596579357</v>
       </c>
       <c r="D47">
-        <v>14222.52682654772</v>
+        <v>14200.26559657936</v>
       </c>
       <c r="E47">
-        <v>3184.37</v>
+        <v>3351.616</v>
       </c>
       <c r="F47">
-        <v>7526.07</v>
+        <v>7693.316</v>
       </c>
       <c r="G47">
         <v>1169.2</v>
@@ -5147,28 +5147,28 @@
         <v>1031.4</v>
       </c>
       <c r="M47">
-        <v>482.421087</v>
+        <v>493.1415556</v>
       </c>
       <c r="N47">
-        <v>548.9789130000001</v>
+        <v>538.2584444000001</v>
       </c>
       <c r="O47">
-        <v>80.15092129800001</v>
+        <v>78.58573288240001</v>
       </c>
       <c r="P47">
-        <v>468.8279917020001</v>
+        <v>459.6727115176001</v>
       </c>
       <c r="Q47">
-        <v>808.6279917020001</v>
+        <v>799.4727115176001</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.09407042630451312</v>
+        <v>0.09488749561098646</v>
       </c>
       <c r="T47">
-        <v>1.114790445831712</v>
+        <v>1.133660406720241</v>
       </c>
       <c r="U47">
         <v>0.0641</v>
@@ -5185,7 +5185,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>2.137966245244168</v>
+        <v>2.091488718173642</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5193,22 +5193,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.07642029162993269</v>
+        <v>0.07646821879238316</v>
       </c>
       <c r="C48">
-        <v>7676.149596579357</v>
+        <v>7486.711944671091</v>
       </c>
       <c r="D48">
-        <v>14200.26559657936</v>
+        <v>14178.07394467109</v>
       </c>
       <c r="E48">
-        <v>3351.616</v>
+        <v>3518.862</v>
       </c>
       <c r="F48">
-        <v>7693.316</v>
+        <v>7860.562</v>
       </c>
       <c r="G48">
         <v>1169.2</v>
@@ -5229,28 +5229,28 @@
         <v>1031.4</v>
       </c>
       <c r="M48">
-        <v>493.1415556</v>
+        <v>503.8620242</v>
       </c>
       <c r="N48">
-        <v>538.2584444000001</v>
+        <v>527.5379758000001</v>
       </c>
       <c r="O48">
-        <v>78.58573288240001</v>
+        <v>77.02054446680002</v>
       </c>
       <c r="P48">
-        <v>459.6727115176001</v>
+        <v>450.5174313332001</v>
       </c>
       <c r="Q48">
-        <v>799.4727115176001</v>
+        <v>790.3174313332001</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.09488749561098646</v>
+        <v>0.09573539772147766</v>
       </c>
       <c r="T48">
-        <v>1.133660406720241</v>
+        <v>1.153242441604565</v>
       </c>
       <c r="U48">
         <v>0.0641</v>
@@ -5267,7 +5267,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>2.091488718173642</v>
+        <v>2.046988958212501</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5275,22 +5275,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.07646821879238316</v>
+        <v>0.07651614595483364</v>
       </c>
       <c r="C49">
-        <v>7486.711944671091</v>
+        <v>7297.343545129811</v>
       </c>
       <c r="D49">
-        <v>14178.07394467109</v>
+        <v>14155.95154512981</v>
       </c>
       <c r="E49">
-        <v>3518.862</v>
+        <v>3686.108</v>
       </c>
       <c r="F49">
-        <v>7860.562</v>
+        <v>8027.808</v>
       </c>
       <c r="G49">
         <v>1169.2</v>
@@ -5311,28 +5311,28 @@
         <v>1031.4</v>
       </c>
       <c r="M49">
-        <v>503.8620242</v>
+        <v>514.5824928000001</v>
       </c>
       <c r="N49">
-        <v>527.5379758000001</v>
+        <v>516.8175072</v>
       </c>
       <c r="O49">
-        <v>77.02054446680002</v>
+        <v>75.4553560512</v>
       </c>
       <c r="P49">
-        <v>450.5174313332001</v>
+        <v>441.3621511488</v>
       </c>
       <c r="Q49">
-        <v>790.3174313332001</v>
+        <v>781.1621511487999</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.09573539772147766</v>
+        <v>0.09661591145160314</v>
       </c>
       <c r="T49">
-        <v>1.153242441604565</v>
+        <v>1.173577631676747</v>
       </c>
       <c r="U49">
         <v>0.0641</v>
@@ -5349,7 +5349,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>2.046988958212501</v>
+        <v>2.004343354916407</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5357,22 +5357,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.07651614595483364</v>
+        <v>0.0798280611172841</v>
       </c>
       <c r="C50">
-        <v>7297.343545129812</v>
+        <v>5752.313768392214</v>
       </c>
       <c r="D50">
-        <v>14155.95154512981</v>
+        <v>12778.16776839221</v>
       </c>
       <c r="E50">
-        <v>3686.107999999999</v>
+        <v>3853.353999999998</v>
       </c>
       <c r="F50">
-        <v>8027.807999999999</v>
+        <v>8195.053999999998</v>
       </c>
       <c r="G50">
         <v>1169.2</v>
@@ -5393,45 +5393,45 @@
         <v>1031.4</v>
       </c>
       <c r="M50">
-        <v>514.5824928</v>
+        <v>589.2243825999999</v>
       </c>
       <c r="N50">
-        <v>516.8175072000001</v>
+        <v>442.1756174000002</v>
       </c>
       <c r="O50">
-        <v>75.45535605120001</v>
+        <v>64.55764014040003</v>
       </c>
       <c r="P50">
-        <v>441.3621511488001</v>
+        <v>377.6179772596001</v>
       </c>
       <c r="Q50">
-        <v>781.1621511488001</v>
+        <v>717.4179772596001</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.09661591145160314</v>
+        <v>0.09753095513192962</v>
       </c>
       <c r="T50">
-        <v>1.173577631676747</v>
+        <v>1.194710280183132</v>
       </c>
       <c r="U50">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V50">
         <v>0.146</v>
       </c>
       <c r="W50">
-        <v>0.0547414</v>
+        <v>0.0614026</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y50">
-        <v>2.004343354916408</v>
+        <v>1.750436727429481</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5439,22 +5439,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.0798280611172841</v>
+        <v>0.08160790027973458</v>
       </c>
       <c r="C51">
-        <v>5752.313768392214</v>
+        <v>4949.926270541855</v>
       </c>
       <c r="D51">
-        <v>12778.16776839221</v>
+        <v>12143.02627054185</v>
       </c>
       <c r="E51">
-        <v>3853.353999999998</v>
+        <v>4020.599999999999</v>
       </c>
       <c r="F51">
-        <v>8195.053999999998</v>
+        <v>8362.299999999999</v>
       </c>
       <c r="G51">
         <v>1169.2</v>
@@ -5475,45 +5475,45 @@
         <v>1031.4</v>
       </c>
       <c r="M51">
-        <v>589.2243825999999</v>
+        <v>633.86234</v>
       </c>
       <c r="N51">
-        <v>442.1756174000002</v>
+        <v>397.5376600000001</v>
       </c>
       <c r="O51">
-        <v>64.55764014040003</v>
+        <v>58.04049836000001</v>
       </c>
       <c r="P51">
-        <v>377.6179772596001</v>
+        <v>339.4971616400001</v>
       </c>
       <c r="Q51">
-        <v>717.4179772596001</v>
+        <v>679.29716164</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.09753095513192962</v>
+        <v>0.09848260055946916</v>
       </c>
       <c r="T51">
-        <v>1.194710280183132</v>
+        <v>1.216688234629772</v>
       </c>
       <c r="U51">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V51">
         <v>0.146</v>
       </c>
       <c r="W51">
-        <v>0.0614026</v>
+        <v>0.0647332</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y51">
-        <v>1.750436727429481</v>
+        <v>1.627167185859315</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5521,22 +5521,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.08160790027973458</v>
+        <v>0.08175574544218504</v>
       </c>
       <c r="C52">
-        <v>4949.926270541855</v>
+        <v>4732.749788791858</v>
       </c>
       <c r="D52">
-        <v>12143.02627054185</v>
+        <v>12093.09578879186</v>
       </c>
       <c r="E52">
-        <v>4020.599999999999</v>
+        <v>4187.846</v>
       </c>
       <c r="F52">
-        <v>8362.299999999999</v>
+        <v>8529.546</v>
       </c>
       <c r="G52">
         <v>1169.2</v>
@@ -5557,28 +5557,28 @@
         <v>1031.4</v>
       </c>
       <c r="M52">
-        <v>633.86234</v>
+        <v>646.5395868000001</v>
       </c>
       <c r="N52">
-        <v>397.5376600000001</v>
+        <v>384.8604132</v>
       </c>
       <c r="O52">
-        <v>58.04049836000001</v>
+        <v>56.1896203272</v>
       </c>
       <c r="P52">
-        <v>339.4971616400001</v>
+        <v>328.6707928728</v>
       </c>
       <c r="Q52">
-        <v>679.29716164</v>
+        <v>668.4707928728</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.09848260055946916</v>
+        <v>0.0994730886575205</v>
       </c>
       <c r="T52">
-        <v>1.216688234629772</v>
+        <v>1.239563248441582</v>
       </c>
       <c r="U52">
         <v>0.07580000000000001</v>
@@ -5595,7 +5595,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>1.627167185859315</v>
+        <v>1.595261946920897</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5603,22 +5603,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.08175574544218504</v>
+        <v>0.08190359060463552</v>
       </c>
       <c r="C53">
-        <v>4732.749788791858</v>
+        <v>4515.982240339736</v>
       </c>
       <c r="D53">
-        <v>12093.09578879186</v>
+        <v>12043.57424033973</v>
       </c>
       <c r="E53">
-        <v>4187.846</v>
+        <v>4355.092</v>
       </c>
       <c r="F53">
-        <v>8529.546</v>
+        <v>8696.791999999999</v>
       </c>
       <c r="G53">
         <v>1169.2</v>
@@ -5639,28 +5639,28 @@
         <v>1031.4</v>
       </c>
       <c r="M53">
-        <v>646.5395868000001</v>
+        <v>659.2168336</v>
       </c>
       <c r="N53">
-        <v>384.8604132</v>
+        <v>372.1831664000001</v>
       </c>
       <c r="O53">
-        <v>56.1896203272</v>
+        <v>54.33874229440001</v>
       </c>
       <c r="P53">
-        <v>328.6707928728</v>
+        <v>317.8444241056001</v>
       </c>
       <c r="Q53">
-        <v>668.4707928728</v>
+        <v>657.6444241056001</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.0994730886575205</v>
+        <v>0.1005048470929907</v>
       </c>
       <c r="T53">
-        <v>1.239563248441582</v>
+        <v>1.263391387828884</v>
       </c>
       <c r="U53">
         <v>0.07580000000000001</v>
@@ -5677,7 +5677,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>1.595261946920897</v>
+        <v>1.564583832557033</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5685,22 +5685,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.08190359060463552</v>
+        <v>0.082051435767086</v>
       </c>
       <c r="C54">
-        <v>4515.982240339736</v>
+        <v>4299.618621895941</v>
       </c>
       <c r="D54">
-        <v>12043.57424033973</v>
+        <v>11994.45662189594</v>
       </c>
       <c r="E54">
-        <v>4355.092</v>
+        <v>4522.338000000001</v>
       </c>
       <c r="F54">
-        <v>8696.791999999999</v>
+        <v>8864.038</v>
       </c>
       <c r="G54">
         <v>1169.2</v>
@@ -5721,28 +5721,28 @@
         <v>1031.4</v>
       </c>
       <c r="M54">
-        <v>659.2168336</v>
+        <v>671.8940804000001</v>
       </c>
       <c r="N54">
-        <v>372.1831664000001</v>
+        <v>359.5059196</v>
       </c>
       <c r="O54">
-        <v>54.33874229440001</v>
+        <v>52.4878642616</v>
       </c>
       <c r="P54">
-        <v>317.8444241056001</v>
+        <v>307.0180553384</v>
       </c>
       <c r="Q54">
-        <v>657.6444241056001</v>
+        <v>646.8180553384</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1005048470929907</v>
+        <v>0.1015805101427362</v>
       </c>
       <c r="T54">
-        <v>1.263391387828884</v>
+        <v>1.288233490594368</v>
       </c>
       <c r="U54">
         <v>0.07580000000000001</v>
@@ -5759,7 +5759,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>1.564583832557033</v>
+        <v>1.535063382886146</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5767,22 +5767,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.082051435767086</v>
+        <v>0.08219928092953646</v>
       </c>
       <c r="C55">
-        <v>4299.618621895941</v>
+        <v>4083.654011459595</v>
       </c>
       <c r="D55">
-        <v>11994.45662189594</v>
+        <v>11945.73801145959</v>
       </c>
       <c r="E55">
-        <v>4522.338000000001</v>
+        <v>4689.584</v>
       </c>
       <c r="F55">
-        <v>8864.038</v>
+        <v>9031.284</v>
       </c>
       <c r="G55">
         <v>1169.2</v>
@@ -5803,28 +5803,28 @@
         <v>1031.4</v>
       </c>
       <c r="M55">
-        <v>671.8940804000001</v>
+        <v>684.5713272</v>
       </c>
       <c r="N55">
-        <v>359.5059196</v>
+        <v>346.8286728</v>
       </c>
       <c r="O55">
-        <v>52.4878642616</v>
+        <v>50.6369862288</v>
       </c>
       <c r="P55">
-        <v>307.0180553384</v>
+        <v>296.1916865712</v>
       </c>
       <c r="Q55">
-        <v>646.8180553384</v>
+        <v>635.9916865712</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1015805101427362</v>
+        <v>0.1027029411511662</v>
       </c>
       <c r="T55">
-        <v>1.288233490594368</v>
+        <v>1.314155684784439</v>
       </c>
       <c r="U55">
         <v>0.07580000000000001</v>
@@ -5841,7 +5841,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>1.535063382886146</v>
+        <v>1.506636283203069</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5849,22 +5849,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.08219928092953646</v>
+        <v>0.1030946423801973</v>
       </c>
       <c r="C56">
-        <v>4083.654011459595</v>
+        <v>-440.2037619061339</v>
       </c>
       <c r="D56">
-        <v>11945.73801145959</v>
+        <v>7589.126238093867</v>
       </c>
       <c r="E56">
-        <v>4689.584</v>
+        <v>4856.830000000001</v>
       </c>
       <c r="F56">
-        <v>9031.284</v>
+        <v>9198.530000000001</v>
       </c>
       <c r="G56">
         <v>1169.2</v>
@@ -5885,45 +5885,45 @@
         <v>1031.4</v>
       </c>
       <c r="M56">
-        <v>684.5713272</v>
+        <v>1090.945658</v>
       </c>
       <c r="N56">
-        <v>346.8286728</v>
+        <v>-59.545658</v>
       </c>
       <c r="O56">
-        <v>50.6369862288</v>
+        <v>-8.693666068000001</v>
       </c>
       <c r="P56">
-        <v>296.1916865712</v>
+        <v>-50.851991932</v>
       </c>
       <c r="Q56">
-        <v>635.9916865712</v>
+        <v>288.9480080679999</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1027029411511662</v>
+        <v>0.1041520206365138</v>
       </c>
       <c r="T56">
-        <v>1.314155684784439</v>
+        <v>1.347621723707015</v>
       </c>
       <c r="U56">
-        <v>0.07580000000000001</v>
+        <v>0.1186</v>
       </c>
       <c r="V56">
-        <v>0.146</v>
+        <v>0.1380310732214308</v>
       </c>
       <c r="W56">
-        <v>0.0647332</v>
+        <v>0.1022295147159383</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y56">
-        <v>1.506636283203069</v>
+        <v>0.9454183097358274</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5931,22 +5931,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1030946423801973</v>
+        <v>0.1038226423801973</v>
       </c>
       <c r="C57">
-        <v>-440.2037619061339</v>
+        <v>-702.6692085685245</v>
       </c>
       <c r="D57">
-        <v>7589.126238093867</v>
+        <v>7493.906791431475</v>
       </c>
       <c r="E57">
-        <v>4856.830000000001</v>
+        <v>5024.076</v>
       </c>
       <c r="F57">
-        <v>9198.530000000001</v>
+        <v>9365.776</v>
       </c>
       <c r="G57">
         <v>1169.2</v>
@@ -5967,37 +5967,37 @@
         <v>1031.4</v>
       </c>
       <c r="M57">
-        <v>1090.945658</v>
+        <v>1110.7810336</v>
       </c>
       <c r="N57">
-        <v>-59.545658</v>
+        <v>-79.38103359999991</v>
       </c>
       <c r="O57">
-        <v>-8.693666068000001</v>
+        <v>-11.58963090559999</v>
       </c>
       <c r="P57">
-        <v>-50.851991932</v>
+        <v>-67.79140269439992</v>
       </c>
       <c r="Q57">
-        <v>288.9480080679999</v>
+        <v>272.0085973056</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1041520206365138</v>
+        <v>0.1054782029237073</v>
       </c>
       <c r="T57">
-        <v>1.347621723707015</v>
+        <v>1.378249490154902</v>
       </c>
       <c r="U57">
         <v>0.1186</v>
       </c>
       <c r="V57">
-        <v>0.1380310732214308</v>
+        <v>0.135566232628191</v>
       </c>
       <c r="W57">
-        <v>0.1022295147159383</v>
+        <v>0.1025218448102966</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -6005,7 +6005,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.9454183097358274</v>
+        <v>0.9285358399191163</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6013,22 +6013,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1038226423801973</v>
+        <v>0.1045506423801973</v>
       </c>
       <c r="C58">
-        <v>-702.6692085685245</v>
+        <v>-962.7748595125449</v>
       </c>
       <c r="D58">
-        <v>7493.906791431475</v>
+        <v>7401.047140487455</v>
       </c>
       <c r="E58">
-        <v>5024.076</v>
+        <v>5191.322000000001</v>
       </c>
       <c r="F58">
-        <v>9365.776</v>
+        <v>9533.022000000001</v>
       </c>
       <c r="G58">
         <v>1169.2</v>
@@ -6049,37 +6049,37 @@
         <v>1031.4</v>
       </c>
       <c r="M58">
-        <v>1110.7810336</v>
+        <v>1130.6164092</v>
       </c>
       <c r="N58">
-        <v>-79.38103359999991</v>
+        <v>-99.21640920000004</v>
       </c>
       <c r="O58">
-        <v>-11.58963090559999</v>
+        <v>-14.4855957432</v>
       </c>
       <c r="P58">
-        <v>-67.79140269439992</v>
+        <v>-84.73081345680004</v>
       </c>
       <c r="Q58">
-        <v>272.0085973056</v>
+        <v>255.0691865431999</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1054782029237073</v>
+        <v>0.1068660681079795</v>
       </c>
       <c r="T58">
-        <v>1.378249490154902</v>
+        <v>1.410301803879435</v>
       </c>
       <c r="U58">
         <v>0.1186</v>
       </c>
       <c r="V58">
-        <v>0.135566232628191</v>
+        <v>0.1331878776698016</v>
       </c>
       <c r="W58">
-        <v>0.1025218448102966</v>
+        <v>0.1028039177083615</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6087,7 +6087,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.9285358399191163</v>
+        <v>0.9122457374643949</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6095,22 +6095,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1045506423801973</v>
+        <v>0.1052786423801973</v>
       </c>
       <c r="C59">
-        <v>-962.7748595125449</v>
+        <v>-1220.607364225181</v>
       </c>
       <c r="D59">
-        <v>7401.047140487455</v>
+        <v>7310.460635774818</v>
       </c>
       <c r="E59">
-        <v>5191.322000000001</v>
+        <v>5358.568</v>
       </c>
       <c r="F59">
-        <v>9533.022000000001</v>
+        <v>9700.268</v>
       </c>
       <c r="G59">
         <v>1169.2</v>
@@ -6131,37 +6131,37 @@
         <v>1031.4</v>
       </c>
       <c r="M59">
-        <v>1130.6164092</v>
+        <v>1150.4517848</v>
       </c>
       <c r="N59">
-        <v>-99.21640920000004</v>
+        <v>-119.0517848</v>
       </c>
       <c r="O59">
-        <v>-14.4855957432</v>
+        <v>-17.38156058079999</v>
       </c>
       <c r="P59">
-        <v>-84.73081345680004</v>
+        <v>-101.6702242192</v>
       </c>
       <c r="Q59">
-        <v>255.0691865431999</v>
+        <v>238.1297757808</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1068660681079795</v>
+        <v>0.1083200221105505</v>
       </c>
       <c r="T59">
-        <v>1.410301803879435</v>
+        <v>1.443880418257517</v>
       </c>
       <c r="U59">
         <v>0.1186</v>
       </c>
       <c r="V59">
-        <v>0.1331878776698016</v>
+        <v>0.1308915349513568</v>
       </c>
       <c r="W59">
-        <v>0.1028039177083615</v>
+        <v>0.1030762639547691</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6169,7 +6169,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.9122457374643949</v>
+        <v>0.8965173626805261</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6177,22 +6177,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1052786423801973</v>
+        <v>0.1060066423801973</v>
       </c>
       <c r="C60">
-        <v>-1220.607364225179</v>
+        <v>-1476.249181238796</v>
       </c>
       <c r="D60">
-        <v>7310.460635774818</v>
+        <v>7222.064818761203</v>
       </c>
       <c r="E60">
-        <v>5358.567999999998</v>
+        <v>5525.813999999999</v>
       </c>
       <c r="F60">
-        <v>9700.267999999998</v>
+        <v>9867.513999999999</v>
       </c>
       <c r="G60">
         <v>1169.2</v>
@@ -6213,37 +6213,37 @@
         <v>1031.4</v>
       </c>
       <c r="M60">
-        <v>1150.4517848</v>
+        <v>1170.2871604</v>
       </c>
       <c r="N60">
-        <v>-119.0517847999997</v>
+        <v>-138.8871603999999</v>
       </c>
       <c r="O60">
-        <v>-17.38156058079996</v>
+        <v>-20.27752541839998</v>
       </c>
       <c r="P60">
-        <v>-101.6702242191998</v>
+        <v>-118.6096349815999</v>
       </c>
       <c r="Q60">
-        <v>238.1297757808002</v>
+        <v>221.1903650184001</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1083200221105505</v>
+        <v>0.1098449006986127</v>
       </c>
       <c r="T60">
-        <v>1.443880418257516</v>
+        <v>1.479097013824773</v>
       </c>
       <c r="U60">
         <v>0.1186</v>
       </c>
       <c r="V60">
-        <v>0.1308915349513568</v>
+        <v>0.1286730343589609</v>
       </c>
       <c r="W60">
-        <v>0.1030762639547691</v>
+        <v>0.1033393781250272</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6251,7 +6251,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.8965173626805262</v>
+        <v>0.881322153143568</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6259,22 +6259,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1060066423801973</v>
+        <v>0.1067346423801973</v>
       </c>
       <c r="C61">
-        <v>-1476.249181238796</v>
+        <v>-1729.778828482566</v>
       </c>
       <c r="D61">
-        <v>7222.064818761203</v>
+        <v>7135.781171517433</v>
       </c>
       <c r="E61">
-        <v>5525.813999999999</v>
+        <v>5693.059999999999</v>
       </c>
       <c r="F61">
-        <v>9867.513999999999</v>
+        <v>10034.76</v>
       </c>
       <c r="G61">
         <v>1169.2</v>
@@ -6295,37 +6295,37 @@
         <v>1031.4</v>
       </c>
       <c r="M61">
-        <v>1170.2871604</v>
+        <v>1190.122536</v>
       </c>
       <c r="N61">
-        <v>-138.8871603999999</v>
+        <v>-158.7225359999998</v>
       </c>
       <c r="O61">
-        <v>-20.27752541839998</v>
+        <v>-23.17349025599997</v>
       </c>
       <c r="P61">
-        <v>-118.6096349815999</v>
+        <v>-135.5490457439998</v>
       </c>
       <c r="Q61">
-        <v>221.1903650184001</v>
+        <v>204.2509542560002</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1098449006986127</v>
+        <v>0.111446023216078</v>
       </c>
       <c r="T61">
-        <v>1.479097013824773</v>
+        <v>1.516074439170392</v>
       </c>
       <c r="U61">
         <v>0.1186</v>
       </c>
       <c r="V61">
-        <v>0.1286730343589609</v>
+        <v>0.1265284837863116</v>
       </c>
       <c r="W61">
-        <v>0.1033393781250272</v>
+        <v>0.1035937218229435</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6333,7 +6333,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.881322153143568</v>
+        <v>0.8666334505911752</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6341,22 +6341,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1067346423801973</v>
+        <v>0.1074626423801973</v>
       </c>
       <c r="C62">
-        <v>-1729.778828482566</v>
+        <v>-1981.271115899741</v>
       </c>
       <c r="D62">
-        <v>7135.781171517433</v>
+        <v>7051.534884100258</v>
       </c>
       <c r="E62">
-        <v>5693.059999999999</v>
+        <v>5860.306</v>
       </c>
       <c r="F62">
-        <v>10034.76</v>
+        <v>10202.006</v>
       </c>
       <c r="G62">
         <v>1169.2</v>
@@ -6377,37 +6377,37 @@
         <v>1031.4</v>
       </c>
       <c r="M62">
-        <v>1190.122536</v>
+        <v>1209.9579116</v>
       </c>
       <c r="N62">
-        <v>-158.7225359999998</v>
+        <v>-178.5579115999999</v>
       </c>
       <c r="O62">
-        <v>-23.17349025599997</v>
+        <v>-26.06945509359998</v>
       </c>
       <c r="P62">
-        <v>-135.5490457439998</v>
+        <v>-152.4884565063999</v>
       </c>
       <c r="Q62">
-        <v>204.2509542560002</v>
+        <v>187.3115434936</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.111446023216078</v>
+        <v>0.1131292545805928</v>
       </c>
       <c r="T62">
-        <v>1.516074439170392</v>
+        <v>1.554948142738864</v>
       </c>
       <c r="U62">
         <v>0.1186</v>
       </c>
       <c r="V62">
-        <v>0.1265284837863116</v>
+        <v>0.1244542463471917</v>
       </c>
       <c r="W62">
-        <v>0.1035937218229435</v>
+        <v>0.1038397263832231</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6415,7 +6415,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.8666334505911752</v>
+        <v>0.8524263448437789</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6423,22 +6423,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1074626423801973</v>
+        <v>0.1081906423801973</v>
       </c>
       <c r="C63">
-        <v>-1981.271115899741</v>
+        <v>-2230.79736177928</v>
       </c>
       <c r="D63">
-        <v>7051.534884100258</v>
+        <v>6969.254638220719</v>
       </c>
       <c r="E63">
-        <v>5860.306</v>
+        <v>6027.551999999999</v>
       </c>
       <c r="F63">
-        <v>10202.006</v>
+        <v>10369.252</v>
       </c>
       <c r="G63">
         <v>1169.2</v>
@@ -6459,37 +6459,37 @@
         <v>1031.4</v>
       </c>
       <c r="M63">
-        <v>1209.9579116</v>
+        <v>1229.7932872</v>
       </c>
       <c r="N63">
-        <v>-178.5579115999999</v>
+        <v>-198.3932871999998</v>
       </c>
       <c r="O63">
-        <v>-26.06945509359998</v>
+        <v>-28.96541993119997</v>
       </c>
       <c r="P63">
-        <v>-152.4884565063999</v>
+        <v>-169.4278672687998</v>
       </c>
       <c r="Q63">
-        <v>187.3115434936</v>
+        <v>170.3721327312001</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1131292545805928</v>
+        <v>0.1149010770695558</v>
       </c>
       <c r="T63">
-        <v>1.554948142738864</v>
+        <v>1.595867830705676</v>
       </c>
       <c r="U63">
         <v>0.1186</v>
       </c>
       <c r="V63">
-        <v>0.1244542463471917</v>
+        <v>0.1224469197932048</v>
       </c>
       <c r="W63">
-        <v>0.1038397263832231</v>
+        <v>0.1040777953125259</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6497,7 +6497,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.8524263448437789</v>
+        <v>0.8386775328301697</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6505,22 +6505,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1081906423801973</v>
+        <v>0.1089186423801973</v>
       </c>
       <c r="C64">
-        <v>-2230.79736177928</v>
+        <v>-2478.425594116657</v>
       </c>
       <c r="D64">
-        <v>6969.254638220719</v>
+        <v>6888.872405883343</v>
       </c>
       <c r="E64">
-        <v>6027.551999999999</v>
+        <v>6194.798</v>
       </c>
       <c r="F64">
-        <v>10369.252</v>
+        <v>10536.498</v>
       </c>
       <c r="G64">
         <v>1169.2</v>
@@ -6541,37 +6541,37 @@
         <v>1031.4</v>
       </c>
       <c r="M64">
-        <v>1229.7932872</v>
+        <v>1249.6286628</v>
       </c>
       <c r="N64">
-        <v>-198.3932871999998</v>
+        <v>-218.2286627999999</v>
       </c>
       <c r="O64">
-        <v>-28.96541993119997</v>
+        <v>-31.86138476879999</v>
       </c>
       <c r="P64">
-        <v>-169.4278672687998</v>
+        <v>-186.3672780312</v>
       </c>
       <c r="Q64">
-        <v>170.3721327312001</v>
+        <v>153.4327219688</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1149010770695558</v>
+        <v>0.1167686737471114</v>
       </c>
       <c r="T64">
-        <v>1.595867830705676</v>
+        <v>1.638999393697722</v>
       </c>
       <c r="U64">
         <v>0.1186</v>
       </c>
       <c r="V64">
-        <v>0.1224469197932048</v>
+        <v>0.1205033178917253</v>
       </c>
       <c r="W64">
-        <v>0.1040777953125259</v>
+        <v>0.1043083064980414</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6579,7 +6579,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.8386775328301697</v>
+        <v>0.8253651910392145</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6587,22 +6587,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1089186423801973</v>
+        <v>0.1096466423801973</v>
       </c>
       <c r="C65">
-        <v>-2478.425594116657</v>
+        <v>-2724.220738198795</v>
       </c>
       <c r="D65">
-        <v>6888.872405883343</v>
+        <v>6810.323261801204</v>
       </c>
       <c r="E65">
-        <v>6194.798</v>
+        <v>6362.043999999999</v>
       </c>
       <c r="F65">
-        <v>10536.498</v>
+        <v>10703.744</v>
       </c>
       <c r="G65">
         <v>1169.2</v>
@@ -6623,37 +6623,37 @@
         <v>1031.4</v>
       </c>
       <c r="M65">
-        <v>1249.6286628</v>
+        <v>1269.4640384</v>
       </c>
       <c r="N65">
-        <v>-218.2286627999999</v>
+        <v>-238.0640383999998</v>
       </c>
       <c r="O65">
-        <v>-31.86138476879999</v>
+        <v>-34.75734960639998</v>
       </c>
       <c r="P65">
-        <v>-186.3672780312</v>
+        <v>-203.3066887935999</v>
       </c>
       <c r="Q65">
-        <v>153.4327219688</v>
+        <v>136.4933112064001</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1167686737471114</v>
+        <v>0.1187400257956422</v>
       </c>
       <c r="T65">
-        <v>1.638999393697722</v>
+        <v>1.684527154633769</v>
       </c>
       <c r="U65">
         <v>0.1186</v>
       </c>
       <c r="V65">
-        <v>0.1205033178917253</v>
+        <v>0.1186204535496671</v>
       </c>
       <c r="W65">
-        <v>0.1043083064980414</v>
+        <v>0.1045316142090095</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6661,7 +6661,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.8253651910392145</v>
+        <v>0.8124688599292268</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6669,22 +6669,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1096466423801973</v>
+        <v>0.1646877327286938</v>
       </c>
       <c r="C66">
-        <v>-2724.220738198795</v>
+        <v>-6044.421289116877</v>
       </c>
       <c r="D66">
-        <v>6810.323261801204</v>
+        <v>3657.368710883123</v>
       </c>
       <c r="E66">
-        <v>6362.043999999999</v>
+        <v>6529.29</v>
       </c>
       <c r="F66">
-        <v>10703.744</v>
+        <v>10870.99</v>
       </c>
       <c r="G66">
         <v>1169.2</v>
@@ -6705,45 +6705,45 @@
         <v>1031.4</v>
       </c>
       <c r="M66">
-        <v>1269.4640384</v>
+        <v>2182.894792</v>
       </c>
       <c r="N66">
-        <v>-238.0640383999998</v>
+        <v>-1151.494792</v>
       </c>
       <c r="O66">
-        <v>-34.75734960639998</v>
+        <v>-168.118239632</v>
       </c>
       <c r="P66">
-        <v>-203.3066887935999</v>
+        <v>-983.3765523679999</v>
       </c>
       <c r="Q66">
-        <v>136.4933112064001</v>
+        <v>-643.576552368</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1187400257956422</v>
+        <v>0.1233471418140792</v>
       </c>
       <c r="T66">
-        <v>1.684527154633769</v>
+        <v>1.790927062680812</v>
       </c>
       <c r="U66">
-        <v>0.1186</v>
+        <v>0.2008</v>
       </c>
       <c r="V66">
-        <v>0.1186204535496671</v>
+        <v>0.06898381019180148</v>
       </c>
       <c r="W66">
-        <v>0.1045316142090095</v>
+        <v>0.1869480509134863</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y66">
-        <v>0.8124688599292268</v>
+        <v>0.4724918506287774</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6751,22 +6751,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1646877327286938</v>
+        <v>0.1662377327286938</v>
       </c>
       <c r="C67">
-        <v>-6044.421289116877</v>
+        <v>-6258.736603470702</v>
       </c>
       <c r="D67">
-        <v>3657.368710883123</v>
+        <v>3610.299396529297</v>
       </c>
       <c r="E67">
-        <v>6529.29</v>
+        <v>6696.535999999999</v>
       </c>
       <c r="F67">
-        <v>10870.99</v>
+        <v>11038.236</v>
       </c>
       <c r="G67">
         <v>1169.2</v>
@@ -6787,37 +6787,37 @@
         <v>1031.4</v>
       </c>
       <c r="M67">
-        <v>2182.894792</v>
+        <v>2216.4777888</v>
       </c>
       <c r="N67">
-        <v>-1151.494792</v>
+        <v>-1185.0777888</v>
       </c>
       <c r="O67">
-        <v>-168.118239632</v>
+        <v>-173.0213571648</v>
       </c>
       <c r="P67">
-        <v>-983.3765523679999</v>
+        <v>-1012.0564316352</v>
       </c>
       <c r="Q67">
-        <v>-643.576552368</v>
+        <v>-672.2564316351999</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1233471418140792</v>
+        <v>0.1256279401027285</v>
       </c>
       <c r="T67">
-        <v>1.790927062680812</v>
+        <v>1.843601388053777</v>
       </c>
       <c r="U67">
         <v>0.2008</v>
       </c>
       <c r="V67">
-        <v>0.06898381019180148</v>
+        <v>0.06793860094647117</v>
       </c>
       <c r="W67">
-        <v>0.1869480509134863</v>
+        <v>0.1871579289299486</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6825,7 +6825,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.4724918506287774</v>
+        <v>0.4653328831950081</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6833,22 +6833,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1662377327286938</v>
+        <v>0.1677877327286938</v>
       </c>
       <c r="C68">
-        <v>-6258.736603470702</v>
+        <v>-6471.855773989136</v>
       </c>
       <c r="D68">
-        <v>3610.299396529297</v>
+        <v>3564.426226010864</v>
       </c>
       <c r="E68">
-        <v>6696.535999999999</v>
+        <v>6863.782</v>
       </c>
       <c r="F68">
-        <v>11038.236</v>
+        <v>11205.482</v>
       </c>
       <c r="G68">
         <v>1169.2</v>
@@ -6869,37 +6869,37 @@
         <v>1031.4</v>
       </c>
       <c r="M68">
-        <v>2216.4777888</v>
+        <v>2250.0607856</v>
       </c>
       <c r="N68">
-        <v>-1185.0777888</v>
+        <v>-1218.6607856</v>
       </c>
       <c r="O68">
-        <v>-173.0213571648</v>
+        <v>-177.9244746976</v>
       </c>
       <c r="P68">
-        <v>-1012.0564316352</v>
+        <v>-1040.7363109024</v>
       </c>
       <c r="Q68">
-        <v>-672.2564316351999</v>
+        <v>-700.9363109024</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1256279401027285</v>
+        <v>0.12804696859069</v>
       </c>
       <c r="T68">
-        <v>1.843601388053777</v>
+        <v>1.899468096782679</v>
       </c>
       <c r="U68">
         <v>0.2008</v>
       </c>
       <c r="V68">
-        <v>0.06793860094647117</v>
+        <v>0.06692459197712085</v>
       </c>
       <c r="W68">
-        <v>0.1871579289299486</v>
+        <v>0.1873615419309941</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6907,7 +6907,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.4653328831950081</v>
+        <v>0.4583876162816497</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6915,22 +6915,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1677877327286938</v>
+        <v>0.1693377327286938</v>
       </c>
       <c r="C69">
-        <v>-6471.855773989136</v>
+        <v>-6683.823823910921</v>
       </c>
       <c r="D69">
-        <v>3564.426226010864</v>
+        <v>3519.704176089078</v>
       </c>
       <c r="E69">
-        <v>6863.782</v>
+        <v>7031.027999999999</v>
       </c>
       <c r="F69">
-        <v>11205.482</v>
+        <v>11372.728</v>
       </c>
       <c r="G69">
         <v>1169.2</v>
@@ -6951,37 +6951,37 @@
         <v>1031.4</v>
       </c>
       <c r="M69">
-        <v>2250.0607856</v>
+        <v>2283.6437824</v>
       </c>
       <c r="N69">
-        <v>-1218.6607856</v>
+        <v>-1252.2437824</v>
       </c>
       <c r="O69">
-        <v>-177.9244746976</v>
+        <v>-182.8275922304</v>
       </c>
       <c r="P69">
-        <v>-1040.7363109024</v>
+        <v>-1069.4161901696</v>
       </c>
       <c r="Q69">
-        <v>-700.9363109024</v>
+        <v>-729.6161901696</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.12804696859069</v>
+        <v>0.1306171863591491</v>
       </c>
       <c r="T69">
-        <v>1.899468096782679</v>
+        <v>1.958826474807138</v>
       </c>
       <c r="U69">
         <v>0.2008</v>
       </c>
       <c r="V69">
-        <v>0.06692459197712085</v>
+        <v>0.06594040680098673</v>
       </c>
       <c r="W69">
-        <v>0.1873615419309941</v>
+        <v>0.1875591663143619</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6989,7 +6989,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.4583876162816497</v>
+        <v>0.4516466219245666</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6997,22 +6997,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1693377327286938</v>
+        <v>0.1708877327286938</v>
       </c>
       <c r="C70">
-        <v>-6683.823823910921</v>
+        <v>-6894.683544888429</v>
       </c>
       <c r="D70">
-        <v>3519.704176089078</v>
+        <v>3476.090455111572</v>
       </c>
       <c r="E70">
-        <v>7031.027999999999</v>
+        <v>7198.274</v>
       </c>
       <c r="F70">
-        <v>11372.728</v>
+        <v>11539.974</v>
       </c>
       <c r="G70">
         <v>1169.2</v>
@@ -7033,37 +7033,37 @@
         <v>1031.4</v>
       </c>
       <c r="M70">
-        <v>2283.6437824</v>
+        <v>2317.2267792</v>
       </c>
       <c r="N70">
-        <v>-1252.2437824</v>
+        <v>-1285.8267792</v>
       </c>
       <c r="O70">
-        <v>-182.8275922304</v>
+        <v>-187.7307097632</v>
       </c>
       <c r="P70">
-        <v>-1069.4161901696</v>
+        <v>-1098.0960694368</v>
       </c>
       <c r="Q70">
-        <v>-729.6161901696</v>
+        <v>-758.2960694368003</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1306171863591491</v>
+        <v>0.1333532246287991</v>
       </c>
       <c r="T70">
-        <v>1.958826474807138</v>
+        <v>2.022014425607368</v>
       </c>
       <c r="U70">
         <v>0.2008</v>
       </c>
       <c r="V70">
-        <v>0.06594040680098673</v>
+        <v>0.06498474873140719</v>
       </c>
       <c r="W70">
-        <v>0.1875591663143619</v>
+        <v>0.1877510624547334</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7071,7 +7071,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.4516466219245666</v>
+        <v>0.4451010187082685</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7079,22 +7079,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1708877327286938</v>
+        <v>0.1724377327286938</v>
       </c>
       <c r="C71">
-        <v>-6894.683544888429</v>
+        <v>-7104.475633556691</v>
       </c>
       <c r="D71">
-        <v>3476.090455111572</v>
+        <v>3433.544366443309</v>
       </c>
       <c r="E71">
-        <v>7198.274</v>
+        <v>7365.52</v>
       </c>
       <c r="F71">
-        <v>11539.974</v>
+        <v>11707.22</v>
       </c>
       <c r="G71">
         <v>1169.2</v>
@@ -7115,37 +7115,37 @@
         <v>1031.4</v>
       </c>
       <c r="M71">
-        <v>2317.2267792</v>
+        <v>2350.809776</v>
       </c>
       <c r="N71">
-        <v>-1285.8267792</v>
+        <v>-1319.409776</v>
       </c>
       <c r="O71">
-        <v>-187.7307097632</v>
+        <v>-192.633827296</v>
       </c>
       <c r="P71">
-        <v>-1098.0960694368</v>
+        <v>-1126.775948704</v>
       </c>
       <c r="Q71">
-        <v>-758.2960694368003</v>
+        <v>-786.9759487040001</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1333532246287991</v>
+        <v>0.136271665449759</v>
       </c>
       <c r="T71">
-        <v>2.022014425607368</v>
+        <v>2.089414906460947</v>
       </c>
       <c r="U71">
         <v>0.2008</v>
       </c>
       <c r="V71">
-        <v>0.06498474873140719</v>
+        <v>0.06405639517810138</v>
       </c>
       <c r="W71">
-        <v>0.1877510624547334</v>
+        <v>0.1879374758482373</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7153,7 +7153,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.4451010187082685</v>
+        <v>0.4387424327267219</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7161,22 +7161,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1724377327286938</v>
+        <v>0.1739877327286938</v>
       </c>
       <c r="C72">
-        <v>-7104.475633556691</v>
+        <v>-7313.238818194406</v>
       </c>
       <c r="D72">
-        <v>3433.544366443309</v>
+        <v>3392.027181805594</v>
       </c>
       <c r="E72">
-        <v>7365.52</v>
+        <v>7532.766000000001</v>
       </c>
       <c r="F72">
-        <v>11707.22</v>
+        <v>11874.466</v>
       </c>
       <c r="G72">
         <v>1169.2</v>
@@ -7197,37 +7197,37 @@
         <v>1031.4</v>
       </c>
       <c r="M72">
-        <v>2350.809776</v>
+        <v>2384.3927728</v>
       </c>
       <c r="N72">
-        <v>-1319.409776</v>
+        <v>-1352.9927728</v>
       </c>
       <c r="O72">
-        <v>-192.633827296</v>
+        <v>-197.5369448288</v>
       </c>
       <c r="P72">
-        <v>-1126.775948704</v>
+        <v>-1155.4558279712</v>
       </c>
       <c r="Q72">
-        <v>-786.9759487040001</v>
+        <v>-815.6558279712003</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.136271665449759</v>
+        <v>0.1393913780514749</v>
       </c>
       <c r="T72">
-        <v>2.089414906460947</v>
+        <v>2.161463696338911</v>
       </c>
       <c r="U72">
         <v>0.2008</v>
       </c>
       <c r="V72">
-        <v>0.06405639517810138</v>
+        <v>0.06315419242911403</v>
       </c>
       <c r="W72">
-        <v>0.1879374758482373</v>
+        <v>0.1881186381602339</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7235,7 +7235,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.4387424327267219</v>
+        <v>0.4325629618432468</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7243,22 +7243,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1739877327286938</v>
+        <v>0.1755377327286938</v>
       </c>
       <c r="C73">
-        <v>-7313.238818194404</v>
+        <v>-7521.009976305447</v>
       </c>
       <c r="D73">
-        <v>3392.027181805594</v>
+        <v>3351.502023694551</v>
       </c>
       <c r="E73">
-        <v>7532.765999999999</v>
+        <v>7700.011999999998</v>
       </c>
       <c r="F73">
-        <v>11874.466</v>
+        <v>12041.712</v>
       </c>
       <c r="G73">
         <v>1169.2</v>
@@ -7279,37 +7279,37 @@
         <v>1031.4</v>
       </c>
       <c r="M73">
-        <v>2384.3927728</v>
+        <v>2417.9757696</v>
       </c>
       <c r="N73">
-        <v>-1352.9927728</v>
+        <v>-1386.5757696</v>
       </c>
       <c r="O73">
-        <v>-197.5369448288</v>
+        <v>-202.4400623615999</v>
       </c>
       <c r="P73">
-        <v>-1155.4558279712</v>
+        <v>-1184.1357072384</v>
       </c>
       <c r="Q73">
-        <v>-815.6558279711999</v>
+        <v>-844.3357072383997</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1393913780514748</v>
+        <v>0.1427339272675989</v>
       </c>
       <c r="T73">
-        <v>2.16146369633891</v>
+        <v>2.238658828351014</v>
       </c>
       <c r="U73">
         <v>0.2008</v>
       </c>
       <c r="V73">
-        <v>0.06315419242911405</v>
+        <v>0.06227705086759858</v>
       </c>
       <c r="W73">
-        <v>0.1881186381602339</v>
+        <v>0.1882947681857862</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7317,7 +7317,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.4325629618432469</v>
+        <v>0.4265551429287574</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7325,22 +7325,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1755377327286938</v>
+        <v>0.1770877327286938</v>
       </c>
       <c r="C74">
-        <v>-7521.009976305447</v>
+        <v>-7727.824243871327</v>
       </c>
       <c r="D74">
-        <v>3351.502023694551</v>
+        <v>3311.933756128672</v>
       </c>
       <c r="E74">
-        <v>7700.011999999998</v>
+        <v>7867.257999999999</v>
       </c>
       <c r="F74">
-        <v>12041.712</v>
+        <v>12208.958</v>
       </c>
       <c r="G74">
         <v>1169.2</v>
@@ -7361,37 +7361,37 @@
         <v>1031.4</v>
       </c>
       <c r="M74">
-        <v>2417.9757696</v>
+        <v>2451.5587664</v>
       </c>
       <c r="N74">
-        <v>-1386.5757696</v>
+        <v>-1420.1587664</v>
       </c>
       <c r="O74">
-        <v>-202.4400623615999</v>
+        <v>-207.3431798944</v>
       </c>
       <c r="P74">
-        <v>-1184.1357072384</v>
+        <v>-1212.8155865056</v>
       </c>
       <c r="Q74">
-        <v>-844.3357072383997</v>
+        <v>-873.0155865055999</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1427339272675989</v>
+        <v>0.1463240727219544</v>
       </c>
       <c r="T74">
-        <v>2.238658828351014</v>
+        <v>2.321572118289941</v>
       </c>
       <c r="U74">
         <v>0.2008</v>
       </c>
       <c r="V74">
-        <v>0.06227705086759858</v>
+        <v>0.06142394058174106</v>
       </c>
       <c r="W74">
-        <v>0.1882947681857862</v>
+        <v>0.1884660727311864</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7399,7 +7399,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.4265551429287574</v>
+        <v>0.420711921792747</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7407,22 +7407,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1770877327286938</v>
+        <v>0.1786377327286938</v>
       </c>
       <c r="C75">
-        <v>-7727.824243871327</v>
+        <v>-7933.71511695482</v>
       </c>
       <c r="D75">
-        <v>3311.933756128672</v>
+        <v>3273.288883045178</v>
       </c>
       <c r="E75">
-        <v>7867.257999999999</v>
+        <v>8034.503999999998</v>
       </c>
       <c r="F75">
-        <v>12208.958</v>
+        <v>12376.204</v>
       </c>
       <c r="G75">
         <v>1169.2</v>
@@ -7443,37 +7443,37 @@
         <v>1031.4</v>
       </c>
       <c r="M75">
-        <v>2451.5587664</v>
+        <v>2485.1417632</v>
       </c>
       <c r="N75">
-        <v>-1420.1587664</v>
+        <v>-1453.7417632</v>
       </c>
       <c r="O75">
-        <v>-207.3431798944</v>
+        <v>-212.2462974271999</v>
       </c>
       <c r="P75">
-        <v>-1212.8155865056</v>
+        <v>-1241.4954657728</v>
       </c>
       <c r="Q75">
-        <v>-873.0155865055999</v>
+        <v>-901.6954657727997</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1463240727219544</v>
+        <v>0.1501903832112604</v>
       </c>
       <c r="T75">
-        <v>2.321572118289941</v>
+        <v>2.410863353608784</v>
       </c>
       <c r="U75">
         <v>0.2008</v>
       </c>
       <c r="V75">
-        <v>0.06142394058174106</v>
+        <v>0.06059388733063645</v>
       </c>
       <c r="W75">
-        <v>0.1884660727311864</v>
+        <v>0.1886327474240082</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7481,7 +7481,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.420711921792747</v>
+        <v>0.4150266255523045</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7489,22 +7489,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1786377327286938</v>
+        <v>0.1801877327286938</v>
       </c>
       <c r="C76">
-        <v>-7933.71511695482</v>
+        <v>-8138.714546272381</v>
       </c>
       <c r="D76">
-        <v>3273.288883045178</v>
+        <v>3235.535453727618</v>
       </c>
       <c r="E76">
-        <v>8034.503999999998</v>
+        <v>8201.75</v>
       </c>
       <c r="F76">
-        <v>12376.204</v>
+        <v>12543.45</v>
       </c>
       <c r="G76">
         <v>1169.2</v>
@@ -7525,37 +7525,37 @@
         <v>1031.4</v>
       </c>
       <c r="M76">
-        <v>2485.1417632</v>
+        <v>2518.72476</v>
       </c>
       <c r="N76">
-        <v>-1453.7417632</v>
+        <v>-1487.32476</v>
       </c>
       <c r="O76">
-        <v>-212.2462974271999</v>
+        <v>-217.14941496</v>
       </c>
       <c r="P76">
-        <v>-1241.4954657728</v>
+        <v>-1270.17534504</v>
       </c>
       <c r="Q76">
-        <v>-901.6954657727997</v>
+        <v>-930.37534504</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1501903832112604</v>
+        <v>0.1543659985397108</v>
       </c>
       <c r="T76">
-        <v>2.410863353608784</v>
+        <v>2.507297887753136</v>
       </c>
       <c r="U76">
         <v>0.2008</v>
       </c>
       <c r="V76">
-        <v>0.06059388733063645</v>
+        <v>0.05978596883289463</v>
       </c>
       <c r="W76">
-        <v>0.1886327474240082</v>
+        <v>0.1887949774583547</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7563,7 +7563,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.4150266255523045</v>
+        <v>0.4094929372116071</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7571,22 +7571,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1801877327286938</v>
+        <v>0.1817377327286938</v>
       </c>
       <c r="C77">
-        <v>-8138.714546272381</v>
+        <v>-8342.853025296488</v>
       </c>
       <c r="D77">
-        <v>3235.535453727618</v>
+        <v>3198.642974703512</v>
       </c>
       <c r="E77">
-        <v>8201.75</v>
+        <v>8368.995999999999</v>
       </c>
       <c r="F77">
-        <v>12543.45</v>
+        <v>12710.696</v>
       </c>
       <c r="G77">
         <v>1169.2</v>
@@ -7607,37 +7607,37 @@
         <v>1031.4</v>
       </c>
       <c r="M77">
-        <v>2518.72476</v>
+        <v>2552.3077568</v>
       </c>
       <c r="N77">
-        <v>-1487.32476</v>
+        <v>-1520.9077568</v>
       </c>
       <c r="O77">
-        <v>-217.14941496</v>
+        <v>-222.0525324928</v>
       </c>
       <c r="P77">
-        <v>-1270.17534504</v>
+        <v>-1298.8552243072</v>
       </c>
       <c r="Q77">
-        <v>-930.37534504</v>
+        <v>-959.0552243072</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1543659985397108</v>
+        <v>0.1588895818121988</v>
       </c>
       <c r="T77">
-        <v>2.507297887753136</v>
+        <v>2.611768633076184</v>
       </c>
       <c r="U77">
         <v>0.2008</v>
       </c>
       <c r="V77">
-        <v>0.05978596883289463</v>
+        <v>0.05899931134825129</v>
       </c>
       <c r="W77">
-        <v>0.1887949774583547</v>
+        <v>0.1889529382812711</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.4094929372116071</v>
+        <v>0.4041048722482965</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7653,22 +7653,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1817377327286938</v>
+        <v>0.1832877327286938</v>
       </c>
       <c r="C78">
-        <v>-8342.853025296488</v>
+        <v>-8546.159672398539</v>
       </c>
       <c r="D78">
-        <v>3198.642974703512</v>
+        <v>3162.582327601461</v>
       </c>
       <c r="E78">
-        <v>8368.995999999999</v>
+        <v>8536.241999999998</v>
       </c>
       <c r="F78">
-        <v>12710.696</v>
+        <v>12877.942</v>
       </c>
       <c r="G78">
         <v>1169.2</v>
@@ -7689,37 +7689,37 @@
         <v>1031.4</v>
       </c>
       <c r="M78">
-        <v>2552.3077568</v>
+        <v>2585.8907536</v>
       </c>
       <c r="N78">
-        <v>-1520.9077568</v>
+        <v>-1554.4907536</v>
       </c>
       <c r="O78">
-        <v>-222.0525324928</v>
+        <v>-226.9556500255999</v>
       </c>
       <c r="P78">
-        <v>-1298.8552243072</v>
+        <v>-1327.5351035744</v>
       </c>
       <c r="Q78">
-        <v>-959.0552243072</v>
+        <v>-987.7351035743998</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1588895818121988</v>
+        <v>0.1638065201518596</v>
       </c>
       <c r="T78">
-        <v>2.611768633076184</v>
+        <v>2.725323791036018</v>
       </c>
       <c r="U78">
         <v>0.2008</v>
       </c>
       <c r="V78">
-        <v>0.05899931134825129</v>
+        <v>0.05823308652554672</v>
       </c>
       <c r="W78">
-        <v>0.1889529382812711</v>
+        <v>0.1891067962256702</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7727,7 +7727,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.4041048722482965</v>
+        <v>0.3988567570242927</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7735,22 +7735,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1832877327286938</v>
+        <v>0.1848377327286937</v>
       </c>
       <c r="C79">
-        <v>-8546.159672398539</v>
+        <v>-8748.662307497354</v>
       </c>
       <c r="D79">
-        <v>3162.582327601461</v>
+        <v>3127.325692502645</v>
       </c>
       <c r="E79">
-        <v>8536.241999999998</v>
+        <v>8703.488000000001</v>
       </c>
       <c r="F79">
-        <v>12877.942</v>
+        <v>13045.188</v>
       </c>
       <c r="G79">
         <v>1169.2</v>
@@ -7771,37 +7771,37 @@
         <v>1031.4</v>
       </c>
       <c r="M79">
-        <v>2585.8907536</v>
+        <v>2619.4737504</v>
       </c>
       <c r="N79">
-        <v>-1554.4907536</v>
+        <v>-1588.0737504</v>
       </c>
       <c r="O79">
-        <v>-226.9556500255999</v>
+        <v>-231.8587675584</v>
       </c>
       <c r="P79">
-        <v>-1327.5351035744</v>
+        <v>-1356.2149828416</v>
       </c>
       <c r="Q79">
-        <v>-987.7351035743998</v>
+        <v>-1016.4149828416</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1638065201518596</v>
+        <v>0.169170452886035</v>
       </c>
       <c r="T79">
-        <v>2.725323791036018</v>
+        <v>2.849202145174018</v>
       </c>
       <c r="U79">
         <v>0.2008</v>
       </c>
       <c r="V79">
-        <v>0.05823308652554672</v>
+        <v>0.05748650849316791</v>
       </c>
       <c r="W79">
-        <v>0.1891067962256702</v>
+        <v>0.1892567090945719</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7809,7 +7809,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.3988567570242927</v>
+        <v>0.3937432088573145</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7817,22 +7817,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1848377327286937</v>
+        <v>0.1863877327286938</v>
       </c>
       <c r="C80">
-        <v>-8748.662307497354</v>
+        <v>-8950.387523637311</v>
       </c>
       <c r="D80">
-        <v>3127.325692502645</v>
+        <v>3092.846476362688</v>
       </c>
       <c r="E80">
-        <v>8703.488000000001</v>
+        <v>8870.734</v>
       </c>
       <c r="F80">
-        <v>13045.188</v>
+        <v>13212.434</v>
       </c>
       <c r="G80">
         <v>1169.2</v>
@@ -7853,37 +7853,37 @@
         <v>1031.4</v>
       </c>
       <c r="M80">
-        <v>2619.4737504</v>
+        <v>2653.0567472</v>
       </c>
       <c r="N80">
-        <v>-1588.0737504</v>
+        <v>-1621.6567472</v>
       </c>
       <c r="O80">
-        <v>-231.8587675584</v>
+        <v>-236.7618850911999</v>
       </c>
       <c r="P80">
-        <v>-1356.2149828416</v>
+        <v>-1384.8948621088</v>
       </c>
       <c r="Q80">
-        <v>-1016.4149828416</v>
+        <v>-1045.0948621088</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.169170452886035</v>
+        <v>0.1750452363567986</v>
       </c>
       <c r="T80">
-        <v>2.849202145174018</v>
+        <v>2.984878437801354</v>
       </c>
       <c r="U80">
         <v>0.2008</v>
       </c>
       <c r="V80">
-        <v>0.05748650849316791</v>
+        <v>0.05675883117046959</v>
       </c>
       <c r="W80">
-        <v>0.1892567090945719</v>
+        <v>0.1894028267009697</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7891,7 +7891,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.3937432088573145</v>
+        <v>0.3887591176059562</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7899,22 +7899,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1863877327286938</v>
+        <v>0.1879377327286938</v>
       </c>
       <c r="C81">
-        <v>-8950.387523637311</v>
+        <v>-9151.360753883151</v>
       </c>
       <c r="D81">
-        <v>3092.846476362688</v>
+        <v>3059.119246116849</v>
       </c>
       <c r="E81">
-        <v>8870.734</v>
+        <v>9037.98</v>
       </c>
       <c r="F81">
-        <v>13212.434</v>
+        <v>13379.68</v>
       </c>
       <c r="G81">
         <v>1169.2</v>
@@ -7935,37 +7935,37 @@
         <v>1031.4</v>
       </c>
       <c r="M81">
-        <v>2653.0567472</v>
+        <v>2686.639744</v>
       </c>
       <c r="N81">
-        <v>-1621.6567472</v>
+        <v>-1655.239744</v>
       </c>
       <c r="O81">
-        <v>-236.7618850911999</v>
+        <v>-241.665002624</v>
       </c>
       <c r="P81">
-        <v>-1384.8948621088</v>
+        <v>-1413.574741376</v>
       </c>
       <c r="Q81">
-        <v>-1045.0948621088</v>
+        <v>-1073.774741376</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.1750452363567986</v>
+        <v>0.1815074981746386</v>
       </c>
       <c r="T81">
-        <v>2.984878437801354</v>
+        <v>3.134122359691421</v>
       </c>
       <c r="U81">
         <v>0.2008</v>
       </c>
       <c r="V81">
-        <v>0.05675883117046959</v>
+        <v>0.05604934578083871</v>
       </c>
       <c r="W81">
-        <v>0.1894028267009697</v>
+        <v>0.1895452913672076</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7973,7 +7973,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.3887591176059562</v>
+        <v>0.3838996286358817</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7981,22 +7981,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1879377327286938</v>
+        <v>0.1894877327286938</v>
       </c>
       <c r="C82">
-        <v>-9151.360753883151</v>
+        <v>-9351.606333885113</v>
       </c>
       <c r="D82">
-        <v>3059.119246116849</v>
+        <v>3026.119666114886</v>
       </c>
       <c r="E82">
-        <v>9037.98</v>
+        <v>9205.225999999999</v>
       </c>
       <c r="F82">
-        <v>13379.68</v>
+        <v>13546.926</v>
       </c>
       <c r="G82">
         <v>1169.2</v>
@@ -8017,37 +8017,37 @@
         <v>1031.4</v>
       </c>
       <c r="M82">
-        <v>2686.639744</v>
+        <v>2720.2227408</v>
       </c>
       <c r="N82">
-        <v>-1655.239744</v>
+        <v>-1688.8227408</v>
       </c>
       <c r="O82">
-        <v>-241.665002624</v>
+        <v>-246.5681201567999</v>
       </c>
       <c r="P82">
-        <v>-1413.574741376</v>
+        <v>-1442.2546206432</v>
       </c>
       <c r="Q82">
-        <v>-1073.774741376</v>
+        <v>-1102.4546206432</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.1815074981746386</v>
+        <v>0.1886499980785669</v>
       </c>
       <c r="T82">
-        <v>3.134122359691421</v>
+        <v>3.299076168096233</v>
       </c>
       <c r="U82">
         <v>0.2008</v>
       </c>
       <c r="V82">
-        <v>0.05604934578083871</v>
+        <v>0.05535737854897651</v>
       </c>
       <c r="W82">
-        <v>0.1895452913672076</v>
+        <v>0.1896842383873655</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8055,7 +8055,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.3838996286358817</v>
+        <v>0.3791601270477843</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8063,22 +8063,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1894877327286938</v>
+        <v>0.1910377327286938</v>
       </c>
       <c r="C83">
-        <v>-9351.606333885113</v>
+        <v>-9551.147560437843</v>
       </c>
       <c r="D83">
-        <v>3026.119666114886</v>
+        <v>2993.824439562157</v>
       </c>
       <c r="E83">
-        <v>9205.225999999999</v>
+        <v>9372.472000000002</v>
       </c>
       <c r="F83">
-        <v>13546.926</v>
+        <v>13714.172</v>
       </c>
       <c r="G83">
         <v>1169.2</v>
@@ -8099,37 +8099,37 @@
         <v>1031.4</v>
       </c>
       <c r="M83">
-        <v>2720.2227408</v>
+        <v>2753.8057376</v>
       </c>
       <c r="N83">
-        <v>-1688.8227408</v>
+        <v>-1722.4057376</v>
       </c>
       <c r="O83">
-        <v>-246.5681201567999</v>
+        <v>-251.4712376896</v>
       </c>
       <c r="P83">
-        <v>-1442.2546206432</v>
+        <v>-1470.9344999104</v>
       </c>
       <c r="Q83">
-        <v>-1102.4546206432</v>
+        <v>-1131.1344999104</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.1886499980785669</v>
+        <v>0.1965861090829318</v>
       </c>
       <c r="T83">
-        <v>3.299076168096233</v>
+        <v>3.482358177434913</v>
       </c>
       <c r="U83">
         <v>0.2008</v>
       </c>
       <c r="V83">
-        <v>0.05535737854897651</v>
+        <v>0.05468228856667191</v>
       </c>
       <c r="W83">
-        <v>0.1896842383873655</v>
+        <v>0.1898197964558123</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8137,7 +8137,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.3791601270477843</v>
+        <v>0.3745362230593967</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8145,22 +8145,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1910377327286938</v>
+        <v>0.1925877327286938</v>
       </c>
       <c r="C84">
-        <v>-9551.147560437843</v>
+        <v>-9750.006746329189</v>
       </c>
       <c r="D84">
-        <v>2993.824439562157</v>
+        <v>2962.211253670811</v>
       </c>
       <c r="E84">
-        <v>9372.472000000002</v>
+        <v>9539.718000000001</v>
       </c>
       <c r="F84">
-        <v>13714.172</v>
+        <v>13881.418</v>
       </c>
       <c r="G84">
         <v>1169.2</v>
@@ -8181,37 +8181,37 @@
         <v>1031.4</v>
       </c>
       <c r="M84">
-        <v>2753.8057376</v>
+        <v>2787.3887344</v>
       </c>
       <c r="N84">
-        <v>-1722.4057376</v>
+        <v>-1755.9887344</v>
       </c>
       <c r="O84">
-        <v>-251.4712376896</v>
+        <v>-256.3743552224</v>
       </c>
       <c r="P84">
-        <v>-1470.9344999104</v>
+        <v>-1499.6143791776</v>
       </c>
       <c r="Q84">
-        <v>-1131.1344999104</v>
+        <v>-1159.8143791776</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.1965861090829318</v>
+        <v>0.2054558802054571</v>
       </c>
       <c r="T84">
-        <v>3.482358177434913</v>
+        <v>3.687202776107554</v>
       </c>
       <c r="U84">
         <v>0.2008</v>
       </c>
       <c r="V84">
-        <v>0.05468228856667191</v>
+        <v>0.05402346581285659</v>
       </c>
       <c r="W84">
-        <v>0.1898197964558123</v>
+        <v>0.1899520880647784</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8219,7 +8219,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.3745362230593967</v>
+        <v>0.3700237384442233</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8227,22 +8227,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1925877327286938</v>
+        <v>0.1941377327286938</v>
       </c>
       <c r="C85">
-        <v>-9750.006746329189</v>
+        <v>-9948.205271750267</v>
       </c>
       <c r="D85">
-        <v>2962.211253670811</v>
+        <v>2931.258728249734</v>
       </c>
       <c r="E85">
-        <v>9539.718000000001</v>
+        <v>9706.964</v>
       </c>
       <c r="F85">
-        <v>13881.418</v>
+        <v>14048.664</v>
       </c>
       <c r="G85">
         <v>1169.2</v>
@@ -8263,37 +8263,37 @@
         <v>1031.4</v>
       </c>
       <c r="M85">
-        <v>2787.3887344</v>
+        <v>2820.9717312</v>
       </c>
       <c r="N85">
-        <v>-1755.9887344</v>
+        <v>-1789.5717312</v>
       </c>
       <c r="O85">
-        <v>-256.3743552224</v>
+        <v>-261.2774727552</v>
       </c>
       <c r="P85">
-        <v>-1499.6143791776</v>
+        <v>-1528.2942584448</v>
       </c>
       <c r="Q85">
-        <v>-1159.8143791776</v>
+        <v>-1188.4942584448</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2054558802054571</v>
+        <v>0.2154343727182982</v>
       </c>
       <c r="T85">
-        <v>3.687202776107554</v>
+        <v>3.917652949614277</v>
       </c>
       <c r="U85">
         <v>0.2008</v>
       </c>
       <c r="V85">
-        <v>0.05402346581285659</v>
+        <v>0.05338032931508449</v>
       </c>
       <c r="W85">
-        <v>0.1899520880647784</v>
+        <v>0.190081229873531</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8301,7 +8301,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.3700237384442233</v>
+        <v>0.3656186939389349</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8309,22 +8309,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1941377327286938</v>
+        <v>0.1956877327286938</v>
       </c>
       <c r="C86">
-        <v>-9948.205271750265</v>
+        <v>-10145.76363251571</v>
       </c>
       <c r="D86">
-        <v>2931.258728249734</v>
+        <v>2900.946367484288</v>
       </c>
       <c r="E86">
-        <v>9706.964</v>
+        <v>9874.209999999999</v>
       </c>
       <c r="F86">
-        <v>14048.664</v>
+        <v>14215.91</v>
       </c>
       <c r="G86">
         <v>1169.2</v>
@@ -8345,37 +8345,37 @@
         <v>1031.4</v>
       </c>
       <c r="M86">
-        <v>2820.9717312</v>
+        <v>2854.554728</v>
       </c>
       <c r="N86">
-        <v>-1789.5717312</v>
+        <v>-1823.154728</v>
       </c>
       <c r="O86">
-        <v>-261.2774727551999</v>
+        <v>-266.1805902879999</v>
       </c>
       <c r="P86">
-        <v>-1528.2942584448</v>
+        <v>-1556.974137712</v>
       </c>
       <c r="Q86">
-        <v>-1188.4942584448</v>
+        <v>-1217.174137712</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2154343727182981</v>
+        <v>0.226743330899518</v>
       </c>
       <c r="T86">
-        <v>3.917652949614275</v>
+        <v>4.178829812921894</v>
       </c>
       <c r="U86">
         <v>0.2008</v>
       </c>
       <c r="V86">
-        <v>0.0533803293150845</v>
+        <v>0.05275232544078939</v>
       </c>
       <c r="W86">
-        <v>0.190081229873531</v>
+        <v>0.1902073330514895</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8383,7 +8383,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.3656186939389349</v>
+        <v>0.3613172975396534</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8391,22 +8391,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1956877327286938</v>
+        <v>0.1972377327286938</v>
       </c>
       <c r="C87">
-        <v>-10145.76363251571</v>
+        <v>-10342.70148532268</v>
       </c>
       <c r="D87">
-        <v>2900.946367484288</v>
+        <v>2871.254514677324</v>
       </c>
       <c r="E87">
-        <v>9874.209999999999</v>
+        <v>10041.456</v>
       </c>
       <c r="F87">
-        <v>14215.91</v>
+        <v>14383.156</v>
       </c>
       <c r="G87">
         <v>1169.2</v>
@@ -8427,37 +8427,37 @@
         <v>1031.4</v>
       </c>
       <c r="M87">
-        <v>2854.554728</v>
+        <v>2888.1377248</v>
       </c>
       <c r="N87">
-        <v>-1823.154728</v>
+        <v>-1856.7377248</v>
       </c>
       <c r="O87">
-        <v>-266.1805902879999</v>
+        <v>-271.0837078207999</v>
       </c>
       <c r="P87">
-        <v>-1556.974137712</v>
+        <v>-1585.6540169792</v>
       </c>
       <c r="Q87">
-        <v>-1217.174137712</v>
+        <v>-1245.8540169792</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.226743330899518</v>
+        <v>0.2396678545351979</v>
       </c>
       <c r="T87">
-        <v>4.178829812921894</v>
+        <v>4.477317656702029</v>
       </c>
       <c r="U87">
         <v>0.2008</v>
       </c>
       <c r="V87">
-        <v>0.05275232544078939</v>
+        <v>0.05213892630775695</v>
       </c>
       <c r="W87">
-        <v>0.1902073330514895</v>
+        <v>0.1903305035974024</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8465,7 +8465,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.3613172975396534</v>
+        <v>0.3571159336147737</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8473,22 +8473,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1972377327286938</v>
+        <v>0.1987877327286938</v>
       </c>
       <c r="C88">
-        <v>-10342.70148532268</v>
+        <v>-10539.03769025853</v>
       </c>
       <c r="D88">
-        <v>2871.254514677324</v>
+        <v>2842.164309741466</v>
       </c>
       <c r="E88">
-        <v>10041.456</v>
+        <v>10208.702</v>
       </c>
       <c r="F88">
-        <v>14383.156</v>
+        <v>14550.402</v>
       </c>
       <c r="G88">
         <v>1169.2</v>
@@ -8509,37 +8509,37 @@
         <v>1031.4</v>
       </c>
       <c r="M88">
-        <v>2888.1377248</v>
+        <v>2921.7207216</v>
       </c>
       <c r="N88">
-        <v>-1856.7377248</v>
+        <v>-1890.3207216</v>
       </c>
       <c r="O88">
-        <v>-271.0837078207999</v>
+        <v>-275.9868253536</v>
       </c>
       <c r="P88">
-        <v>-1585.6540169792</v>
+        <v>-1614.3338962464</v>
       </c>
       <c r="Q88">
-        <v>-1245.8540169792</v>
+        <v>-1274.5338962464</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.2396678545351979</v>
+        <v>0.2545807664225208</v>
       </c>
       <c r="T88">
-        <v>4.477317656702029</v>
+        <v>4.821726707217569</v>
       </c>
       <c r="U88">
         <v>0.2008</v>
       </c>
       <c r="V88">
-        <v>0.05213892630775695</v>
+        <v>0.05153962830421951</v>
       </c>
       <c r="W88">
-        <v>0.1903305035974024</v>
+        <v>0.1904508426365127</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8547,7 +8547,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.3571159336147737</v>
+        <v>0.3530111527686268</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8555,22 +8555,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1987877327286938</v>
+        <v>0.2003377327286938</v>
       </c>
       <c r="C89">
-        <v>-10539.03769025853</v>
+        <v>-10734.79035075053</v>
       </c>
       <c r="D89">
-        <v>2842.164309741466</v>
+        <v>2813.657649249473</v>
       </c>
       <c r="E89">
-        <v>10208.702</v>
+        <v>10375.948</v>
       </c>
       <c r="F89">
-        <v>14550.402</v>
+        <v>14717.648</v>
       </c>
       <c r="G89">
         <v>1169.2</v>
@@ -8591,37 +8591,37 @@
         <v>1031.4</v>
       </c>
       <c r="M89">
-        <v>2921.7207216</v>
+        <v>2955.3037184</v>
       </c>
       <c r="N89">
-        <v>-1890.3207216</v>
+        <v>-1923.9037184</v>
       </c>
       <c r="O89">
-        <v>-275.9868253536</v>
+        <v>-280.8899428864</v>
       </c>
       <c r="P89">
-        <v>-1614.3338962464</v>
+        <v>-1643.0137755136</v>
       </c>
       <c r="Q89">
-        <v>-1274.5338962464</v>
+        <v>-1303.2137755136</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.2545807664225208</v>
+        <v>0.2719791636243975</v>
       </c>
       <c r="T89">
-        <v>4.821726707217569</v>
+        <v>5.223537266152367</v>
       </c>
       <c r="U89">
         <v>0.2008</v>
       </c>
       <c r="V89">
-        <v>0.05153962830421951</v>
+        <v>0.05095395070985338</v>
       </c>
       <c r="W89">
-        <v>0.1904508426365127</v>
+        <v>0.1905684466974615</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8629,7 +8629,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.3530111527686268</v>
+        <v>0.348999662396256</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8637,22 +8637,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2003377327286938</v>
+        <v>0.2018877327286938</v>
       </c>
       <c r="C90">
-        <v>-10734.79035075053</v>
+        <v>-10929.97685113512</v>
       </c>
       <c r="D90">
-        <v>2813.657649249473</v>
+        <v>2785.717148864876</v>
       </c>
       <c r="E90">
-        <v>10375.948</v>
+        <v>10543.194</v>
       </c>
       <c r="F90">
-        <v>14717.648</v>
+        <v>14884.894</v>
       </c>
       <c r="G90">
         <v>1169.2</v>
@@ -8673,37 +8673,37 @@
         <v>1031.4</v>
       </c>
       <c r="M90">
-        <v>2955.3037184</v>
+        <v>2988.8867152</v>
       </c>
       <c r="N90">
-        <v>-1923.9037184</v>
+        <v>-1957.4867152</v>
       </c>
       <c r="O90">
-        <v>-280.8899428864</v>
+        <v>-285.7930604191999</v>
       </c>
       <c r="P90">
-        <v>-1643.0137755136</v>
+        <v>-1671.6936547808</v>
       </c>
       <c r="Q90">
-        <v>-1303.2137755136</v>
+        <v>-1331.8936547808</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.2719791636243975</v>
+        <v>0.2925409057720701</v>
       </c>
       <c r="T90">
-        <v>5.223537266152367</v>
+        <v>5.698404290348038</v>
       </c>
       <c r="U90">
         <v>0.2008</v>
       </c>
       <c r="V90">
-        <v>0.05095395070985338</v>
+        <v>0.05038143440974267</v>
       </c>
       <c r="W90">
-        <v>0.1905684466974615</v>
+        <v>0.1906834079705237</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8711,7 +8711,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.348999662396256</v>
+        <v>0.3450783178749498</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8719,22 +8719,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2018877327286938</v>
+        <v>0.2034377327286938</v>
       </c>
       <c r="C91">
-        <v>-10929.97685113512</v>
+        <v>-11124.61389201092</v>
       </c>
       <c r="D91">
-        <v>2785.717148864876</v>
+        <v>2758.326107989075</v>
       </c>
       <c r="E91">
-        <v>10543.194</v>
+        <v>10710.44</v>
       </c>
       <c r="F91">
-        <v>14884.894</v>
+        <v>15052.14</v>
       </c>
       <c r="G91">
         <v>1169.2</v>
@@ -8755,37 +8755,37 @@
         <v>1031.4</v>
       </c>
       <c r="M91">
-        <v>2988.8867152</v>
+        <v>3022.469712</v>
       </c>
       <c r="N91">
-        <v>-1957.4867152</v>
+        <v>-1991.069712</v>
       </c>
       <c r="O91">
-        <v>-285.7930604191999</v>
+        <v>-290.696177952</v>
       </c>
       <c r="P91">
-        <v>-1671.6936547808</v>
+        <v>-1700.373534048</v>
       </c>
       <c r="Q91">
-        <v>-1331.8936547808</v>
+        <v>-1360.573534048</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.2925409057720701</v>
+        <v>0.317214996349277</v>
       </c>
       <c r="T91">
-        <v>5.698404290348038</v>
+        <v>6.268244719382841</v>
       </c>
       <c r="U91">
         <v>0.2008</v>
       </c>
       <c r="V91">
-        <v>0.05038143440974267</v>
+        <v>0.04982164069407886</v>
       </c>
       <c r="W91">
-        <v>0.1906834079705237</v>
+        <v>0.190795814548629</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8793,7 +8793,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.3450783178749498</v>
+        <v>0.3412441143430058</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8801,22 +8801,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2034377327286938</v>
+        <v>0.2049877327286938</v>
       </c>
       <c r="C92">
-        <v>-11124.61389201092</v>
+        <v>-11318.71752352622</v>
       </c>
       <c r="D92">
-        <v>2758.326107989075</v>
+        <v>2731.468476473776</v>
       </c>
       <c r="E92">
-        <v>10710.44</v>
+        <v>10877.686</v>
       </c>
       <c r="F92">
-        <v>15052.14</v>
+        <v>15219.386</v>
       </c>
       <c r="G92">
         <v>1169.2</v>
@@ -8837,37 +8837,37 @@
         <v>1031.4</v>
       </c>
       <c r="M92">
-        <v>3022.469712</v>
+        <v>3056.0527088</v>
       </c>
       <c r="N92">
-        <v>-1991.069712</v>
+        <v>-2024.6527088</v>
       </c>
       <c r="O92">
-        <v>-290.696177952</v>
+        <v>-295.5992954847999</v>
       </c>
       <c r="P92">
-        <v>-1700.373534048</v>
+        <v>-1729.0534133152</v>
       </c>
       <c r="Q92">
-        <v>-1360.573534048</v>
+        <v>-1389.2534133152</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.317214996349277</v>
+        <v>0.3473722181658634</v>
       </c>
       <c r="T92">
-        <v>6.268244719382841</v>
+        <v>6.964716354869824</v>
       </c>
       <c r="U92">
         <v>0.2008</v>
       </c>
       <c r="V92">
-        <v>0.04982164069407886</v>
+        <v>0.04927415013700107</v>
       </c>
       <c r="W92">
-        <v>0.190795814548629</v>
+        <v>0.1909057506524902</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8875,7 +8875,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.3412441143430058</v>
+        <v>0.3374941790205553</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8883,22 +8883,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2049877327286938</v>
+        <v>0.2065377327286938</v>
       </c>
       <c r="C93">
-        <v>-11318.71752352622</v>
+        <v>-11512.30317674057</v>
       </c>
       <c r="D93">
-        <v>2731.468476473776</v>
+        <v>2705.128823259429</v>
       </c>
       <c r="E93">
-        <v>10877.686</v>
+        <v>11044.932</v>
       </c>
       <c r="F93">
-        <v>15219.386</v>
+        <v>15386.632</v>
       </c>
       <c r="G93">
         <v>1169.2</v>
@@ -8919,37 +8919,37 @@
         <v>1031.4</v>
       </c>
       <c r="M93">
-        <v>3056.0527088</v>
+        <v>3089.6357056</v>
       </c>
       <c r="N93">
-        <v>-2024.6527088</v>
+        <v>-2058.2357056</v>
       </c>
       <c r="O93">
-        <v>-295.5992954847999</v>
+        <v>-300.5024130176</v>
       </c>
       <c r="P93">
-        <v>-1729.0534133152</v>
+        <v>-1757.7332925824</v>
       </c>
       <c r="Q93">
-        <v>-1389.2534133152</v>
+        <v>-1417.9332925824</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.3473722181658634</v>
+        <v>0.3850687454365965</v>
       </c>
       <c r="T93">
-        <v>6.964716354869824</v>
+        <v>7.835305899228555</v>
       </c>
       <c r="U93">
         <v>0.2008</v>
       </c>
       <c r="V93">
-        <v>0.04927415013700107</v>
+        <v>0.0487385615485554</v>
       </c>
       <c r="W93">
-        <v>0.1909057506524902</v>
+        <v>0.1910132968410501</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8957,7 +8957,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.3374941790205553</v>
+        <v>0.3338257640312013</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8965,22 +8965,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2065377327286938</v>
+        <v>0.2080877327286938</v>
       </c>
       <c r="C94">
-        <v>-11512.30317674057</v>
+        <v>-11705.38569318918</v>
       </c>
       <c r="D94">
-        <v>2705.128823259429</v>
+        <v>2679.292306810822</v>
       </c>
       <c r="E94">
-        <v>11044.932</v>
+        <v>11212.178</v>
       </c>
       <c r="F94">
-        <v>15386.632</v>
+        <v>15553.878</v>
       </c>
       <c r="G94">
         <v>1169.2</v>
@@ -9001,37 +9001,37 @@
         <v>1031.4</v>
       </c>
       <c r="M94">
-        <v>3089.6357056</v>
+        <v>3123.2187024</v>
       </c>
       <c r="N94">
-        <v>-2058.2357056</v>
+        <v>-2091.8187024</v>
       </c>
       <c r="O94">
-        <v>-300.5024130176</v>
+        <v>-305.4055305504</v>
       </c>
       <c r="P94">
-        <v>-1757.7332925824</v>
+        <v>-1786.4131718496</v>
       </c>
       <c r="Q94">
-        <v>-1417.9332925824</v>
+        <v>-1446.6131718496</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.3850687454365965</v>
+        <v>0.433535709070396</v>
       </c>
       <c r="T94">
-        <v>7.835305899228555</v>
+        <v>8.954635313404063</v>
       </c>
       <c r="U94">
         <v>0.2008</v>
       </c>
       <c r="V94">
-        <v>0.0487385615485554</v>
+        <v>0.04821449099426986</v>
       </c>
       <c r="W94">
-        <v>0.1910132968410501</v>
+        <v>0.1911185302083506</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9039,7 +9039,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.3338257640312013</v>
+        <v>0.33023623968678</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9047,22 +9047,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2080877327286938</v>
+        <v>0.2096377327286938</v>
       </c>
       <c r="C95">
-        <v>-11705.38569318918</v>
+        <v>-11897.97935276912</v>
       </c>
       <c r="D95">
-        <v>2679.292306810822</v>
+        <v>2653.944647230876</v>
       </c>
       <c r="E95">
-        <v>11212.178</v>
+        <v>11379.424</v>
       </c>
       <c r="F95">
-        <v>15553.878</v>
+        <v>15721.124</v>
       </c>
       <c r="G95">
         <v>1169.2</v>
@@ -9083,37 +9083,37 @@
         <v>1031.4</v>
       </c>
       <c r="M95">
-        <v>3123.2187024</v>
+        <v>3156.8016992</v>
       </c>
       <c r="N95">
-        <v>-2091.8187024</v>
+        <v>-2125.4016992</v>
       </c>
       <c r="O95">
-        <v>-305.4055305504</v>
+        <v>-310.3086480832</v>
       </c>
       <c r="P95">
-        <v>-1786.4131718496</v>
+        <v>-1815.0930511168</v>
       </c>
       <c r="Q95">
-        <v>-1446.6131718496</v>
+        <v>-1475.2930511168</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.433535709070396</v>
+        <v>0.4981583272487954</v>
       </c>
       <c r="T95">
-        <v>8.954635313404063</v>
+        <v>10.44707453230474</v>
       </c>
       <c r="U95">
         <v>0.2008</v>
       </c>
       <c r="V95">
-        <v>0.04821449099426986</v>
+        <v>0.04770157087730954</v>
       </c>
       <c r="W95">
-        <v>0.1911185302083506</v>
+        <v>0.1912215245678363</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9121,7 +9121,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.33023623968678</v>
+        <v>0.3267230882007502</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9129,22 +9129,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2096377327286938</v>
+        <v>0.2111877327286938</v>
       </c>
       <c r="C96">
-        <v>-11897.97935276912</v>
+        <v>-12090.09790005747</v>
       </c>
       <c r="D96">
-        <v>2653.944647230876</v>
+        <v>2629.072099942524</v>
       </c>
       <c r="E96">
-        <v>11379.424</v>
+        <v>11546.67</v>
       </c>
       <c r="F96">
-        <v>15721.124</v>
+        <v>15888.37</v>
       </c>
       <c r="G96">
         <v>1169.2</v>
@@ -9165,37 +9165,37 @@
         <v>1031.4</v>
       </c>
       <c r="M96">
-        <v>3156.8016992</v>
+        <v>3190.384696</v>
       </c>
       <c r="N96">
-        <v>-2125.4016992</v>
+        <v>-2158.984696</v>
       </c>
       <c r="O96">
-        <v>-310.3086480832</v>
+        <v>-315.211765616</v>
       </c>
       <c r="P96">
-        <v>-1815.0930511168</v>
+        <v>-1843.772930384</v>
       </c>
       <c r="Q96">
-        <v>-1475.2930511168</v>
+        <v>-1503.972930384</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.4981583272487954</v>
+        <v>0.5886299926985549</v>
       </c>
       <c r="T96">
-        <v>10.44707453230474</v>
+        <v>12.5364894387657</v>
       </c>
       <c r="U96">
         <v>0.2008</v>
       </c>
       <c r="V96">
-        <v>0.04770157087730954</v>
+        <v>0.04719944907860102</v>
       </c>
       <c r="W96">
-        <v>0.1912215245678363</v>
+        <v>0.1913223506250169</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9203,7 +9203,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.3267230882007502</v>
+        <v>0.3232838977986372</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9211,22 +9211,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2111877327286938</v>
+        <v>0.2127377327286938</v>
       </c>
       <c r="C97">
-        <v>-12090.09790005747</v>
+        <v>-12281.75456916327</v>
       </c>
       <c r="D97">
-        <v>2629.072099942524</v>
+        <v>2604.661430836734</v>
       </c>
       <c r="E97">
-        <v>11546.67</v>
+        <v>11713.916</v>
       </c>
       <c r="F97">
-        <v>15888.37</v>
+        <v>16055.616</v>
       </c>
       <c r="G97">
         <v>1169.2</v>
@@ -9247,37 +9247,37 @@
         <v>1031.4</v>
       </c>
       <c r="M97">
-        <v>3190.384696</v>
+        <v>3223.9676928</v>
       </c>
       <c r="N97">
-        <v>-2158.984696</v>
+        <v>-2192.5676928</v>
       </c>
       <c r="O97">
-        <v>-315.211765616</v>
+        <v>-320.1148831487999</v>
       </c>
       <c r="P97">
-        <v>-1843.772930384</v>
+        <v>-1872.4528096512</v>
       </c>
       <c r="Q97">
-        <v>-1503.972930384</v>
+        <v>-1532.6528096512</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.5886299926985549</v>
+        <v>0.7243374908731938</v>
       </c>
       <c r="T97">
-        <v>12.5364894387657</v>
+        <v>15.67061179845713</v>
       </c>
       <c r="U97">
         <v>0.2008</v>
       </c>
       <c r="V97">
-        <v>0.04719944907860102</v>
+        <v>0.04670778815069893</v>
       </c>
       <c r="W97">
-        <v>0.1913223506250169</v>
+        <v>0.1914210761393396</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9285,7 +9285,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.3232838977986372</v>
+        <v>0.3199163571965681</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9293,22 +9293,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2127377327286938</v>
+        <v>0.2142877327286938</v>
       </c>
       <c r="C98">
-        <v>-12281.75456916326</v>
+        <v>-12472.96210720768</v>
       </c>
       <c r="D98">
-        <v>2604.661430836734</v>
+        <v>2580.699892792314</v>
       </c>
       <c r="E98">
-        <v>11713.916</v>
+        <v>11881.162</v>
       </c>
       <c r="F98">
-        <v>16055.616</v>
+        <v>16222.862</v>
       </c>
       <c r="G98">
         <v>1169.2</v>
@@ -9329,37 +9329,37 @@
         <v>1031.4</v>
       </c>
       <c r="M98">
-        <v>3223.9676928</v>
+        <v>3257.5506896</v>
       </c>
       <c r="N98">
-        <v>-2192.5676928</v>
+        <v>-2226.1506896</v>
       </c>
       <c r="O98">
-        <v>-320.1148831487999</v>
+        <v>-325.0180006815999</v>
       </c>
       <c r="P98">
-        <v>-1872.4528096512</v>
+        <v>-1901.1326889184</v>
       </c>
       <c r="Q98">
-        <v>-1532.6528096512</v>
+        <v>-1561.3326889184</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.7243374908731919</v>
+        <v>0.9505166544975893</v>
       </c>
       <c r="T98">
-        <v>15.67061179845709</v>
+        <v>20.89414906460945</v>
       </c>
       <c r="U98">
         <v>0.2008</v>
       </c>
       <c r="V98">
-        <v>0.04670778815069893</v>
+        <v>0.04622626456151648</v>
       </c>
       <c r="W98">
-        <v>0.1914210761393396</v>
+        <v>0.1915177660760475</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9367,7 +9367,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.3199163571965681</v>
+        <v>0.3166182504213457</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9375,22 +9375,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2142877327286938</v>
+        <v>0.2158377327286937</v>
       </c>
       <c r="C99">
-        <v>-12472.96210720768</v>
+        <v>-12663.73279652009</v>
       </c>
       <c r="D99">
-        <v>2580.699892792314</v>
+        <v>2557.175203479909</v>
       </c>
       <c r="E99">
-        <v>11881.162</v>
+        <v>12048.408</v>
       </c>
       <c r="F99">
-        <v>16222.862</v>
+        <v>16390.108</v>
       </c>
       <c r="G99">
         <v>1169.2</v>
@@ -9411,37 +9411,37 @@
         <v>1031.4</v>
       </c>
       <c r="M99">
-        <v>3257.5506896</v>
+        <v>3291.1336864</v>
       </c>
       <c r="N99">
-        <v>-2226.1506896</v>
+        <v>-2259.733686399999</v>
       </c>
       <c r="O99">
-        <v>-325.0180006815999</v>
+        <v>-329.9211182143999</v>
       </c>
       <c r="P99">
-        <v>-1901.1326889184</v>
+        <v>-1929.8125681856</v>
       </c>
       <c r="Q99">
-        <v>-1561.3326889184</v>
+        <v>-1590.0125681856</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>0.9505166544975893</v>
+        <v>1.402874981746384</v>
       </c>
       <c r="T99">
-        <v>20.89414906460945</v>
+        <v>31.34122359691417</v>
       </c>
       <c r="U99">
         <v>0.2008</v>
       </c>
       <c r="V99">
-        <v>0.04622626456151648</v>
+        <v>0.04575456798435814</v>
       </c>
       <c r="W99">
-        <v>0.1915177660760475</v>
+        <v>0.1916124827487409</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9449,7 +9449,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.3166182504213457</v>
+        <v>0.3133874519476585</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9457,22 +9457,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2158377327286937</v>
+        <v>0.2173877327286937</v>
       </c>
       <c r="C100">
-        <v>-12663.73279652009</v>
+        <v>-12854.07847563095</v>
       </c>
       <c r="D100">
-        <v>2557.175203479909</v>
+        <v>2534.075524369044</v>
       </c>
       <c r="E100">
-        <v>12048.408</v>
+        <v>12215.654</v>
       </c>
       <c r="F100">
-        <v>16390.108</v>
+        <v>16557.354</v>
       </c>
       <c r="G100">
         <v>1169.2</v>
@@ -9493,37 +9493,37 @@
         <v>1031.4</v>
       </c>
       <c r="M100">
-        <v>3291.1336864</v>
+        <v>3324.7166832</v>
       </c>
       <c r="N100">
-        <v>-2259.733686399999</v>
+        <v>-2293.3166832</v>
       </c>
       <c r="O100">
-        <v>-329.9211182143999</v>
+        <v>-334.8242357472</v>
       </c>
       <c r="P100">
-        <v>-1929.8125681856</v>
+        <v>-1958.4924474528</v>
       </c>
       <c r="Q100">
-        <v>-1590.0125681856</v>
+        <v>-1618.6924474528</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.402874981746384</v>
+        <v>2.759949963492768</v>
       </c>
       <c r="T100">
-        <v>31.34122359691417</v>
+        <v>62.68244719382835</v>
       </c>
       <c r="U100">
         <v>0.2008</v>
       </c>
       <c r="V100">
-        <v>0.04575456798435814</v>
+        <v>0.04529240063098079</v>
       </c>
       <c r="W100">
-        <v>0.1916124827487409</v>
+        <v>0.1917052859532991</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9531,91 +9531,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.3133874519476585</v>
+        <v>0.3102219221300053</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2173877327286937</v>
-      </c>
-      <c r="C101">
-        <v>-12854.07847563095</v>
-      </c>
-      <c r="D101">
-        <v>2534.075524369044</v>
-      </c>
-      <c r="E101">
-        <v>12215.654</v>
-      </c>
-      <c r="F101">
-        <v>16557.354</v>
-      </c>
-      <c r="G101">
-        <v>1169.2</v>
-      </c>
-      <c r="H101">
-        <v>12382.9</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>1371.2</v>
-      </c>
-      <c r="K101">
-        <v>339.8</v>
-      </c>
-      <c r="L101">
-        <v>1031.4</v>
-      </c>
-      <c r="M101">
-        <v>3324.7166832</v>
-      </c>
-      <c r="N101">
-        <v>-2293.3166832</v>
-      </c>
-      <c r="O101">
-        <v>-334.8242357472</v>
-      </c>
-      <c r="P101">
-        <v>-1958.4924474528</v>
-      </c>
-      <c r="Q101">
-        <v>-1618.6924474528</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>2.759949963492768</v>
-      </c>
-      <c r="T101">
-        <v>62.68244719382835</v>
-      </c>
-      <c r="U101">
-        <v>0.2008</v>
-      </c>
-      <c r="V101">
-        <v>0.04529240063098079</v>
-      </c>
-      <c r="W101">
-        <v>0.1917052859532991</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>C2/C</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.3102219221300053</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
